--- a/target project.xlsx
+++ b/target project.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="147">
   <si>
     <t xml:space="preserve"> cek ulang tampilan dashboard bad produk mesin dominan, masih menampilkan data mesin yang tidak di pilih di sortasi,</t>
   </si>
@@ -485,6 +485,9 @@
   </si>
   <si>
     <t>menambahkan portal produktifitas di packing</t>
+  </si>
+  <si>
+    <t>macam-macam sortasi : sortasi - release, sortasi - tampung, sortasi - kasar</t>
   </si>
 </sst>
 </file>
@@ -1895,16 +1898,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1925,20 +1949,11 @@
     <xf numFmtId="1" fontId="5" fillId="10" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,17 +1961,11 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1976,8 +1985,11 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1992,15 +2004,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4924,7 +4927,7 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="154" t="s">
+      <c r="D8" s="157" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4934,7 +4937,7 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="155"/>
+      <c r="D9" s="158"/>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
@@ -4942,7 +4945,7 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="154" t="s">
+      <c r="D10" s="157" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4952,7 +4955,7 @@
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="155"/>
+      <c r="D11" s="158"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
@@ -5061,7 +5064,7 @@
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="187">
+      <c r="A24" s="154">
         <v>46266</v>
       </c>
       <c r="B24" s="152"/>
@@ -5072,8 +5075,8 @@
       <c r="A25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="189"/>
-      <c r="C25" s="188"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="155"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4">
@@ -5089,7 +5092,7 @@
         <v>143</v>
       </c>
       <c r="B27" s="152"/>
-      <c r="C27" s="188"/>
+      <c r="C27" s="155"/>
       <c r="D27" s="1"/>
     </row>
     <row r="28" spans="1:4">
@@ -5109,7 +5112,9 @@
       <c r="D29" s="1"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>146</v>
+      </c>
       <c r="B30" s="13"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -10825,141 +10830,141 @@
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
-      <c r="K4" s="164" t="s">
+      <c r="K4" s="159" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="156"/>
-      <c r="M4" s="165"/>
-      <c r="O4" s="164" t="s">
+      <c r="L4" s="160"/>
+      <c r="M4" s="161"/>
+      <c r="O4" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="156"/>
-      <c r="Q4" s="165"/>
-      <c r="S4" s="164" t="s">
+      <c r="P4" s="160"/>
+      <c r="Q4" s="161"/>
+      <c r="S4" s="159" t="s">
         <v>49</v>
       </c>
-      <c r="T4" s="156"/>
-      <c r="U4" s="165"/>
-      <c r="W4" s="164" t="s">
+      <c r="T4" s="160"/>
+      <c r="U4" s="161"/>
+      <c r="W4" s="159" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="156"/>
-      <c r="Y4" s="165"/>
-      <c r="AA4" s="164" t="s">
+      <c r="X4" s="160"/>
+      <c r="Y4" s="161"/>
+      <c r="AA4" s="159" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="156"/>
-      <c r="AC4" s="156"/>
+      <c r="AB4" s="160"/>
+      <c r="AC4" s="160"/>
       <c r="AD4" s="29"/>
-      <c r="AF4" s="164" t="s">
+      <c r="AF4" s="159" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="156"/>
-      <c r="AH4" s="165"/>
-      <c r="AJ4" s="164" t="s">
+      <c r="AG4" s="160"/>
+      <c r="AH4" s="161"/>
+      <c r="AJ4" s="159" t="s">
         <v>53</v>
       </c>
-      <c r="AK4" s="156"/>
-      <c r="AL4" s="156"/>
-      <c r="AN4" s="164" t="s">
+      <c r="AK4" s="160"/>
+      <c r="AL4" s="160"/>
+      <c r="AN4" s="159" t="s">
         <v>54</v>
       </c>
-      <c r="AO4" s="156"/>
-      <c r="AP4" s="165"/>
-      <c r="AR4" s="156" t="s">
+      <c r="AO4" s="160"/>
+      <c r="AP4" s="161"/>
+      <c r="AR4" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="AS4" s="156"/>
-      <c r="AT4" s="156"/>
-      <c r="AV4" s="156" t="s">
+      <c r="AS4" s="160"/>
+      <c r="AT4" s="160"/>
+      <c r="AV4" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="AW4" s="156"/>
-      <c r="AX4" s="156"/>
-      <c r="AZ4" s="156" t="s">
+      <c r="AW4" s="160"/>
+      <c r="AX4" s="160"/>
+      <c r="AZ4" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="BA4" s="156"/>
-      <c r="BB4" s="156"/>
-      <c r="BD4" s="156" t="s">
+      <c r="BA4" s="160"/>
+      <c r="BB4" s="160"/>
+      <c r="BD4" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="BE4" s="156"/>
-      <c r="BF4" s="156"/>
+      <c r="BE4" s="160"/>
+      <c r="BF4" s="160"/>
       <c r="BG4" s="30"/>
-      <c r="BH4" s="158" t="s">
+      <c r="BH4" s="165" t="s">
         <v>59</v>
       </c>
-      <c r="BI4" s="159"/>
-      <c r="BJ4" s="160"/>
+      <c r="BI4" s="166"/>
+      <c r="BJ4" s="167"/>
       <c r="BK4" s="30"/>
-      <c r="BL4" s="164" t="s">
+      <c r="BL4" s="159" t="s">
         <v>47</v>
       </c>
-      <c r="BM4" s="156"/>
-      <c r="BN4" s="165"/>
-      <c r="BP4" s="164" t="s">
+      <c r="BM4" s="160"/>
+      <c r="BN4" s="161"/>
+      <c r="BP4" s="159" t="s">
         <v>48</v>
       </c>
-      <c r="BQ4" s="156"/>
-      <c r="BR4" s="165"/>
-      <c r="BT4" s="164" t="s">
+      <c r="BQ4" s="160"/>
+      <c r="BR4" s="161"/>
+      <c r="BT4" s="159" t="s">
         <v>49</v>
       </c>
-      <c r="BU4" s="156"/>
-      <c r="BV4" s="165"/>
-      <c r="BX4" s="164" t="s">
+      <c r="BU4" s="160"/>
+      <c r="BV4" s="161"/>
+      <c r="BX4" s="159" t="s">
         <v>50</v>
       </c>
-      <c r="BY4" s="156"/>
-      <c r="BZ4" s="165"/>
-      <c r="CB4" s="164" t="s">
+      <c r="BY4" s="160"/>
+      <c r="BZ4" s="161"/>
+      <c r="CB4" s="159" t="s">
         <v>51</v>
       </c>
-      <c r="CC4" s="156"/>
-      <c r="CD4" s="156"/>
+      <c r="CC4" s="160"/>
+      <c r="CD4" s="160"/>
       <c r="CE4" s="29"/>
-      <c r="CG4" s="164" t="s">
+      <c r="CG4" s="159" t="s">
         <v>52</v>
       </c>
-      <c r="CH4" s="156"/>
-      <c r="CI4" s="165"/>
-      <c r="CK4" s="164" t="s">
+      <c r="CH4" s="160"/>
+      <c r="CI4" s="161"/>
+      <c r="CK4" s="159" t="s">
         <v>53</v>
       </c>
-      <c r="CL4" s="156"/>
-      <c r="CM4" s="156"/>
-      <c r="CO4" s="164" t="s">
+      <c r="CL4" s="160"/>
+      <c r="CM4" s="160"/>
+      <c r="CO4" s="159" t="s">
         <v>54</v>
       </c>
-      <c r="CP4" s="156"/>
-      <c r="CQ4" s="165"/>
-      <c r="CS4" s="156" t="s">
+      <c r="CP4" s="160"/>
+      <c r="CQ4" s="161"/>
+      <c r="CS4" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="CT4" s="156"/>
-      <c r="CU4" s="156"/>
-      <c r="CW4" s="156" t="s">
+      <c r="CT4" s="160"/>
+      <c r="CU4" s="160"/>
+      <c r="CW4" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="CX4" s="156"/>
-      <c r="CY4" s="156"/>
-      <c r="DA4" s="156" t="s">
+      <c r="CX4" s="160"/>
+      <c r="CY4" s="160"/>
+      <c r="DA4" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="DB4" s="156"/>
-      <c r="DC4" s="156"/>
-      <c r="DE4" s="156" t="s">
+      <c r="DB4" s="160"/>
+      <c r="DC4" s="160"/>
+      <c r="DE4" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="DF4" s="156"/>
-      <c r="DG4" s="156"/>
+      <c r="DF4" s="160"/>
+      <c r="DG4" s="160"/>
       <c r="DH4" s="30"/>
-      <c r="DI4" s="158" t="s">
+      <c r="DI4" s="165" t="s">
         <v>60</v>
       </c>
-      <c r="DJ4" s="159"/>
-      <c r="DK4" s="160"/>
+      <c r="DJ4" s="166"/>
+      <c r="DK4" s="167"/>
       <c r="DL4" s="31"/>
       <c r="DM4" s="31"/>
       <c r="DN4" s="31"/>
@@ -10974,89 +10979,89 @@
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
-      <c r="K5" s="166"/>
-      <c r="L5" s="157"/>
-      <c r="M5" s="167"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="157"/>
-      <c r="Q5" s="167"/>
-      <c r="S5" s="166"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="167"/>
-      <c r="W5" s="166"/>
-      <c r="X5" s="157"/>
-      <c r="Y5" s="167"/>
-      <c r="AA5" s="166"/>
-      <c r="AB5" s="157"/>
-      <c r="AC5" s="157"/>
+      <c r="K5" s="162"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="164"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="163"/>
+      <c r="Q5" s="164"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="163"/>
+      <c r="U5" s="164"/>
+      <c r="W5" s="162"/>
+      <c r="X5" s="163"/>
+      <c r="Y5" s="164"/>
+      <c r="AA5" s="162"/>
+      <c r="AB5" s="163"/>
+      <c r="AC5" s="163"/>
       <c r="AD5" s="34"/>
-      <c r="AF5" s="166"/>
-      <c r="AG5" s="157"/>
-      <c r="AH5" s="167"/>
-      <c r="AJ5" s="166"/>
-      <c r="AK5" s="157"/>
-      <c r="AL5" s="157"/>
-      <c r="AN5" s="166"/>
-      <c r="AO5" s="157"/>
-      <c r="AP5" s="167"/>
-      <c r="AR5" s="157"/>
-      <c r="AS5" s="157"/>
-      <c r="AT5" s="157"/>
-      <c r="AV5" s="157"/>
-      <c r="AW5" s="157"/>
-      <c r="AX5" s="157"/>
-      <c r="AZ5" s="157"/>
-      <c r="BA5" s="157"/>
-      <c r="BB5" s="157"/>
-      <c r="BD5" s="157"/>
-      <c r="BE5" s="157"/>
-      <c r="BF5" s="157"/>
+      <c r="AF5" s="162"/>
+      <c r="AG5" s="163"/>
+      <c r="AH5" s="164"/>
+      <c r="AJ5" s="162"/>
+      <c r="AK5" s="163"/>
+      <c r="AL5" s="163"/>
+      <c r="AN5" s="162"/>
+      <c r="AO5" s="163"/>
+      <c r="AP5" s="164"/>
+      <c r="AR5" s="163"/>
+      <c r="AS5" s="163"/>
+      <c r="AT5" s="163"/>
+      <c r="AV5" s="163"/>
+      <c r="AW5" s="163"/>
+      <c r="AX5" s="163"/>
+      <c r="AZ5" s="163"/>
+      <c r="BA5" s="163"/>
+      <c r="BB5" s="163"/>
+      <c r="BD5" s="163"/>
+      <c r="BE5" s="163"/>
+      <c r="BF5" s="163"/>
       <c r="BG5" s="30"/>
-      <c r="BH5" s="161"/>
-      <c r="BI5" s="162"/>
-      <c r="BJ5" s="163"/>
+      <c r="BH5" s="168"/>
+      <c r="BI5" s="169"/>
+      <c r="BJ5" s="170"/>
       <c r="BK5" s="30"/>
-      <c r="BL5" s="166"/>
-      <c r="BM5" s="157"/>
-      <c r="BN5" s="167"/>
-      <c r="BP5" s="166"/>
-      <c r="BQ5" s="157"/>
-      <c r="BR5" s="167"/>
-      <c r="BT5" s="166"/>
-      <c r="BU5" s="157"/>
-      <c r="BV5" s="167"/>
-      <c r="BX5" s="166"/>
-      <c r="BY5" s="157"/>
-      <c r="BZ5" s="167"/>
-      <c r="CB5" s="166"/>
-      <c r="CC5" s="157"/>
-      <c r="CD5" s="157"/>
+      <c r="BL5" s="162"/>
+      <c r="BM5" s="163"/>
+      <c r="BN5" s="164"/>
+      <c r="BP5" s="162"/>
+      <c r="BQ5" s="163"/>
+      <c r="BR5" s="164"/>
+      <c r="BT5" s="162"/>
+      <c r="BU5" s="163"/>
+      <c r="BV5" s="164"/>
+      <c r="BX5" s="162"/>
+      <c r="BY5" s="163"/>
+      <c r="BZ5" s="164"/>
+      <c r="CB5" s="162"/>
+      <c r="CC5" s="163"/>
+      <c r="CD5" s="163"/>
       <c r="CE5" s="34"/>
-      <c r="CG5" s="166"/>
-      <c r="CH5" s="157"/>
-      <c r="CI5" s="167"/>
-      <c r="CK5" s="166"/>
-      <c r="CL5" s="157"/>
-      <c r="CM5" s="157"/>
-      <c r="CO5" s="166"/>
-      <c r="CP5" s="157"/>
-      <c r="CQ5" s="167"/>
-      <c r="CS5" s="157"/>
-      <c r="CT5" s="157"/>
-      <c r="CU5" s="157"/>
-      <c r="CW5" s="157"/>
-      <c r="CX5" s="157"/>
-      <c r="CY5" s="157"/>
-      <c r="DA5" s="157"/>
-      <c r="DB5" s="157"/>
-      <c r="DC5" s="157"/>
-      <c r="DE5" s="157"/>
-      <c r="DF5" s="157"/>
-      <c r="DG5" s="157"/>
+      <c r="CG5" s="162"/>
+      <c r="CH5" s="163"/>
+      <c r="CI5" s="164"/>
+      <c r="CK5" s="162"/>
+      <c r="CL5" s="163"/>
+      <c r="CM5" s="163"/>
+      <c r="CO5" s="162"/>
+      <c r="CP5" s="163"/>
+      <c r="CQ5" s="164"/>
+      <c r="CS5" s="163"/>
+      <c r="CT5" s="163"/>
+      <c r="CU5" s="163"/>
+      <c r="CW5" s="163"/>
+      <c r="CX5" s="163"/>
+      <c r="CY5" s="163"/>
+      <c r="DA5" s="163"/>
+      <c r="DB5" s="163"/>
+      <c r="DC5" s="163"/>
+      <c r="DE5" s="163"/>
+      <c r="DF5" s="163"/>
+      <c r="DG5" s="163"/>
       <c r="DH5" s="30"/>
-      <c r="DI5" s="161"/>
-      <c r="DJ5" s="162"/>
-      <c r="DK5" s="163"/>
+      <c r="DI5" s="168"/>
+      <c r="DJ5" s="169"/>
+      <c r="DK5" s="170"/>
       <c r="DL5" s="31"/>
       <c r="DM5" s="31"/>
       <c r="DN5" s="31"/>
@@ -14798,12 +14803,14 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="AF4:AH5"/>
-    <mergeCell ref="K4:M5"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="S4:U5"/>
-    <mergeCell ref="W4:Y5"/>
-    <mergeCell ref="AA4:AC5"/>
+    <mergeCell ref="DE4:DG5"/>
+    <mergeCell ref="DI4:DK5"/>
+    <mergeCell ref="CG4:CI5"/>
+    <mergeCell ref="CK4:CM5"/>
+    <mergeCell ref="CO4:CQ5"/>
+    <mergeCell ref="CS4:CU5"/>
+    <mergeCell ref="CW4:CY5"/>
+    <mergeCell ref="DA4:DC5"/>
     <mergeCell ref="CB4:CD5"/>
     <mergeCell ref="AJ4:AL5"/>
     <mergeCell ref="AN4:AP5"/>
@@ -14816,14 +14823,12 @@
     <mergeCell ref="BP4:BR5"/>
     <mergeCell ref="BT4:BV5"/>
     <mergeCell ref="BX4:BZ5"/>
-    <mergeCell ref="DE4:DG5"/>
-    <mergeCell ref="DI4:DK5"/>
-    <mergeCell ref="CG4:CI5"/>
-    <mergeCell ref="CK4:CM5"/>
-    <mergeCell ref="CO4:CQ5"/>
-    <mergeCell ref="CS4:CU5"/>
-    <mergeCell ref="CW4:CY5"/>
-    <mergeCell ref="DA4:DC5"/>
+    <mergeCell ref="AF4:AH5"/>
+    <mergeCell ref="K4:M5"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="S4:U5"/>
+    <mergeCell ref="W4:Y5"/>
+    <mergeCell ref="AA4:AC5"/>
   </mergeCells>
   <conditionalFormatting sqref="BR10 BR12 BR14 BR16 BR18 BR20 BR22 BR24 BV10 BV12 BV14 BV16 BV18 BV20 BV22 BV24 BZ10 BZ12 BZ14 BZ16 BZ18 BZ20 BZ22 BZ24 AC10 AC12 AC14 AC16 AC18 AC20 AC22 AC24 AH10 AH12 AH14 AH16 AH18 AH20 AH22 AH24 AL10 AL12 AL14 AL16 AL18 AL20 AL22 AL24 AP10 AP12:AP14 AP16 AP18 AP20 AP22 AP24 AT24 AT20 AT18 AT16 AT14 AT12 AT10 AT22 BJ10 BJ12 BJ14 BJ16 BJ18 BJ20 BJ22 BJ24 Y10 Y12 Y14 Y16 Y18 Y20 Y22 Y24 U10 U12 U14 U16 U18 U20 U22 U24 Q10 Q12 Q14 Q16 Q18 Q20 Q22 Q24">
     <cfRule type="cellIs" dxfId="22" priority="23" stopIfTrue="1" operator="greaterThan">
@@ -15889,10 +15894,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="128"/>
-      <c r="B4" s="169">
+      <c r="B4" s="173">
         <v>0.01</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="C4" s="174" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="130">
@@ -15921,8 +15926,8 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="128"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="170"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="174"/>
       <c r="D5" s="130">
         <v>2</v>
       </c>
@@ -15951,8 +15956,8 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="128"/>
-      <c r="B6" s="170"/>
-      <c r="C6" s="170"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="174"/>
       <c r="D6" s="130">
         <v>3</v>
       </c>
@@ -15981,8 +15986,8 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="135"/>
-      <c r="B7" s="170"/>
-      <c r="C7" s="170"/>
+      <c r="B7" s="174"/>
+      <c r="C7" s="174"/>
       <c r="D7" s="130">
         <v>4</v>
       </c>
@@ -16009,8 +16014,8 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="135"/>
-      <c r="B8" s="170"/>
-      <c r="C8" s="170"/>
+      <c r="B8" s="174"/>
+      <c r="C8" s="174"/>
       <c r="D8" s="130">
         <v>5</v>
       </c>
@@ -16039,8 +16044,8 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="135"/>
-      <c r="B9" s="170"/>
-      <c r="C9" s="170"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
       <c r="D9" s="130">
         <v>6</v>
       </c>
@@ -16067,10 +16072,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="135"/>
-      <c r="D10" s="168" t="s">
+      <c r="D10" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="168"/>
+      <c r="E10" s="175"/>
       <c r="F10" s="136">
         <f>SUM(F4:F9)</f>
         <v>25</v>
@@ -16128,10 +16133,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="135"/>
-      <c r="B13" s="169">
+      <c r="B13" s="173">
         <v>0.01</v>
       </c>
-      <c r="C13" s="170" t="s">
+      <c r="C13" s="174" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="130">
@@ -16157,8 +16162,8 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="135"/>
-      <c r="B14" s="169"/>
-      <c r="C14" s="170"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="174"/>
       <c r="D14" s="130">
         <v>2</v>
       </c>
@@ -16185,8 +16190,8 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="135"/>
-      <c r="B15" s="170"/>
-      <c r="C15" s="170"/>
+      <c r="B15" s="174"/>
+      <c r="C15" s="174"/>
       <c r="D15" s="130">
         <v>2</v>
       </c>
@@ -16215,8 +16220,8 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="135"/>
-      <c r="B16" s="170"/>
-      <c r="C16" s="170"/>
+      <c r="B16" s="174"/>
+      <c r="C16" s="174"/>
       <c r="D16" s="130">
         <v>3</v>
       </c>
@@ -16243,8 +16248,8 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="135"/>
-      <c r="B17" s="170"/>
-      <c r="C17" s="170"/>
+      <c r="B17" s="174"/>
+      <c r="C17" s="174"/>
       <c r="D17" s="130">
         <v>4</v>
       </c>
@@ -16273,8 +16278,8 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="135"/>
-      <c r="B18" s="170"/>
-      <c r="C18" s="170"/>
+      <c r="B18" s="174"/>
+      <c r="C18" s="174"/>
       <c r="D18" s="130">
         <v>5</v>
       </c>
@@ -16301,10 +16306,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="135"/>
-      <c r="D19" s="168" t="s">
+      <c r="D19" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="168"/>
+      <c r="E19" s="175"/>
       <c r="F19" s="138">
         <f>SUM(F13:F18)</f>
         <v>6</v>
@@ -16359,10 +16364,10 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="B22" s="169">
+      <c r="B22" s="173">
         <v>0.01</v>
       </c>
-      <c r="C22" s="170" t="s">
+      <c r="C22" s="174" t="s">
         <v>101</v>
       </c>
       <c r="D22" s="130">
@@ -16387,8 +16392,8 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="B23" s="169"/>
-      <c r="C23" s="170"/>
+      <c r="B23" s="173"/>
+      <c r="C23" s="174"/>
       <c r="D23" s="130">
         <v>2</v>
       </c>
@@ -16414,8 +16419,8 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="B24" s="170"/>
-      <c r="C24" s="170"/>
+      <c r="B24" s="174"/>
+      <c r="C24" s="174"/>
       <c r="D24" s="130">
         <v>2</v>
       </c>
@@ -16443,8 +16448,8 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="B25" s="170"/>
-      <c r="C25" s="170"/>
+      <c r="B25" s="174"/>
+      <c r="C25" s="174"/>
       <c r="D25" s="130">
         <v>3</v>
       </c>
@@ -16470,8 +16475,8 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="B26" s="170"/>
-      <c r="C26" s="170"/>
+      <c r="B26" s="174"/>
+      <c r="C26" s="174"/>
       <c r="D26" s="130">
         <v>4</v>
       </c>
@@ -16497,8 +16502,8 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="B27" s="170"/>
-      <c r="C27" s="170"/>
+      <c r="B27" s="174"/>
+      <c r="C27" s="174"/>
       <c r="D27" s="130">
         <v>5</v>
       </c>
@@ -16524,10 +16529,10 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="D28" s="168" t="s">
+      <c r="D28" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="168"/>
+      <c r="E28" s="175"/>
       <c r="F28" s="138">
         <f>SUM(F22:F27)</f>
         <v>6</v>
@@ -16582,10 +16587,10 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="B31" s="169">
+      <c r="B31" s="173">
         <v>0.01</v>
       </c>
-      <c r="C31" s="170" t="s">
+      <c r="C31" s="174" t="s">
         <v>103</v>
       </c>
       <c r="D31" s="130">
@@ -16612,8 +16617,8 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="B32" s="169"/>
-      <c r="C32" s="170"/>
+      <c r="B32" s="173"/>
+      <c r="C32" s="174"/>
       <c r="D32" s="130">
         <v>2</v>
       </c>
@@ -16641,8 +16646,8 @@
       </c>
     </row>
     <row r="33" spans="2:10">
-      <c r="B33" s="170"/>
-      <c r="C33" s="170"/>
+      <c r="B33" s="174"/>
+      <c r="C33" s="174"/>
       <c r="D33" s="130">
         <v>2</v>
       </c>
@@ -16670,8 +16675,8 @@
       </c>
     </row>
     <row r="34" spans="2:10">
-      <c r="B34" s="170"/>
-      <c r="C34" s="170"/>
+      <c r="B34" s="174"/>
+      <c r="C34" s="174"/>
       <c r="D34" s="130">
         <v>3</v>
       </c>
@@ -16697,8 +16702,8 @@
       </c>
     </row>
     <row r="35" spans="2:10">
-      <c r="B35" s="170"/>
-      <c r="C35" s="170"/>
+      <c r="B35" s="174"/>
+      <c r="C35" s="174"/>
       <c r="D35" s="130">
         <v>4</v>
       </c>
@@ -16726,8 +16731,8 @@
       </c>
     </row>
     <row r="36" spans="2:10">
-      <c r="B36" s="170"/>
-      <c r="C36" s="170"/>
+      <c r="B36" s="174"/>
+      <c r="C36" s="174"/>
       <c r="D36" s="130">
         <v>5</v>
       </c>
@@ -16753,10 +16758,10 @@
       </c>
     </row>
     <row r="37" spans="2:10">
-      <c r="D37" s="168" t="s">
+      <c r="D37" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="168"/>
+      <c r="E37" s="175"/>
       <c r="F37" s="138">
         <f>SUM(F31:F36)</f>
         <v>687</v>
@@ -16811,10 +16816,10 @@
       </c>
     </row>
     <row r="40" spans="2:10">
-      <c r="B40" s="169">
+      <c r="B40" s="173">
         <v>0.01</v>
       </c>
-      <c r="C40" s="170" t="s">
+      <c r="C40" s="174" t="s">
         <v>104</v>
       </c>
       <c r="D40" s="130">
@@ -16839,8 +16844,8 @@
       </c>
     </row>
     <row r="41" spans="2:10">
-      <c r="B41" s="169"/>
-      <c r="C41" s="170"/>
+      <c r="B41" s="173"/>
+      <c r="C41" s="174"/>
       <c r="D41" s="130">
         <v>2</v>
       </c>
@@ -16866,8 +16871,8 @@
       </c>
     </row>
     <row r="42" spans="2:10">
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
+      <c r="B42" s="174"/>
+      <c r="C42" s="174"/>
       <c r="D42" s="130">
         <v>2</v>
       </c>
@@ -16895,8 +16900,8 @@
       </c>
     </row>
     <row r="43" spans="2:10">
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
+      <c r="B43" s="174"/>
+      <c r="C43" s="174"/>
       <c r="D43" s="130">
         <v>3</v>
       </c>
@@ -16922,8 +16927,8 @@
       </c>
     </row>
     <row r="44" spans="2:10">
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
+      <c r="B44" s="174"/>
+      <c r="C44" s="174"/>
       <c r="D44" s="130">
         <v>4</v>
       </c>
@@ -16949,8 +16954,8 @@
       </c>
     </row>
     <row r="45" spans="2:10">
-      <c r="B45" s="170"/>
-      <c r="C45" s="170"/>
+      <c r="B45" s="174"/>
+      <c r="C45" s="174"/>
       <c r="D45" s="130">
         <v>5</v>
       </c>
@@ -16976,10 +16981,10 @@
       </c>
     </row>
     <row r="46" spans="2:10">
-      <c r="D46" s="168" t="s">
+      <c r="D46" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E46" s="168"/>
+      <c r="E46" s="175"/>
       <c r="F46" s="138">
         <f>SUM(F40:F45)</f>
         <v>6</v>
@@ -17034,10 +17039,10 @@
       </c>
     </row>
     <row r="49" spans="2:14">
-      <c r="B49" s="169">
+      <c r="B49" s="173">
         <v>0.01</v>
       </c>
-      <c r="C49" s="170" t="s">
+      <c r="C49" s="174" t="s">
         <v>105</v>
       </c>
       <c r="D49" s="130">
@@ -17062,8 +17067,8 @@
       </c>
     </row>
     <row r="50" spans="2:14">
-      <c r="B50" s="169"/>
-      <c r="C50" s="170"/>
+      <c r="B50" s="173"/>
+      <c r="C50" s="174"/>
       <c r="D50" s="130">
         <v>2</v>
       </c>
@@ -17089,8 +17094,8 @@
       </c>
     </row>
     <row r="51" spans="2:14">
-      <c r="B51" s="170"/>
-      <c r="C51" s="170"/>
+      <c r="B51" s="174"/>
+      <c r="C51" s="174"/>
       <c r="D51" s="130">
         <v>2</v>
       </c>
@@ -17116,8 +17121,8 @@
       </c>
     </row>
     <row r="52" spans="2:14">
-      <c r="B52" s="170"/>
-      <c r="C52" s="170"/>
+      <c r="B52" s="174"/>
+      <c r="C52" s="174"/>
       <c r="D52" s="130">
         <v>3</v>
       </c>
@@ -17143,8 +17148,8 @@
       </c>
     </row>
     <row r="53" spans="2:14">
-      <c r="B53" s="170"/>
-      <c r="C53" s="170"/>
+      <c r="B53" s="174"/>
+      <c r="C53" s="174"/>
       <c r="D53" s="130">
         <v>4</v>
       </c>
@@ -17170,8 +17175,8 @@
       </c>
     </row>
     <row r="54" spans="2:14">
-      <c r="B54" s="170"/>
-      <c r="C54" s="170"/>
+      <c r="B54" s="174"/>
+      <c r="C54" s="174"/>
       <c r="D54" s="130">
         <v>5</v>
       </c>
@@ -17198,10 +17203,10 @@
       <c r="N54" s="140"/>
     </row>
     <row r="55" spans="2:14">
-      <c r="D55" s="168" t="s">
+      <c r="D55" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E55" s="168"/>
+      <c r="E55" s="175"/>
       <c r="F55" s="138">
         <f>SUM(F49:F54)</f>
         <v>0</v>
@@ -17256,10 +17261,10 @@
       </c>
     </row>
     <row r="58" spans="2:14">
-      <c r="B58" s="169">
+      <c r="B58" s="173">
         <v>0.01</v>
       </c>
-      <c r="C58" s="170" t="s">
+      <c r="C58" s="174" t="s">
         <v>106</v>
       </c>
       <c r="D58" s="130">
@@ -17284,8 +17289,8 @@
       </c>
     </row>
     <row r="59" spans="2:14">
-      <c r="B59" s="169"/>
-      <c r="C59" s="170"/>
+      <c r="B59" s="173"/>
+      <c r="C59" s="174"/>
       <c r="D59" s="130"/>
       <c r="E59" s="130" t="s">
         <v>94</v>
@@ -17309,8 +17314,8 @@
       </c>
     </row>
     <row r="60" spans="2:14">
-      <c r="B60" s="170"/>
-      <c r="C60" s="170"/>
+      <c r="B60" s="174"/>
+      <c r="C60" s="174"/>
       <c r="D60" s="130">
         <v>2</v>
       </c>
@@ -17336,8 +17341,8 @@
       </c>
     </row>
     <row r="61" spans="2:14">
-      <c r="B61" s="170"/>
-      <c r="C61" s="170"/>
+      <c r="B61" s="174"/>
+      <c r="C61" s="174"/>
       <c r="D61" s="130">
         <v>3</v>
       </c>
@@ -17363,8 +17368,8 @@
       </c>
     </row>
     <row r="62" spans="2:14">
-      <c r="B62" s="170"/>
-      <c r="C62" s="170"/>
+      <c r="B62" s="174"/>
+      <c r="C62" s="174"/>
       <c r="D62" s="130">
         <v>4</v>
       </c>
@@ -17390,8 +17395,8 @@
       </c>
     </row>
     <row r="63" spans="2:14">
-      <c r="B63" s="170"/>
-      <c r="C63" s="170"/>
+      <c r="B63" s="174"/>
+      <c r="C63" s="174"/>
       <c r="D63" s="130">
         <v>5</v>
       </c>
@@ -17417,10 +17422,10 @@
       </c>
     </row>
     <row r="64" spans="2:14">
-      <c r="D64" s="168" t="s">
+      <c r="D64" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="168"/>
+      <c r="E64" s="175"/>
       <c r="F64" s="138">
         <f>SUM(F58:F63)</f>
         <v>0</v>
@@ -17475,10 +17480,10 @@
       </c>
     </row>
     <row r="67" spans="2:10">
-      <c r="B67" s="169">
+      <c r="B67" s="173">
         <v>0.01</v>
       </c>
-      <c r="C67" s="170" t="s">
+      <c r="C67" s="174" t="s">
         <v>107</v>
       </c>
       <c r="D67" s="130">
@@ -17503,8 +17508,8 @@
       </c>
     </row>
     <row r="68" spans="2:10">
-      <c r="B68" s="169"/>
-      <c r="C68" s="170"/>
+      <c r="B68" s="173"/>
+      <c r="C68" s="174"/>
       <c r="D68" s="130">
         <v>2</v>
       </c>
@@ -17530,8 +17535,8 @@
       </c>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="170"/>
-      <c r="C69" s="170"/>
+      <c r="B69" s="174"/>
+      <c r="C69" s="174"/>
       <c r="D69" s="130">
         <v>3</v>
       </c>
@@ -17557,8 +17562,8 @@
       </c>
     </row>
     <row r="70" spans="2:10">
-      <c r="B70" s="170"/>
-      <c r="C70" s="170"/>
+      <c r="B70" s="174"/>
+      <c r="C70" s="174"/>
       <c r="D70" s="130">
         <v>4</v>
       </c>
@@ -17584,8 +17589,8 @@
       </c>
     </row>
     <row r="71" spans="2:10">
-      <c r="B71" s="170"/>
-      <c r="C71" s="170"/>
+      <c r="B71" s="174"/>
+      <c r="C71" s="174"/>
       <c r="D71" s="130">
         <v>5</v>
       </c>
@@ -17611,8 +17616,8 @@
       </c>
     </row>
     <row r="72" spans="2:10">
-      <c r="B72" s="170"/>
-      <c r="C72" s="170"/>
+      <c r="B72" s="174"/>
+      <c r="C72" s="174"/>
       <c r="D72" s="130">
         <v>6</v>
       </c>
@@ -17638,10 +17643,10 @@
       </c>
     </row>
     <row r="73" spans="2:10">
-      <c r="D73" s="168" t="s">
+      <c r="D73" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E73" s="168"/>
+      <c r="E73" s="175"/>
       <c r="F73" s="138">
         <f>SUM(F67:F72)</f>
         <v>0</v>
@@ -17693,10 +17698,10 @@
       </c>
     </row>
     <row r="76" spans="2:10">
-      <c r="B76" s="169">
+      <c r="B76" s="173">
         <v>0.01</v>
       </c>
-      <c r="C76" s="170" t="s">
+      <c r="C76" s="174" t="s">
         <v>108</v>
       </c>
       <c r="D76" s="130">
@@ -17723,8 +17728,8 @@
       </c>
     </row>
     <row r="77" spans="2:10">
-      <c r="B77" s="169"/>
-      <c r="C77" s="170"/>
+      <c r="B77" s="173"/>
+      <c r="C77" s="174"/>
       <c r="D77" s="130">
         <v>2</v>
       </c>
@@ -17752,8 +17757,8 @@
       </c>
     </row>
     <row r="78" spans="2:10">
-      <c r="B78" s="170"/>
-      <c r="C78" s="170"/>
+      <c r="B78" s="174"/>
+      <c r="C78" s="174"/>
       <c r="D78" s="130">
         <v>3</v>
       </c>
@@ -17781,8 +17786,8 @@
       </c>
     </row>
     <row r="79" spans="2:10">
-      <c r="B79" s="170"/>
-      <c r="C79" s="170"/>
+      <c r="B79" s="174"/>
+      <c r="C79" s="174"/>
       <c r="D79" s="130">
         <v>4</v>
       </c>
@@ -17808,8 +17813,8 @@
       </c>
     </row>
     <row r="80" spans="2:10">
-      <c r="B80" s="170"/>
-      <c r="C80" s="170"/>
+      <c r="B80" s="174"/>
+      <c r="C80" s="174"/>
       <c r="D80" s="130">
         <v>5</v>
       </c>
@@ -17835,8 +17840,8 @@
       </c>
     </row>
     <row r="81" spans="2:10">
-      <c r="B81" s="170"/>
-      <c r="C81" s="170"/>
+      <c r="B81" s="174"/>
+      <c r="C81" s="174"/>
       <c r="D81" s="130">
         <v>6</v>
       </c>
@@ -17862,10 +17867,10 @@
       </c>
     </row>
     <row r="82" spans="2:10">
-      <c r="D82" s="168" t="s">
+      <c r="D82" s="175" t="s">
         <v>99</v>
       </c>
-      <c r="E82" s="168"/>
+      <c r="E82" s="175"/>
       <c r="F82" s="138">
         <f>SUM(F76:F81)</f>
         <v>8.5500000000000007</v>
@@ -17889,24 +17894,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="C49:C54"/>
     <mergeCell ref="D73:E73"/>
     <mergeCell ref="B76:B81"/>
     <mergeCell ref="C76:C81"/>
@@ -17917,6 +17904,24 @@
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="B67:B72"/>
     <mergeCell ref="C67:C72"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C49:C54"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18254,17 +18259,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="176" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="129" t="s">
@@ -18296,10 +18301,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="175">
+      <c r="A4" s="177">
         <v>0.01</v>
       </c>
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="180" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="130">
@@ -18330,8 +18335,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5">
-      <c r="A5" s="176"/>
-      <c r="B5" s="179"/>
+      <c r="A5" s="178"/>
+      <c r="B5" s="181"/>
       <c r="C5" s="130">
         <v>2</v>
       </c>
@@ -18360,8 +18365,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5">
-      <c r="A6" s="176"/>
-      <c r="B6" s="179"/>
+      <c r="A6" s="178"/>
+      <c r="B6" s="181"/>
       <c r="C6" s="130">
         <v>3</v>
       </c>
@@ -18390,8 +18395,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
-      <c r="A7" s="176"/>
-      <c r="B7" s="179"/>
+      <c r="A7" s="178"/>
+      <c r="B7" s="181"/>
       <c r="C7" s="130">
         <v>4</v>
       </c>
@@ -18420,8 +18425,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5">
-      <c r="A8" s="176"/>
-      <c r="B8" s="179"/>
+      <c r="A8" s="178"/>
+      <c r="B8" s="181"/>
       <c r="C8" s="130">
         <v>5</v>
       </c>
@@ -18450,8 +18455,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
-      <c r="A9" s="177"/>
-      <c r="B9" s="180"/>
+      <c r="A9" s="179"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="130">
         <v>6</v>
       </c>
@@ -18482,10 +18487,10 @@
     <row r="10" spans="1:9" ht="16.5">
       <c r="A10" s="126"/>
       <c r="B10" s="126"/>
-      <c r="C10" s="173" t="s">
+      <c r="C10" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="174"/>
+      <c r="D10" s="184"/>
       <c r="E10" s="146">
         <f>SUM(E4:E9)</f>
         <v>306</v>
@@ -18548,10 +18553,10 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.5">
-      <c r="A13" s="175">
+      <c r="A13" s="177">
         <v>0.01</v>
       </c>
-      <c r="B13" s="178" t="s">
+      <c r="B13" s="180" t="s">
         <v>100</v>
       </c>
       <c r="C13" s="130">
@@ -18582,8 +18587,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5">
-      <c r="A14" s="176"/>
-      <c r="B14" s="179"/>
+      <c r="A14" s="178"/>
+      <c r="B14" s="181"/>
       <c r="C14" s="130">
         <v>2</v>
       </c>
@@ -18612,8 +18617,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5">
-      <c r="A15" s="176"/>
-      <c r="B15" s="179"/>
+      <c r="A15" s="178"/>
+      <c r="B15" s="181"/>
       <c r="C15" s="130">
         <v>2</v>
       </c>
@@ -18642,8 +18647,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5">
-      <c r="A16" s="176"/>
-      <c r="B16" s="179"/>
+      <c r="A16" s="178"/>
+      <c r="B16" s="181"/>
       <c r="C16" s="130">
         <v>3</v>
       </c>
@@ -18672,8 +18677,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5">
-      <c r="A17" s="176"/>
-      <c r="B17" s="179"/>
+      <c r="A17" s="178"/>
+      <c r="B17" s="181"/>
       <c r="C17" s="130">
         <v>4</v>
       </c>
@@ -18702,8 +18707,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5">
-      <c r="A18" s="177"/>
-      <c r="B18" s="180"/>
+      <c r="A18" s="179"/>
+      <c r="B18" s="182"/>
       <c r="C18" s="130">
         <v>5</v>
       </c>
@@ -18734,10 +18739,10 @@
     <row r="19" spans="1:9" ht="16.5">
       <c r="A19" s="126"/>
       <c r="B19" s="126"/>
-      <c r="C19" s="173" t="s">
+      <c r="C19" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="174"/>
+      <c r="D19" s="184"/>
       <c r="E19" s="146">
         <f>SUM(E13:E18)</f>
         <v>474</v>
@@ -18800,10 +18805,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A22" s="175">
+      <c r="A22" s="177">
         <v>0.01</v>
       </c>
-      <c r="B22" s="178" t="s">
+      <c r="B22" s="180" t="s">
         <v>101</v>
       </c>
       <c r="C22" s="130">
@@ -18834,8 +18839,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5">
-      <c r="A23" s="176"/>
-      <c r="B23" s="179"/>
+      <c r="A23" s="178"/>
+      <c r="B23" s="181"/>
       <c r="C23" s="130">
         <v>2</v>
       </c>
@@ -18864,8 +18869,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5">
-      <c r="A24" s="176"/>
-      <c r="B24" s="179"/>
+      <c r="A24" s="178"/>
+      <c r="B24" s="181"/>
       <c r="C24" s="130">
         <v>2</v>
       </c>
@@ -18894,8 +18899,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5">
-      <c r="A25" s="176"/>
-      <c r="B25" s="179"/>
+      <c r="A25" s="178"/>
+      <c r="B25" s="181"/>
       <c r="C25" s="130">
         <v>3</v>
       </c>
@@ -18924,8 +18929,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5">
-      <c r="A26" s="176"/>
-      <c r="B26" s="179"/>
+      <c r="A26" s="178"/>
+      <c r="B26" s="181"/>
       <c r="C26" s="130">
         <v>4</v>
       </c>
@@ -18954,8 +18959,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5">
-      <c r="A27" s="177"/>
-      <c r="B27" s="180"/>
+      <c r="A27" s="179"/>
+      <c r="B27" s="182"/>
       <c r="C27" s="130">
         <v>5</v>
       </c>
@@ -18986,10 +18991,10 @@
     <row r="28" spans="1:9" ht="16.5">
       <c r="A28" s="126"/>
       <c r="B28" s="126"/>
-      <c r="C28" s="173" t="s">
+      <c r="C28" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="174"/>
+      <c r="D28" s="184"/>
       <c r="E28" s="146">
         <f>SUM(E22:E27)</f>
         <v>1855</v>
@@ -19052,10 +19057,10 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A31" s="175">
+      <c r="A31" s="177">
         <v>0.01</v>
       </c>
-      <c r="B31" s="178" t="s">
+      <c r="B31" s="180" t="s">
         <v>103</v>
       </c>
       <c r="C31" s="130">
@@ -19086,8 +19091,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5">
-      <c r="A32" s="176"/>
-      <c r="B32" s="179"/>
+      <c r="A32" s="178"/>
+      <c r="B32" s="181"/>
       <c r="C32" s="130">
         <v>2</v>
       </c>
@@ -19116,8 +19121,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5">
-      <c r="A33" s="176"/>
-      <c r="B33" s="179"/>
+      <c r="A33" s="178"/>
+      <c r="B33" s="181"/>
       <c r="C33" s="130">
         <v>2</v>
       </c>
@@ -19146,8 +19151,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5">
-      <c r="A34" s="176"/>
-      <c r="B34" s="179"/>
+      <c r="A34" s="178"/>
+      <c r="B34" s="181"/>
       <c r="C34" s="130">
         <v>3</v>
       </c>
@@ -19176,8 +19181,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5">
-      <c r="A35" s="176"/>
-      <c r="B35" s="179"/>
+      <c r="A35" s="178"/>
+      <c r="B35" s="181"/>
       <c r="C35" s="130">
         <v>4</v>
       </c>
@@ -19206,8 +19211,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5">
-      <c r="A36" s="177"/>
-      <c r="B36" s="180"/>
+      <c r="A36" s="179"/>
+      <c r="B36" s="182"/>
       <c r="C36" s="130">
         <v>5</v>
       </c>
@@ -19238,10 +19243,10 @@
     <row r="37" spans="1:9" ht="16.5">
       <c r="A37" s="126"/>
       <c r="B37" s="126"/>
-      <c r="C37" s="173" t="s">
+      <c r="C37" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="174"/>
+      <c r="D37" s="184"/>
       <c r="E37" s="146">
         <f>SUM(E31:E36)</f>
         <v>5270</v>
@@ -19304,10 +19309,10 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.5">
-      <c r="A40" s="175">
+      <c r="A40" s="177">
         <v>0.01</v>
       </c>
-      <c r="B40" s="178" t="s">
+      <c r="B40" s="180" t="s">
         <v>104</v>
       </c>
       <c r="C40" s="130">
@@ -19338,8 +19343,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5">
-      <c r="A41" s="176"/>
-      <c r="B41" s="179"/>
+      <c r="A41" s="178"/>
+      <c r="B41" s="181"/>
       <c r="C41" s="130">
         <v>2</v>
       </c>
@@ -19368,8 +19373,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.5">
-      <c r="A42" s="176"/>
-      <c r="B42" s="179"/>
+      <c r="A42" s="178"/>
+      <c r="B42" s="181"/>
       <c r="C42" s="130">
         <v>2</v>
       </c>
@@ -19398,8 +19403,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.5">
-      <c r="A43" s="176"/>
-      <c r="B43" s="179"/>
+      <c r="A43" s="178"/>
+      <c r="B43" s="181"/>
       <c r="C43" s="130">
         <v>3</v>
       </c>
@@ -19428,8 +19433,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.5">
-      <c r="A44" s="176"/>
-      <c r="B44" s="179"/>
+      <c r="A44" s="178"/>
+      <c r="B44" s="181"/>
       <c r="C44" s="130">
         <v>4</v>
       </c>
@@ -19458,8 +19463,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.5">
-      <c r="A45" s="177"/>
-      <c r="B45" s="180"/>
+      <c r="A45" s="179"/>
+      <c r="B45" s="182"/>
       <c r="C45" s="130">
         <v>5</v>
       </c>
@@ -19490,10 +19495,10 @@
     <row r="46" spans="1:9" ht="16.5">
       <c r="A46" s="126"/>
       <c r="B46" s="126"/>
-      <c r="C46" s="173" t="s">
+      <c r="C46" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="174"/>
+      <c r="D46" s="184"/>
       <c r="E46" s="146">
         <f>SUM(E40:E45)</f>
         <v>1161</v>
@@ -19556,10 +19561,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="16.5">
-      <c r="A49" s="175">
+      <c r="A49" s="177">
         <v>0.01</v>
       </c>
-      <c r="B49" s="178" t="s">
+      <c r="B49" s="180" t="s">
         <v>105</v>
       </c>
       <c r="C49" s="130">
@@ -19590,8 +19595,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="16.5">
-      <c r="A50" s="176"/>
-      <c r="B50" s="179"/>
+      <c r="A50" s="178"/>
+      <c r="B50" s="181"/>
       <c r="C50" s="130">
         <v>2</v>
       </c>
@@ -19620,8 +19625,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="16.5">
-      <c r="A51" s="176"/>
-      <c r="B51" s="179"/>
+      <c r="A51" s="178"/>
+      <c r="B51" s="181"/>
       <c r="C51" s="130">
         <v>2</v>
       </c>
@@ -19650,8 +19655,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="16.5">
-      <c r="A52" s="176"/>
-      <c r="B52" s="179"/>
+      <c r="A52" s="178"/>
+      <c r="B52" s="181"/>
       <c r="C52" s="130">
         <v>3</v>
       </c>
@@ -19680,8 +19685,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="16.5">
-      <c r="A53" s="176"/>
-      <c r="B53" s="179"/>
+      <c r="A53" s="178"/>
+      <c r="B53" s="181"/>
       <c r="C53" s="130">
         <v>4</v>
       </c>
@@ -19710,8 +19715,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="16.5">
-      <c r="A54" s="177"/>
-      <c r="B54" s="180"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="182"/>
       <c r="C54" s="130">
         <v>5</v>
       </c>
@@ -19742,10 +19747,10 @@
     <row r="55" spans="1:9" ht="16.5">
       <c r="A55" s="126"/>
       <c r="B55" s="126"/>
-      <c r="C55" s="173" t="s">
+      <c r="C55" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D55" s="174"/>
+      <c r="D55" s="184"/>
       <c r="E55" s="146">
         <f>SUM(E49:E54)</f>
         <v>138</v>
@@ -19808,10 +19813,10 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="16.5">
-      <c r="A58" s="175">
+      <c r="A58" s="177">
         <v>0.01</v>
       </c>
-      <c r="B58" s="178" t="s">
+      <c r="B58" s="180" t="s">
         <v>106</v>
       </c>
       <c r="C58" s="130">
@@ -19842,8 +19847,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="16.5">
-      <c r="A59" s="176"/>
-      <c r="B59" s="179"/>
+      <c r="A59" s="178"/>
+      <c r="B59" s="181"/>
       <c r="C59" s="130"/>
       <c r="D59" s="130" t="s">
         <v>94</v>
@@ -19870,8 +19875,8 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5">
-      <c r="A60" s="176"/>
-      <c r="B60" s="179"/>
+      <c r="A60" s="178"/>
+      <c r="B60" s="181"/>
       <c r="C60" s="130">
         <v>2</v>
       </c>
@@ -19900,8 +19905,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5">
-      <c r="A61" s="176"/>
-      <c r="B61" s="179"/>
+      <c r="A61" s="178"/>
+      <c r="B61" s="181"/>
       <c r="C61" s="130">
         <v>3</v>
       </c>
@@ -19930,8 +19935,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="16.5">
-      <c r="A62" s="176"/>
-      <c r="B62" s="179"/>
+      <c r="A62" s="178"/>
+      <c r="B62" s="181"/>
       <c r="C62" s="130">
         <v>4</v>
       </c>
@@ -19960,8 +19965,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5">
-      <c r="A63" s="177"/>
-      <c r="B63" s="180"/>
+      <c r="A63" s="179"/>
+      <c r="B63" s="182"/>
       <c r="C63" s="130">
         <v>5</v>
       </c>
@@ -19992,10 +19997,10 @@
     <row r="64" spans="1:9" ht="16.5">
       <c r="A64" s="126"/>
       <c r="B64" s="126"/>
-      <c r="C64" s="173" t="s">
+      <c r="C64" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D64" s="174"/>
+      <c r="D64" s="184"/>
       <c r="E64" s="146">
         <f>SUM(E58:E63)</f>
         <v>18</v>
@@ -20058,10 +20063,10 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="16.5">
-      <c r="A67" s="175">
+      <c r="A67" s="177">
         <v>0.01</v>
       </c>
-      <c r="B67" s="178" t="s">
+      <c r="B67" s="180" t="s">
         <v>107</v>
       </c>
       <c r="C67" s="130">
@@ -20092,8 +20097,8 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5">
-      <c r="A68" s="176"/>
-      <c r="B68" s="179"/>
+      <c r="A68" s="178"/>
+      <c r="B68" s="181"/>
       <c r="C68" s="130">
         <v>2</v>
       </c>
@@ -20122,8 +20127,8 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="16.5">
-      <c r="A69" s="176"/>
-      <c r="B69" s="179"/>
+      <c r="A69" s="178"/>
+      <c r="B69" s="181"/>
       <c r="C69" s="130">
         <v>3</v>
       </c>
@@ -20152,8 +20157,8 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="16.5">
-      <c r="A70" s="176"/>
-      <c r="B70" s="179"/>
+      <c r="A70" s="178"/>
+      <c r="B70" s="181"/>
       <c r="C70" s="130">
         <v>4</v>
       </c>
@@ -20182,8 +20187,8 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="16.5">
-      <c r="A71" s="176"/>
-      <c r="B71" s="179"/>
+      <c r="A71" s="178"/>
+      <c r="B71" s="181"/>
       <c r="C71" s="130">
         <v>5</v>
       </c>
@@ -20212,8 +20217,8 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="16.5">
-      <c r="A72" s="177"/>
-      <c r="B72" s="180"/>
+      <c r="A72" s="179"/>
+      <c r="B72" s="182"/>
       <c r="C72" s="130">
         <v>6</v>
       </c>
@@ -20244,10 +20249,10 @@
     <row r="73" spans="1:9" ht="16.5">
       <c r="A73" s="126"/>
       <c r="B73" s="126"/>
-      <c r="C73" s="173" t="s">
+      <c r="C73" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="174"/>
+      <c r="D73" s="184"/>
       <c r="E73" s="151">
         <f>SUM(E67:E72)</f>
         <v>3.8085000000000004</v>
@@ -20310,10 +20315,10 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="16.5">
-      <c r="A76" s="175">
+      <c r="A76" s="177">
         <v>0.01</v>
       </c>
-      <c r="B76" s="178" t="s">
+      <c r="B76" s="180" t="s">
         <v>108</v>
       </c>
       <c r="C76" s="130">
@@ -20344,8 +20349,8 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="16.5">
-      <c r="A77" s="176"/>
-      <c r="B77" s="179"/>
+      <c r="A77" s="178"/>
+      <c r="B77" s="181"/>
       <c r="C77" s="130">
         <v>2</v>
       </c>
@@ -20374,8 +20379,8 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5">
-      <c r="A78" s="176"/>
-      <c r="B78" s="179"/>
+      <c r="A78" s="178"/>
+      <c r="B78" s="181"/>
       <c r="C78" s="130">
         <v>3</v>
       </c>
@@ -20404,8 +20409,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="16.5">
-      <c r="A79" s="176"/>
-      <c r="B79" s="179"/>
+      <c r="A79" s="178"/>
+      <c r="B79" s="181"/>
       <c r="C79" s="130">
         <v>4</v>
       </c>
@@ -20434,8 +20439,8 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="16.5">
-      <c r="A80" s="176"/>
-      <c r="B80" s="179"/>
+      <c r="A80" s="178"/>
+      <c r="B80" s="181"/>
       <c r="C80" s="130">
         <v>5</v>
       </c>
@@ -20464,8 +20469,8 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="16.5">
-      <c r="A81" s="177"/>
-      <c r="B81" s="180"/>
+      <c r="A81" s="179"/>
+      <c r="B81" s="182"/>
       <c r="C81" s="130">
         <v>6</v>
       </c>
@@ -20496,10 +20501,10 @@
     <row r="82" spans="1:9" ht="16.5">
       <c r="A82" s="126"/>
       <c r="B82" s="126"/>
-      <c r="C82" s="173" t="s">
+      <c r="C82" s="183" t="s">
         <v>99</v>
       </c>
-      <c r="D82" s="174"/>
+      <c r="D82" s="184"/>
       <c r="E82" s="151">
         <f>SUM(E76:E81)</f>
         <v>188.65</v>
@@ -20523,24 +20528,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="A76:A81"/>
     <mergeCell ref="B76:B81"/>
@@ -20551,6 +20538,24 @@
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="A67:A72"/>
     <mergeCell ref="B67:B72"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B13:B18"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20568,43 +20573,43 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:11">
-      <c r="B5" s="182" t="s">
+      <c r="B5" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="182"/>
-      <c r="D5" s="182"/>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="182"/>
-      <c r="K5" s="182"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="185"/>
+      <c r="G5" s="185"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="185" t="s">
+      <c r="B8" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="183">
+      <c r="C8" s="186">
         <v>46174</v>
       </c>
-      <c r="D8" s="183"/>
-      <c r="E8" s="183"/>
-      <c r="F8" s="183"/>
-      <c r="G8" s="184" t="s">
+      <c r="D8" s="186"/>
+      <c r="E8" s="186"/>
+      <c r="F8" s="186"/>
+      <c r="G8" s="187" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="184" t="s">
+      <c r="H8" s="187" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="184" t="s">
+      <c r="I8" s="187" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
+      <c r="J8" s="187"/>
+      <c r="K8" s="187"/>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="186"/>
+      <c r="B9" s="189"/>
       <c r="C9" s="153" t="s">
         <v>113</v>
       </c>
@@ -20617,8 +20622,8 @@
       <c r="F9" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
+      <c r="G9" s="187"/>
+      <c r="H9" s="187"/>
       <c r="I9" s="153" t="s">
         <v>65</v>
       </c>

--- a/target project.xlsx
+++ b/target project.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950"/>
+    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TARGET" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="169">
   <si>
     <t xml:space="preserve"> cek ulang tampilan dashboard bad produk mesin dominan, masih menampilkan data mesin yang tidak di pilih di sortasi,</t>
   </si>
@@ -488,6 +488,72 @@
   </si>
   <si>
     <t>macam-macam sortasi : sortasi - release, sortasi - tampung, sortasi - kasar</t>
+  </si>
+  <si>
+    <t>Project Website Berbek</t>
+  </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Fitur</t>
+  </si>
+  <si>
+    <t>KPI PVDC &amp; WIRE</t>
+  </si>
+  <si>
+    <t>Proses kerja Sortasi</t>
+  </si>
+  <si>
+    <t>Drystore</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>Navbar Portal Packing</t>
+  </si>
+  <si>
+    <t>Yield</t>
+  </si>
+  <si>
+    <t>Packing</t>
+  </si>
+  <si>
+    <t>Progress %</t>
+  </si>
+  <si>
+    <t>Belum Sinkron dengan release</t>
+  </si>
+  <si>
+    <t>Jenis sortasi : release, tampung, kasar, filtop</t>
+  </si>
+  <si>
+    <t>Rework dan Kupas</t>
+  </si>
+  <si>
+    <t>data dari rework retort dan filkar belum masuk, hanya dari sortasi</t>
+  </si>
+  <si>
+    <t>Download Excel di analisa</t>
+  </si>
+  <si>
+    <t>Perhitungan Performa SRCO</t>
+  </si>
+  <si>
+    <t>Menampilkan Suhu di Dashboard</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>menunggu link API nya.</t>
+  </si>
+  <si>
+    <t>Hanya tampilan di dashboard</t>
+  </si>
+  <si>
+    <t>Tinggal tempel jika ada fitur baru</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1537,7 @@
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1907,28 +1973,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1949,11 +2006,20 @@
     <xf numFmtId="1" fontId="5" fillId="10" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1961,11 +2027,17 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1985,11 +2057,8 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2005,6 +2074,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="248">
@@ -4927,7 +5002,7 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="157" t="s">
+      <c r="D8" s="158" t="s">
         <v>13</v>
       </c>
     </row>
@@ -4937,7 +5012,7 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="158"/>
+      <c r="D9" s="159"/>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
@@ -4945,7 +5020,7 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="157" t="s">
+      <c r="D10" s="158" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4955,7 +5030,7 @@
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="158"/>
+      <c r="D11" s="159"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
@@ -5142,51 +5217,213 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I6:J10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="157" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="88.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="9:10">
-      <c r="I6" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="191" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="192" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="192">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="9:10">
-      <c r="I7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="9:10">
-      <c r="I8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="9:10">
-      <c r="I9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="9:10">
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" t="s">
-        <v>38</v>
-      </c>
+      <c r="E3" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <f>IF(B4="","",A3+1)</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="192">
+        <v>100</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1">
+        <f t="shared" ref="A5:A13" si="0">IF(B5="","",A4+1)</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="192">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="192">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="192">
+        <v>50</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="192"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="192"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="192">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="192"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10830,47 +11067,47 @@
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
-      <c r="K4" s="159" t="s">
+      <c r="K4" s="168" t="s">
         <v>47</v>
       </c>
       <c r="L4" s="160"/>
-      <c r="M4" s="161"/>
-      <c r="O4" s="159" t="s">
+      <c r="M4" s="169"/>
+      <c r="O4" s="168" t="s">
         <v>48</v>
       </c>
       <c r="P4" s="160"/>
-      <c r="Q4" s="161"/>
-      <c r="S4" s="159" t="s">
+      <c r="Q4" s="169"/>
+      <c r="S4" s="168" t="s">
         <v>49</v>
       </c>
       <c r="T4" s="160"/>
-      <c r="U4" s="161"/>
-      <c r="W4" s="159" t="s">
+      <c r="U4" s="169"/>
+      <c r="W4" s="168" t="s">
         <v>50</v>
       </c>
       <c r="X4" s="160"/>
-      <c r="Y4" s="161"/>
-      <c r="AA4" s="159" t="s">
+      <c r="Y4" s="169"/>
+      <c r="AA4" s="168" t="s">
         <v>51</v>
       </c>
       <c r="AB4" s="160"/>
       <c r="AC4" s="160"/>
       <c r="AD4" s="29"/>
-      <c r="AF4" s="159" t="s">
+      <c r="AF4" s="168" t="s">
         <v>52</v>
       </c>
       <c r="AG4" s="160"/>
-      <c r="AH4" s="161"/>
-      <c r="AJ4" s="159" t="s">
+      <c r="AH4" s="169"/>
+      <c r="AJ4" s="168" t="s">
         <v>53</v>
       </c>
       <c r="AK4" s="160"/>
       <c r="AL4" s="160"/>
-      <c r="AN4" s="159" t="s">
+      <c r="AN4" s="168" t="s">
         <v>54</v>
       </c>
       <c r="AO4" s="160"/>
-      <c r="AP4" s="161"/>
+      <c r="AP4" s="169"/>
       <c r="AR4" s="160" t="s">
         <v>55</v>
       </c>
@@ -10892,53 +11129,53 @@
       <c r="BE4" s="160"/>
       <c r="BF4" s="160"/>
       <c r="BG4" s="30"/>
-      <c r="BH4" s="165" t="s">
+      <c r="BH4" s="162" t="s">
         <v>59</v>
       </c>
-      <c r="BI4" s="166"/>
-      <c r="BJ4" s="167"/>
+      <c r="BI4" s="163"/>
+      <c r="BJ4" s="164"/>
       <c r="BK4" s="30"/>
-      <c r="BL4" s="159" t="s">
+      <c r="BL4" s="168" t="s">
         <v>47</v>
       </c>
       <c r="BM4" s="160"/>
-      <c r="BN4" s="161"/>
-      <c r="BP4" s="159" t="s">
+      <c r="BN4" s="169"/>
+      <c r="BP4" s="168" t="s">
         <v>48</v>
       </c>
       <c r="BQ4" s="160"/>
-      <c r="BR4" s="161"/>
-      <c r="BT4" s="159" t="s">
+      <c r="BR4" s="169"/>
+      <c r="BT4" s="168" t="s">
         <v>49</v>
       </c>
       <c r="BU4" s="160"/>
-      <c r="BV4" s="161"/>
-      <c r="BX4" s="159" t="s">
+      <c r="BV4" s="169"/>
+      <c r="BX4" s="168" t="s">
         <v>50</v>
       </c>
       <c r="BY4" s="160"/>
-      <c r="BZ4" s="161"/>
-      <c r="CB4" s="159" t="s">
+      <c r="BZ4" s="169"/>
+      <c r="CB4" s="168" t="s">
         <v>51</v>
       </c>
       <c r="CC4" s="160"/>
       <c r="CD4" s="160"/>
       <c r="CE4" s="29"/>
-      <c r="CG4" s="159" t="s">
+      <c r="CG4" s="168" t="s">
         <v>52</v>
       </c>
       <c r="CH4" s="160"/>
-      <c r="CI4" s="161"/>
-      <c r="CK4" s="159" t="s">
+      <c r="CI4" s="169"/>
+      <c r="CK4" s="168" t="s">
         <v>53</v>
       </c>
       <c r="CL4" s="160"/>
       <c r="CM4" s="160"/>
-      <c r="CO4" s="159" t="s">
+      <c r="CO4" s="168" t="s">
         <v>54</v>
       </c>
       <c r="CP4" s="160"/>
-      <c r="CQ4" s="161"/>
+      <c r="CQ4" s="169"/>
       <c r="CS4" s="160" t="s">
         <v>55</v>
       </c>
@@ -10960,11 +11197,11 @@
       <c r="DF4" s="160"/>
       <c r="DG4" s="160"/>
       <c r="DH4" s="30"/>
-      <c r="DI4" s="165" t="s">
+      <c r="DI4" s="162" t="s">
         <v>60</v>
       </c>
-      <c r="DJ4" s="166"/>
-      <c r="DK4" s="167"/>
+      <c r="DJ4" s="163"/>
+      <c r="DK4" s="164"/>
       <c r="DL4" s="31"/>
       <c r="DM4" s="31"/>
       <c r="DN4" s="31"/>
@@ -10979,89 +11216,89 @@
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="163"/>
-      <c r="M5" s="164"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="163"/>
-      <c r="Q5" s="164"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="163"/>
-      <c r="U5" s="164"/>
-      <c r="W5" s="162"/>
-      <c r="X5" s="163"/>
-      <c r="Y5" s="164"/>
-      <c r="AA5" s="162"/>
-      <c r="AB5" s="163"/>
-      <c r="AC5" s="163"/>
+      <c r="K5" s="170"/>
+      <c r="L5" s="161"/>
+      <c r="M5" s="171"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="161"/>
+      <c r="Q5" s="171"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="161"/>
+      <c r="U5" s="171"/>
+      <c r="W5" s="170"/>
+      <c r="X5" s="161"/>
+      <c r="Y5" s="171"/>
+      <c r="AA5" s="170"/>
+      <c r="AB5" s="161"/>
+      <c r="AC5" s="161"/>
       <c r="AD5" s="34"/>
-      <c r="AF5" s="162"/>
-      <c r="AG5" s="163"/>
-      <c r="AH5" s="164"/>
-      <c r="AJ5" s="162"/>
-      <c r="AK5" s="163"/>
-      <c r="AL5" s="163"/>
-      <c r="AN5" s="162"/>
-      <c r="AO5" s="163"/>
-      <c r="AP5" s="164"/>
-      <c r="AR5" s="163"/>
-      <c r="AS5" s="163"/>
-      <c r="AT5" s="163"/>
-      <c r="AV5" s="163"/>
-      <c r="AW5" s="163"/>
-      <c r="AX5" s="163"/>
-      <c r="AZ5" s="163"/>
-      <c r="BA5" s="163"/>
-      <c r="BB5" s="163"/>
-      <c r="BD5" s="163"/>
-      <c r="BE5" s="163"/>
-      <c r="BF5" s="163"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="161"/>
+      <c r="AH5" s="171"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="161"/>
+      <c r="AL5" s="161"/>
+      <c r="AN5" s="170"/>
+      <c r="AO5" s="161"/>
+      <c r="AP5" s="171"/>
+      <c r="AR5" s="161"/>
+      <c r="AS5" s="161"/>
+      <c r="AT5" s="161"/>
+      <c r="AV5" s="161"/>
+      <c r="AW5" s="161"/>
+      <c r="AX5" s="161"/>
+      <c r="AZ5" s="161"/>
+      <c r="BA5" s="161"/>
+      <c r="BB5" s="161"/>
+      <c r="BD5" s="161"/>
+      <c r="BE5" s="161"/>
+      <c r="BF5" s="161"/>
       <c r="BG5" s="30"/>
-      <c r="BH5" s="168"/>
-      <c r="BI5" s="169"/>
-      <c r="BJ5" s="170"/>
+      <c r="BH5" s="165"/>
+      <c r="BI5" s="166"/>
+      <c r="BJ5" s="167"/>
       <c r="BK5" s="30"/>
-      <c r="BL5" s="162"/>
-      <c r="BM5" s="163"/>
-      <c r="BN5" s="164"/>
-      <c r="BP5" s="162"/>
-      <c r="BQ5" s="163"/>
-      <c r="BR5" s="164"/>
-      <c r="BT5" s="162"/>
-      <c r="BU5" s="163"/>
-      <c r="BV5" s="164"/>
-      <c r="BX5" s="162"/>
-      <c r="BY5" s="163"/>
-      <c r="BZ5" s="164"/>
-      <c r="CB5" s="162"/>
-      <c r="CC5" s="163"/>
-      <c r="CD5" s="163"/>
+      <c r="BL5" s="170"/>
+      <c r="BM5" s="161"/>
+      <c r="BN5" s="171"/>
+      <c r="BP5" s="170"/>
+      <c r="BQ5" s="161"/>
+      <c r="BR5" s="171"/>
+      <c r="BT5" s="170"/>
+      <c r="BU5" s="161"/>
+      <c r="BV5" s="171"/>
+      <c r="BX5" s="170"/>
+      <c r="BY5" s="161"/>
+      <c r="BZ5" s="171"/>
+      <c r="CB5" s="170"/>
+      <c r="CC5" s="161"/>
+      <c r="CD5" s="161"/>
       <c r="CE5" s="34"/>
-      <c r="CG5" s="162"/>
-      <c r="CH5" s="163"/>
-      <c r="CI5" s="164"/>
-      <c r="CK5" s="162"/>
-      <c r="CL5" s="163"/>
-      <c r="CM5" s="163"/>
-      <c r="CO5" s="162"/>
-      <c r="CP5" s="163"/>
-      <c r="CQ5" s="164"/>
-      <c r="CS5" s="163"/>
-      <c r="CT5" s="163"/>
-      <c r="CU5" s="163"/>
-      <c r="CW5" s="163"/>
-      <c r="CX5" s="163"/>
-      <c r="CY5" s="163"/>
-      <c r="DA5" s="163"/>
-      <c r="DB5" s="163"/>
-      <c r="DC5" s="163"/>
-      <c r="DE5" s="163"/>
-      <c r="DF5" s="163"/>
-      <c r="DG5" s="163"/>
+      <c r="CG5" s="170"/>
+      <c r="CH5" s="161"/>
+      <c r="CI5" s="171"/>
+      <c r="CK5" s="170"/>
+      <c r="CL5" s="161"/>
+      <c r="CM5" s="161"/>
+      <c r="CO5" s="170"/>
+      <c r="CP5" s="161"/>
+      <c r="CQ5" s="171"/>
+      <c r="CS5" s="161"/>
+      <c r="CT5" s="161"/>
+      <c r="CU5" s="161"/>
+      <c r="CW5" s="161"/>
+      <c r="CX5" s="161"/>
+      <c r="CY5" s="161"/>
+      <c r="DA5" s="161"/>
+      <c r="DB5" s="161"/>
+      <c r="DC5" s="161"/>
+      <c r="DE5" s="161"/>
+      <c r="DF5" s="161"/>
+      <c r="DG5" s="161"/>
       <c r="DH5" s="30"/>
-      <c r="DI5" s="168"/>
-      <c r="DJ5" s="169"/>
-      <c r="DK5" s="170"/>
+      <c r="DI5" s="165"/>
+      <c r="DJ5" s="166"/>
+      <c r="DK5" s="167"/>
       <c r="DL5" s="31"/>
       <c r="DM5" s="31"/>
       <c r="DN5" s="31"/>
@@ -14803,14 +15040,12 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="DE4:DG5"/>
-    <mergeCell ref="DI4:DK5"/>
-    <mergeCell ref="CG4:CI5"/>
-    <mergeCell ref="CK4:CM5"/>
-    <mergeCell ref="CO4:CQ5"/>
-    <mergeCell ref="CS4:CU5"/>
-    <mergeCell ref="CW4:CY5"/>
-    <mergeCell ref="DA4:DC5"/>
+    <mergeCell ref="AF4:AH5"/>
+    <mergeCell ref="K4:M5"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="S4:U5"/>
+    <mergeCell ref="W4:Y5"/>
+    <mergeCell ref="AA4:AC5"/>
     <mergeCell ref="CB4:CD5"/>
     <mergeCell ref="AJ4:AL5"/>
     <mergeCell ref="AN4:AP5"/>
@@ -14823,12 +15058,14 @@
     <mergeCell ref="BP4:BR5"/>
     <mergeCell ref="BT4:BV5"/>
     <mergeCell ref="BX4:BZ5"/>
-    <mergeCell ref="AF4:AH5"/>
-    <mergeCell ref="K4:M5"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="S4:U5"/>
-    <mergeCell ref="W4:Y5"/>
-    <mergeCell ref="AA4:AC5"/>
+    <mergeCell ref="DE4:DG5"/>
+    <mergeCell ref="DI4:DK5"/>
+    <mergeCell ref="CG4:CI5"/>
+    <mergeCell ref="CK4:CM5"/>
+    <mergeCell ref="CO4:CQ5"/>
+    <mergeCell ref="CS4:CU5"/>
+    <mergeCell ref="CW4:CY5"/>
+    <mergeCell ref="DA4:DC5"/>
   </mergeCells>
   <conditionalFormatting sqref="BR10 BR12 BR14 BR16 BR18 BR20 BR22 BR24 BV10 BV12 BV14 BV16 BV18 BV20 BV22 BV24 BZ10 BZ12 BZ14 BZ16 BZ18 BZ20 BZ22 BZ24 AC10 AC12 AC14 AC16 AC18 AC20 AC22 AC24 AH10 AH12 AH14 AH16 AH18 AH20 AH22 AH24 AL10 AL12 AL14 AL16 AL18 AL20 AL22 AL24 AP10 AP12:AP14 AP16 AP18 AP20 AP22 AP24 AT24 AT20 AT18 AT16 AT14 AT12 AT10 AT22 BJ10 BJ12 BJ14 BJ16 BJ18 BJ20 BJ22 BJ24 Y10 Y12 Y14 Y16 Y18 Y20 Y22 Y24 U10 U12 U14 U16 U18 U20 U22 U24 Q10 Q12 Q14 Q16 Q18 Q20 Q22 Q24">
     <cfRule type="cellIs" dxfId="22" priority="23" stopIfTrue="1" operator="greaterThan">
@@ -15843,18 +16080,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="B1" s="171">
+      <c r="B1" s="175">
         <f>+'[1]01'!B1:J1</f>
         <v>46174</v>
       </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="176"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="176"/>
+      <c r="J1" s="176"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="127">
@@ -16072,10 +16309,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="135"/>
-      <c r="D10" s="175" t="s">
+      <c r="D10" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="175"/>
+      <c r="E10" s="172"/>
       <c r="F10" s="136">
         <f>SUM(F4:F9)</f>
         <v>25</v>
@@ -16306,10 +16543,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="135"/>
-      <c r="D19" s="175" t="s">
+      <c r="D19" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="175"/>
+      <c r="E19" s="172"/>
       <c r="F19" s="138">
         <f>SUM(F13:F18)</f>
         <v>6</v>
@@ -16529,10 +16766,10 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="D28" s="175" t="s">
+      <c r="D28" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="175"/>
+      <c r="E28" s="172"/>
       <c r="F28" s="138">
         <f>SUM(F22:F27)</f>
         <v>6</v>
@@ -16758,10 +16995,10 @@
       </c>
     </row>
     <row r="37" spans="2:10">
-      <c r="D37" s="175" t="s">
+      <c r="D37" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="175"/>
+      <c r="E37" s="172"/>
       <c r="F37" s="138">
         <f>SUM(F31:F36)</f>
         <v>687</v>
@@ -16981,10 +17218,10 @@
       </c>
     </row>
     <row r="46" spans="2:10">
-      <c r="D46" s="175" t="s">
+      <c r="D46" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E46" s="175"/>
+      <c r="E46" s="172"/>
       <c r="F46" s="138">
         <f>SUM(F40:F45)</f>
         <v>6</v>
@@ -17203,10 +17440,10 @@
       <c r="N54" s="140"/>
     </row>
     <row r="55" spans="2:14">
-      <c r="D55" s="175" t="s">
+      <c r="D55" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E55" s="175"/>
+      <c r="E55" s="172"/>
       <c r="F55" s="138">
         <f>SUM(F49:F54)</f>
         <v>0</v>
@@ -17422,10 +17659,10 @@
       </c>
     </row>
     <row r="64" spans="2:14">
-      <c r="D64" s="175" t="s">
+      <c r="D64" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E64" s="175"/>
+      <c r="E64" s="172"/>
       <c r="F64" s="138">
         <f>SUM(F58:F63)</f>
         <v>0</v>
@@ -17643,10 +17880,10 @@
       </c>
     </row>
     <row r="73" spans="2:10">
-      <c r="D73" s="175" t="s">
+      <c r="D73" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E73" s="175"/>
+      <c r="E73" s="172"/>
       <c r="F73" s="138">
         <f>SUM(F67:F72)</f>
         <v>0</v>
@@ -17867,10 +18104,10 @@
       </c>
     </row>
     <row r="82" spans="2:10">
-      <c r="D82" s="175" t="s">
+      <c r="D82" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="E82" s="175"/>
+      <c r="E82" s="172"/>
       <c r="F82" s="138">
         <f>SUM(F76:F81)</f>
         <v>8.5500000000000007</v>
@@ -17894,6 +18131,24 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C49:C54"/>
     <mergeCell ref="D73:E73"/>
     <mergeCell ref="B76:B81"/>
     <mergeCell ref="C76:C81"/>
@@ -17904,24 +18159,6 @@
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="B67:B72"/>
     <mergeCell ref="C67:C72"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="C49:C54"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18259,17 +18496,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="185" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="129" t="s">
@@ -18301,10 +18538,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="177">
+      <c r="A4" s="179">
         <v>0.01</v>
       </c>
-      <c r="B4" s="180" t="s">
+      <c r="B4" s="182" t="s">
         <v>92</v>
       </c>
       <c r="C4" s="130">
@@ -18335,8 +18572,8 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5">
-      <c r="A5" s="178"/>
-      <c r="B5" s="181"/>
+      <c r="A5" s="180"/>
+      <c r="B5" s="183"/>
       <c r="C5" s="130">
         <v>2</v>
       </c>
@@ -18365,8 +18602,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5">
-      <c r="A6" s="178"/>
-      <c r="B6" s="181"/>
+      <c r="A6" s="180"/>
+      <c r="B6" s="183"/>
       <c r="C6" s="130">
         <v>3</v>
       </c>
@@ -18395,8 +18632,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
-      <c r="A7" s="178"/>
-      <c r="B7" s="181"/>
+      <c r="A7" s="180"/>
+      <c r="B7" s="183"/>
       <c r="C7" s="130">
         <v>4</v>
       </c>
@@ -18425,8 +18662,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5">
-      <c r="A8" s="178"/>
-      <c r="B8" s="181"/>
+      <c r="A8" s="180"/>
+      <c r="B8" s="183"/>
       <c r="C8" s="130">
         <v>5</v>
       </c>
@@ -18455,8 +18692,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
-      <c r="A9" s="179"/>
-      <c r="B9" s="182"/>
+      <c r="A9" s="181"/>
+      <c r="B9" s="184"/>
       <c r="C9" s="130">
         <v>6</v>
       </c>
@@ -18487,10 +18724,10 @@
     <row r="10" spans="1:9" ht="16.5">
       <c r="A10" s="126"/>
       <c r="B10" s="126"/>
-      <c r="C10" s="183" t="s">
+      <c r="C10" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="184"/>
+      <c r="D10" s="178"/>
       <c r="E10" s="146">
         <f>SUM(E4:E9)</f>
         <v>306</v>
@@ -18553,10 +18790,10 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.5">
-      <c r="A13" s="177">
+      <c r="A13" s="179">
         <v>0.01</v>
       </c>
-      <c r="B13" s="180" t="s">
+      <c r="B13" s="182" t="s">
         <v>100</v>
       </c>
       <c r="C13" s="130">
@@ -18587,8 +18824,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5">
-      <c r="A14" s="178"/>
-      <c r="B14" s="181"/>
+      <c r="A14" s="180"/>
+      <c r="B14" s="183"/>
       <c r="C14" s="130">
         <v>2</v>
       </c>
@@ -18617,8 +18854,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5">
-      <c r="A15" s="178"/>
-      <c r="B15" s="181"/>
+      <c r="A15" s="180"/>
+      <c r="B15" s="183"/>
       <c r="C15" s="130">
         <v>2</v>
       </c>
@@ -18647,8 +18884,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5">
-      <c r="A16" s="178"/>
-      <c r="B16" s="181"/>
+      <c r="A16" s="180"/>
+      <c r="B16" s="183"/>
       <c r="C16" s="130">
         <v>3</v>
       </c>
@@ -18677,8 +18914,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5">
-      <c r="A17" s="178"/>
-      <c r="B17" s="181"/>
+      <c r="A17" s="180"/>
+      <c r="B17" s="183"/>
       <c r="C17" s="130">
         <v>4</v>
       </c>
@@ -18707,8 +18944,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5">
-      <c r="A18" s="179"/>
-      <c r="B18" s="182"/>
+      <c r="A18" s="181"/>
+      <c r="B18" s="184"/>
       <c r="C18" s="130">
         <v>5</v>
       </c>
@@ -18739,10 +18976,10 @@
     <row r="19" spans="1:9" ht="16.5">
       <c r="A19" s="126"/>
       <c r="B19" s="126"/>
-      <c r="C19" s="183" t="s">
+      <c r="C19" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="184"/>
+      <c r="D19" s="178"/>
       <c r="E19" s="146">
         <f>SUM(E13:E18)</f>
         <v>474</v>
@@ -18805,10 +19042,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A22" s="177">
+      <c r="A22" s="179">
         <v>0.01</v>
       </c>
-      <c r="B22" s="180" t="s">
+      <c r="B22" s="182" t="s">
         <v>101</v>
       </c>
       <c r="C22" s="130">
@@ -18839,8 +19076,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5">
-      <c r="A23" s="178"/>
-      <c r="B23" s="181"/>
+      <c r="A23" s="180"/>
+      <c r="B23" s="183"/>
       <c r="C23" s="130">
         <v>2</v>
       </c>
@@ -18869,8 +19106,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5">
-      <c r="A24" s="178"/>
-      <c r="B24" s="181"/>
+      <c r="A24" s="180"/>
+      <c r="B24" s="183"/>
       <c r="C24" s="130">
         <v>2</v>
       </c>
@@ -18899,8 +19136,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5">
-      <c r="A25" s="178"/>
-      <c r="B25" s="181"/>
+      <c r="A25" s="180"/>
+      <c r="B25" s="183"/>
       <c r="C25" s="130">
         <v>3</v>
       </c>
@@ -18929,8 +19166,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5">
-      <c r="A26" s="178"/>
-      <c r="B26" s="181"/>
+      <c r="A26" s="180"/>
+      <c r="B26" s="183"/>
       <c r="C26" s="130">
         <v>4</v>
       </c>
@@ -18959,8 +19196,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5">
-      <c r="A27" s="179"/>
-      <c r="B27" s="182"/>
+      <c r="A27" s="181"/>
+      <c r="B27" s="184"/>
       <c r="C27" s="130">
         <v>5</v>
       </c>
@@ -18991,10 +19228,10 @@
     <row r="28" spans="1:9" ht="16.5">
       <c r="A28" s="126"/>
       <c r="B28" s="126"/>
-      <c r="C28" s="183" t="s">
+      <c r="C28" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="184"/>
+      <c r="D28" s="178"/>
       <c r="E28" s="146">
         <f>SUM(E22:E27)</f>
         <v>1855</v>
@@ -19057,10 +19294,10 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A31" s="177">
+      <c r="A31" s="179">
         <v>0.01</v>
       </c>
-      <c r="B31" s="180" t="s">
+      <c r="B31" s="182" t="s">
         <v>103</v>
       </c>
       <c r="C31" s="130">
@@ -19091,8 +19328,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5">
-      <c r="A32" s="178"/>
-      <c r="B32" s="181"/>
+      <c r="A32" s="180"/>
+      <c r="B32" s="183"/>
       <c r="C32" s="130">
         <v>2</v>
       </c>
@@ -19121,8 +19358,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5">
-      <c r="A33" s="178"/>
-      <c r="B33" s="181"/>
+      <c r="A33" s="180"/>
+      <c r="B33" s="183"/>
       <c r="C33" s="130">
         <v>2</v>
       </c>
@@ -19151,8 +19388,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5">
-      <c r="A34" s="178"/>
-      <c r="B34" s="181"/>
+      <c r="A34" s="180"/>
+      <c r="B34" s="183"/>
       <c r="C34" s="130">
         <v>3</v>
       </c>
@@ -19181,8 +19418,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5">
-      <c r="A35" s="178"/>
-      <c r="B35" s="181"/>
+      <c r="A35" s="180"/>
+      <c r="B35" s="183"/>
       <c r="C35" s="130">
         <v>4</v>
       </c>
@@ -19211,8 +19448,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5">
-      <c r="A36" s="179"/>
-      <c r="B36" s="182"/>
+      <c r="A36" s="181"/>
+      <c r="B36" s="184"/>
       <c r="C36" s="130">
         <v>5</v>
       </c>
@@ -19243,10 +19480,10 @@
     <row r="37" spans="1:9" ht="16.5">
       <c r="A37" s="126"/>
       <c r="B37" s="126"/>
-      <c r="C37" s="183" t="s">
+      <c r="C37" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="184"/>
+      <c r="D37" s="178"/>
       <c r="E37" s="146">
         <f>SUM(E31:E36)</f>
         <v>5270</v>
@@ -19309,10 +19546,10 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="16.5">
-      <c r="A40" s="177">
+      <c r="A40" s="179">
         <v>0.01</v>
       </c>
-      <c r="B40" s="180" t="s">
+      <c r="B40" s="182" t="s">
         <v>104</v>
       </c>
       <c r="C40" s="130">
@@ -19343,8 +19580,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5">
-      <c r="A41" s="178"/>
-      <c r="B41" s="181"/>
+      <c r="A41" s="180"/>
+      <c r="B41" s="183"/>
       <c r="C41" s="130">
         <v>2</v>
       </c>
@@ -19373,8 +19610,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.5">
-      <c r="A42" s="178"/>
-      <c r="B42" s="181"/>
+      <c r="A42" s="180"/>
+      <c r="B42" s="183"/>
       <c r="C42" s="130">
         <v>2</v>
       </c>
@@ -19403,8 +19640,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.5">
-      <c r="A43" s="178"/>
-      <c r="B43" s="181"/>
+      <c r="A43" s="180"/>
+      <c r="B43" s="183"/>
       <c r="C43" s="130">
         <v>3</v>
       </c>
@@ -19433,8 +19670,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.5">
-      <c r="A44" s="178"/>
-      <c r="B44" s="181"/>
+      <c r="A44" s="180"/>
+      <c r="B44" s="183"/>
       <c r="C44" s="130">
         <v>4</v>
       </c>
@@ -19463,8 +19700,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.5">
-      <c r="A45" s="179"/>
-      <c r="B45" s="182"/>
+      <c r="A45" s="181"/>
+      <c r="B45" s="184"/>
       <c r="C45" s="130">
         <v>5</v>
       </c>
@@ -19495,10 +19732,10 @@
     <row r="46" spans="1:9" ht="16.5">
       <c r="A46" s="126"/>
       <c r="B46" s="126"/>
-      <c r="C46" s="183" t="s">
+      <c r="C46" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="184"/>
+      <c r="D46" s="178"/>
       <c r="E46" s="146">
         <f>SUM(E40:E45)</f>
         <v>1161</v>
@@ -19561,10 +19798,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="16.5">
-      <c r="A49" s="177">
+      <c r="A49" s="179">
         <v>0.01</v>
       </c>
-      <c r="B49" s="180" t="s">
+      <c r="B49" s="182" t="s">
         <v>105</v>
       </c>
       <c r="C49" s="130">
@@ -19595,8 +19832,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="16.5">
-      <c r="A50" s="178"/>
-      <c r="B50" s="181"/>
+      <c r="A50" s="180"/>
+      <c r="B50" s="183"/>
       <c r="C50" s="130">
         <v>2</v>
       </c>
@@ -19625,8 +19862,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="16.5">
-      <c r="A51" s="178"/>
-      <c r="B51" s="181"/>
+      <c r="A51" s="180"/>
+      <c r="B51" s="183"/>
       <c r="C51" s="130">
         <v>2</v>
       </c>
@@ -19655,8 +19892,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="16.5">
-      <c r="A52" s="178"/>
-      <c r="B52" s="181"/>
+      <c r="A52" s="180"/>
+      <c r="B52" s="183"/>
       <c r="C52" s="130">
         <v>3</v>
       </c>
@@ -19685,8 +19922,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="16.5">
-      <c r="A53" s="178"/>
-      <c r="B53" s="181"/>
+      <c r="A53" s="180"/>
+      <c r="B53" s="183"/>
       <c r="C53" s="130">
         <v>4</v>
       </c>
@@ -19715,8 +19952,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="16.5">
-      <c r="A54" s="179"/>
-      <c r="B54" s="182"/>
+      <c r="A54" s="181"/>
+      <c r="B54" s="184"/>
       <c r="C54" s="130">
         <v>5</v>
       </c>
@@ -19747,10 +19984,10 @@
     <row r="55" spans="1:9" ht="16.5">
       <c r="A55" s="126"/>
       <c r="B55" s="126"/>
-      <c r="C55" s="183" t="s">
+      <c r="C55" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D55" s="184"/>
+      <c r="D55" s="178"/>
       <c r="E55" s="146">
         <f>SUM(E49:E54)</f>
         <v>138</v>
@@ -19813,10 +20050,10 @@
       </c>
     </row>
     <row r="58" spans="1:9" ht="16.5">
-      <c r="A58" s="177">
+      <c r="A58" s="179">
         <v>0.01</v>
       </c>
-      <c r="B58" s="180" t="s">
+      <c r="B58" s="182" t="s">
         <v>106</v>
       </c>
       <c r="C58" s="130">
@@ -19847,8 +20084,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="16.5">
-      <c r="A59" s="178"/>
-      <c r="B59" s="181"/>
+      <c r="A59" s="180"/>
+      <c r="B59" s="183"/>
       <c r="C59" s="130"/>
       <c r="D59" s="130" t="s">
         <v>94</v>
@@ -19875,8 +20112,8 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5">
-      <c r="A60" s="178"/>
-      <c r="B60" s="181"/>
+      <c r="A60" s="180"/>
+      <c r="B60" s="183"/>
       <c r="C60" s="130">
         <v>2</v>
       </c>
@@ -19905,8 +20142,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5">
-      <c r="A61" s="178"/>
-      <c r="B61" s="181"/>
+      <c r="A61" s="180"/>
+      <c r="B61" s="183"/>
       <c r="C61" s="130">
         <v>3</v>
       </c>
@@ -19935,8 +20172,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="16.5">
-      <c r="A62" s="178"/>
-      <c r="B62" s="181"/>
+      <c r="A62" s="180"/>
+      <c r="B62" s="183"/>
       <c r="C62" s="130">
         <v>4</v>
       </c>
@@ -19965,8 +20202,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5">
-      <c r="A63" s="179"/>
-      <c r="B63" s="182"/>
+      <c r="A63" s="181"/>
+      <c r="B63" s="184"/>
       <c r="C63" s="130">
         <v>5</v>
       </c>
@@ -19997,10 +20234,10 @@
     <row r="64" spans="1:9" ht="16.5">
       <c r="A64" s="126"/>
       <c r="B64" s="126"/>
-      <c r="C64" s="183" t="s">
+      <c r="C64" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D64" s="184"/>
+      <c r="D64" s="178"/>
       <c r="E64" s="146">
         <f>SUM(E58:E63)</f>
         <v>18</v>
@@ -20063,10 +20300,10 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="16.5">
-      <c r="A67" s="177">
+      <c r="A67" s="179">
         <v>0.01</v>
       </c>
-      <c r="B67" s="180" t="s">
+      <c r="B67" s="182" t="s">
         <v>107</v>
       </c>
       <c r="C67" s="130">
@@ -20097,8 +20334,8 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5">
-      <c r="A68" s="178"/>
-      <c r="B68" s="181"/>
+      <c r="A68" s="180"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="130">
         <v>2</v>
       </c>
@@ -20127,8 +20364,8 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="16.5">
-      <c r="A69" s="178"/>
-      <c r="B69" s="181"/>
+      <c r="A69" s="180"/>
+      <c r="B69" s="183"/>
       <c r="C69" s="130">
         <v>3</v>
       </c>
@@ -20157,8 +20394,8 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="16.5">
-      <c r="A70" s="178"/>
-      <c r="B70" s="181"/>
+      <c r="A70" s="180"/>
+      <c r="B70" s="183"/>
       <c r="C70" s="130">
         <v>4</v>
       </c>
@@ -20187,8 +20424,8 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="16.5">
-      <c r="A71" s="178"/>
-      <c r="B71" s="181"/>
+      <c r="A71" s="180"/>
+      <c r="B71" s="183"/>
       <c r="C71" s="130">
         <v>5</v>
       </c>
@@ -20217,8 +20454,8 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="16.5">
-      <c r="A72" s="179"/>
-      <c r="B72" s="182"/>
+      <c r="A72" s="181"/>
+      <c r="B72" s="184"/>
       <c r="C72" s="130">
         <v>6</v>
       </c>
@@ -20249,10 +20486,10 @@
     <row r="73" spans="1:9" ht="16.5">
       <c r="A73" s="126"/>
       <c r="B73" s="126"/>
-      <c r="C73" s="183" t="s">
+      <c r="C73" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="184"/>
+      <c r="D73" s="178"/>
       <c r="E73" s="151">
         <f>SUM(E67:E72)</f>
         <v>3.8085000000000004</v>
@@ -20315,10 +20552,10 @@
       </c>
     </row>
     <row r="76" spans="1:9" ht="16.5">
-      <c r="A76" s="177">
+      <c r="A76" s="179">
         <v>0.01</v>
       </c>
-      <c r="B76" s="180" t="s">
+      <c r="B76" s="182" t="s">
         <v>108</v>
       </c>
       <c r="C76" s="130">
@@ -20349,8 +20586,8 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="16.5">
-      <c r="A77" s="178"/>
-      <c r="B77" s="181"/>
+      <c r="A77" s="180"/>
+      <c r="B77" s="183"/>
       <c r="C77" s="130">
         <v>2</v>
       </c>
@@ -20379,8 +20616,8 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5">
-      <c r="A78" s="178"/>
-      <c r="B78" s="181"/>
+      <c r="A78" s="180"/>
+      <c r="B78" s="183"/>
       <c r="C78" s="130">
         <v>3</v>
       </c>
@@ -20409,8 +20646,8 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="16.5">
-      <c r="A79" s="178"/>
-      <c r="B79" s="181"/>
+      <c r="A79" s="180"/>
+      <c r="B79" s="183"/>
       <c r="C79" s="130">
         <v>4</v>
       </c>
@@ -20439,8 +20676,8 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="16.5">
-      <c r="A80" s="178"/>
-      <c r="B80" s="181"/>
+      <c r="A80" s="180"/>
+      <c r="B80" s="183"/>
       <c r="C80" s="130">
         <v>5</v>
       </c>
@@ -20469,8 +20706,8 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="16.5">
-      <c r="A81" s="179"/>
-      <c r="B81" s="182"/>
+      <c r="A81" s="181"/>
+      <c r="B81" s="184"/>
       <c r="C81" s="130">
         <v>6</v>
       </c>
@@ -20501,10 +20738,10 @@
     <row r="82" spans="1:9" ht="16.5">
       <c r="A82" s="126"/>
       <c r="B82" s="126"/>
-      <c r="C82" s="183" t="s">
+      <c r="C82" s="177" t="s">
         <v>99</v>
       </c>
-      <c r="D82" s="184"/>
+      <c r="D82" s="178"/>
       <c r="E82" s="151">
         <f>SUM(E76:E81)</f>
         <v>188.65</v>
@@ -20528,6 +20765,24 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="A76:A81"/>
     <mergeCell ref="B76:B81"/>
@@ -20538,24 +20793,6 @@
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="A67:A72"/>
     <mergeCell ref="B67:B72"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="B13:B18"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20564,7 +20801,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B5:K45"/>
+  <dimension ref="B5:O45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
@@ -20572,44 +20809,47 @@
     <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:11">
-      <c r="B5" s="185" t="s">
+    <row r="5" spans="2:15">
+      <c r="B5" s="186" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="188" t="s">
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="189" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="186">
+      <c r="C8" s="187">
         <v>46174</v>
       </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="187" t="s">
+      <c r="D8" s="187"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="187" t="s">
+      <c r="H8" s="188" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="187" t="s">
+      <c r="I8" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="187"/>
-      <c r="K8" s="187"/>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="189"/>
+      <c r="J8" s="188"/>
+      <c r="K8" s="188"/>
+      <c r="N8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="190"/>
       <c r="C9" s="153" t="s">
         <v>113</v>
       </c>
@@ -20622,8 +20862,8 @@
       <c r="F9" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="187"/>
-      <c r="H9" s="187"/>
+      <c r="G9" s="188"/>
+      <c r="H9" s="188"/>
       <c r="I9" s="153" t="s">
         <v>65</v>
       </c>
@@ -20633,8 +20873,14 @@
       <c r="K9" s="153" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -20645,8 +20891,14 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="2:11">
+      <c r="N10" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15">
       <c r="B11" s="1" t="s">
         <v>117</v>
       </c>
@@ -20677,8 +20929,14 @@
       <c r="K11" s="1">
         <v>-163331.99999999924</v>
       </c>
-    </row>
-    <row r="12" spans="2:11">
+      <c r="N11" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15">
       <c r="B12" s="1" t="s">
         <v>119</v>
       </c>
@@ -20709,8 +20967,14 @@
       <c r="K12" s="1">
         <v>141499.10000000533</v>
       </c>
-    </row>
-    <row r="13" spans="2:11">
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15">
       <c r="B13" s="1" t="s">
         <v>120</v>
       </c>
@@ -20742,7 +21006,7 @@
         <v>-496177.00000000768</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:15">
       <c r="B14" s="1" t="s">
         <v>121</v>
       </c>
@@ -20774,7 +21038,7 @@
         <v>56.068920000000162</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:15">
       <c r="B15" s="1" t="s">
         <v>123</v>
       </c>
@@ -20806,7 +21070,7 @@
         <v>358018.04999999818</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="2:15">
       <c r="B16" s="1" t="s">
         <v>124</v>
       </c>

--- a/target project.xlsx
+++ b/target project.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950"/>
   </bookViews>
   <sheets>
     <sheet name="TARGET" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="168">
   <si>
     <t xml:space="preserve"> cek ulang tampilan dashboard bad produk mesin dominan, masih menampilkan data mesin yang tidak di pilih di sortasi,</t>
   </si>
@@ -118,13 +118,7 @@
     <t>table pvdc dan wire</t>
   </si>
   <si>
-    <t>kode batch yang sudah di input tidak boleh di input ulang lagi, hilangkan dari dropdown</t>
-  </si>
-  <si>
     <t>filkar</t>
-  </si>
-  <si>
-    <t>release boleh lebih dari wip, tapi kasih warning</t>
   </si>
   <si>
     <t>sortasi</t>
@@ -475,16 +469,7 @@
     <t>edit filkar masih error</t>
   </si>
   <si>
-    <t>membuat tabel cucian dan detail cucian di database</t>
-  </si>
-  <si>
     <t>membuat controller dan modelnya, view</t>
-  </si>
-  <si>
-    <t>menampilkan sensor suhu di portal dashboard maintenance</t>
-  </si>
-  <si>
-    <t>menambahkan portal produktifitas di packing</t>
   </si>
   <si>
     <t>macam-macam sortasi : sortasi - release, sortasi - tampung, sortasi - kasar</t>
@@ -547,13 +532,25 @@
     <t>Maintenance</t>
   </si>
   <si>
-    <t>menunggu link API nya.</t>
-  </si>
-  <si>
     <t>Hanya tampilan di dashboard</t>
   </si>
   <si>
     <t>Tinggal tempel jika ada fitur baru</t>
+  </si>
+  <si>
+    <t>rework</t>
+  </si>
+  <si>
+    <t>edit kupas error</t>
+  </si>
+  <si>
+    <t>kondisi saat tambah group kupas berat total tidak boleh lebih dari total rework</t>
+  </si>
+  <si>
+    <t>pvdc dan wire, tiap hari input pemakaian.</t>
+  </si>
+  <si>
+    <t>rencananya akan menggunakan iframe dari grafana</t>
   </si>
 </sst>
 </file>
@@ -1537,7 +1534,7 @@
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1976,16 +1973,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="10" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2006,20 +2021,11 @@
     <xf numFmtId="1" fontId="5" fillId="10" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2027,17 +2033,11 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="28" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2057,8 +2057,11 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2075,12 +2078,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="248">
     <cellStyle name="20% - Accent1 2" xfId="8"/>
@@ -4941,7 +4939,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="4" t="s">
@@ -4953,7 +4951,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="4"/>
@@ -5002,7 +5000,7 @@
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="158" t="s">
+      <c r="D8" s="159" t="s">
         <v>13</v>
       </c>
     </row>
@@ -5012,7 +5010,7 @@
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="159"/>
+      <c r="D9" s="160"/>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="4" t="s">
@@ -5020,7 +5018,7 @@
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="158" t="s">
+      <c r="D10" s="159" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5030,7 +5028,7 @@
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="159"/>
+      <c r="D11" s="160"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
@@ -5070,141 +5068,120 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" ht="30">
-      <c r="A17" s="11" t="s">
-        <v>23</v>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
+    <row r="18" spans="1:4" ht="45">
+      <c r="A18" s="14" t="s">
+        <v>26</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="15" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" ht="45">
-      <c r="A20" s="14" t="s">
-        <v>28</v>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1"/>
-      <c r="D20" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="D20" s="1"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>40</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="13"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>43</v>
-      </c>
+      <c r="A22" s="154">
+        <v>46266</v>
+      </c>
+      <c r="B22" s="152"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="1"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="156"/>
+      <c r="C23" s="155"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="154">
-        <v>46266</v>
+      <c r="A24" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="B24" s="152"/>
-      <c r="C24" s="1"/>
+      <c r="C24" s="155"/>
       <c r="D24" s="1"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="156"/>
-      <c r="C25" s="155"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="152"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="1"/>
       <c r="D26" s="1"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="152"/>
-      <c r="C27" s="155"/>
+      <c r="A27" s="1"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="1"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B28" s="152"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="1"/>
-    </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="1"/>
+      <c r="A29" s="193">
+        <v>46151</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="1"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="1"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="A32" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5230,29 +5207,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="191" t="s">
-        <v>147</v>
-      </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
-      <c r="E1" s="191"/>
+      <c r="A1" s="161" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" s="192" t="s">
-        <v>157</v>
+        <v>148</v>
+      </c>
+      <c r="D2" s="158" t="s">
+        <v>152</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5260,16 +5237,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="192">
-        <v>30</v>
+      <c r="D3" s="158">
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5278,34 +5255,34 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D4" s="192">
+        <v>151</v>
+      </c>
+      <c r="D4" s="158">
         <v>100</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A13" si="0">IF(B5="","",A4+1)</f>
+        <f t="shared" ref="A5:A7" si="0">IF(B5="","",A4+1)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D5" s="192">
+        <v>151</v>
+      </c>
+      <c r="D5" s="158">
         <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5314,16 +5291,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="192">
+        <v>150</v>
+      </c>
+      <c r="D6" s="158">
         <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5332,92 +5309,92 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="192">
-        <v>50</v>
+        <v>150</v>
+      </c>
+      <c r="D7" s="158">
+        <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B9="","",A7+1)</f>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="192"/>
-      <c r="E8" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="D8" s="158">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B10="","",A8+1)</f>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="192"/>
+        <v>150</v>
+      </c>
+      <c r="D9" s="158"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
+        <f>IF(B8="","",A9+1)</f>
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" s="192">
-        <v>50</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>166</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D10" s="158"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A11" s="1">
+        <f t="shared" ref="A11:A13" si="1">IF(B9="","",A10+1)</f>
+        <v>9</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="192"/>
+      <c r="D11" s="158"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A12" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="192"/>
+      <c r="D12" s="158"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="192"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="1"/>
     </row>
   </sheetData>
@@ -10785,7 +10762,7 @@
   <sheetData>
     <row r="1" spans="2:118" ht="18" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -10884,7 +10861,7 @@
     </row>
     <row r="2" spans="2:118" ht="18" customHeight="1">
       <c r="B2" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
@@ -11061,147 +11038,147 @@
     </row>
     <row r="4" spans="2:118" ht="22.5" customHeight="1">
       <c r="B4" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
-      <c r="K4" s="168" t="s">
+      <c r="K4" s="162" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="163"/>
+      <c r="M4" s="164"/>
+      <c r="O4" s="162" t="s">
+        <v>46</v>
+      </c>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="164"/>
+      <c r="S4" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="160"/>
-      <c r="M4" s="169"/>
-      <c r="O4" s="168" t="s">
+      <c r="T4" s="163"/>
+      <c r="U4" s="164"/>
+      <c r="W4" s="162" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="160"/>
-      <c r="Q4" s="169"/>
-      <c r="S4" s="168" t="s">
+      <c r="X4" s="163"/>
+      <c r="Y4" s="164"/>
+      <c r="AA4" s="162" t="s">
         <v>49</v>
       </c>
-      <c r="T4" s="160"/>
-      <c r="U4" s="169"/>
-      <c r="W4" s="168" t="s">
+      <c r="AB4" s="163"/>
+      <c r="AC4" s="163"/>
+      <c r="AD4" s="29"/>
+      <c r="AF4" s="162" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="160"/>
-      <c r="Y4" s="169"/>
-      <c r="AA4" s="168" t="s">
+      <c r="AG4" s="163"/>
+      <c r="AH4" s="164"/>
+      <c r="AJ4" s="162" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="160"/>
-      <c r="AC4" s="160"/>
-      <c r="AD4" s="29"/>
-      <c r="AF4" s="168" t="s">
+      <c r="AK4" s="163"/>
+      <c r="AL4" s="163"/>
+      <c r="AN4" s="162" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="160"/>
-      <c r="AH4" s="169"/>
-      <c r="AJ4" s="168" t="s">
+      <c r="AO4" s="163"/>
+      <c r="AP4" s="164"/>
+      <c r="AR4" s="163" t="s">
         <v>53</v>
       </c>
-      <c r="AK4" s="160"/>
-      <c r="AL4" s="160"/>
-      <c r="AN4" s="168" t="s">
+      <c r="AS4" s="163"/>
+      <c r="AT4" s="163"/>
+      <c r="AV4" s="163" t="s">
         <v>54</v>
       </c>
-      <c r="AO4" s="160"/>
-      <c r="AP4" s="169"/>
-      <c r="AR4" s="160" t="s">
+      <c r="AW4" s="163"/>
+      <c r="AX4" s="163"/>
+      <c r="AZ4" s="163" t="s">
         <v>55</v>
       </c>
-      <c r="AS4" s="160"/>
-      <c r="AT4" s="160"/>
-      <c r="AV4" s="160" t="s">
+      <c r="BA4" s="163"/>
+      <c r="BB4" s="163"/>
+      <c r="BD4" s="163" t="s">
         <v>56</v>
       </c>
-      <c r="AW4" s="160"/>
-      <c r="AX4" s="160"/>
-      <c r="AZ4" s="160" t="s">
+      <c r="BE4" s="163"/>
+      <c r="BF4" s="163"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="BA4" s="160"/>
-      <c r="BB4" s="160"/>
-      <c r="BD4" s="160" t="s">
+      <c r="BI4" s="169"/>
+      <c r="BJ4" s="170"/>
+      <c r="BK4" s="30"/>
+      <c r="BL4" s="162" t="s">
+        <v>45</v>
+      </c>
+      <c r="BM4" s="163"/>
+      <c r="BN4" s="164"/>
+      <c r="BP4" s="162" t="s">
+        <v>46</v>
+      </c>
+      <c r="BQ4" s="163"/>
+      <c r="BR4" s="164"/>
+      <c r="BT4" s="162" t="s">
+        <v>47</v>
+      </c>
+      <c r="BU4" s="163"/>
+      <c r="BV4" s="164"/>
+      <c r="BX4" s="162" t="s">
+        <v>48</v>
+      </c>
+      <c r="BY4" s="163"/>
+      <c r="BZ4" s="164"/>
+      <c r="CB4" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="CC4" s="163"/>
+      <c r="CD4" s="163"/>
+      <c r="CE4" s="29"/>
+      <c r="CG4" s="162" t="s">
+        <v>50</v>
+      </c>
+      <c r="CH4" s="163"/>
+      <c r="CI4" s="164"/>
+      <c r="CK4" s="162" t="s">
+        <v>51</v>
+      </c>
+      <c r="CL4" s="163"/>
+      <c r="CM4" s="163"/>
+      <c r="CO4" s="162" t="s">
+        <v>52</v>
+      </c>
+      <c r="CP4" s="163"/>
+      <c r="CQ4" s="164"/>
+      <c r="CS4" s="163" t="s">
+        <v>53</v>
+      </c>
+      <c r="CT4" s="163"/>
+      <c r="CU4" s="163"/>
+      <c r="CW4" s="163" t="s">
+        <v>54</v>
+      </c>
+      <c r="CX4" s="163"/>
+      <c r="CY4" s="163"/>
+      <c r="DA4" s="163" t="s">
+        <v>55</v>
+      </c>
+      <c r="DB4" s="163"/>
+      <c r="DC4" s="163"/>
+      <c r="DE4" s="163" t="s">
+        <v>56</v>
+      </c>
+      <c r="DF4" s="163"/>
+      <c r="DG4" s="163"/>
+      <c r="DH4" s="30"/>
+      <c r="DI4" s="168" t="s">
         <v>58</v>
       </c>
-      <c r="BE4" s="160"/>
-      <c r="BF4" s="160"/>
-      <c r="BG4" s="30"/>
-      <c r="BH4" s="162" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI4" s="163"/>
-      <c r="BJ4" s="164"/>
-      <c r="BK4" s="30"/>
-      <c r="BL4" s="168" t="s">
-        <v>47</v>
-      </c>
-      <c r="BM4" s="160"/>
-      <c r="BN4" s="169"/>
-      <c r="BP4" s="168" t="s">
-        <v>48</v>
-      </c>
-      <c r="BQ4" s="160"/>
-      <c r="BR4" s="169"/>
-      <c r="BT4" s="168" t="s">
-        <v>49</v>
-      </c>
-      <c r="BU4" s="160"/>
-      <c r="BV4" s="169"/>
-      <c r="BX4" s="168" t="s">
-        <v>50</v>
-      </c>
-      <c r="BY4" s="160"/>
-      <c r="BZ4" s="169"/>
-      <c r="CB4" s="168" t="s">
-        <v>51</v>
-      </c>
-      <c r="CC4" s="160"/>
-      <c r="CD4" s="160"/>
-      <c r="CE4" s="29"/>
-      <c r="CG4" s="168" t="s">
-        <v>52</v>
-      </c>
-      <c r="CH4" s="160"/>
-      <c r="CI4" s="169"/>
-      <c r="CK4" s="168" t="s">
-        <v>53</v>
-      </c>
-      <c r="CL4" s="160"/>
-      <c r="CM4" s="160"/>
-      <c r="CO4" s="168" t="s">
-        <v>54</v>
-      </c>
-      <c r="CP4" s="160"/>
-      <c r="CQ4" s="169"/>
-      <c r="CS4" s="160" t="s">
-        <v>55</v>
-      </c>
-      <c r="CT4" s="160"/>
-      <c r="CU4" s="160"/>
-      <c r="CW4" s="160" t="s">
-        <v>56</v>
-      </c>
-      <c r="CX4" s="160"/>
-      <c r="CY4" s="160"/>
-      <c r="DA4" s="160" t="s">
-        <v>57</v>
-      </c>
-      <c r="DB4" s="160"/>
-      <c r="DC4" s="160"/>
-      <c r="DE4" s="160" t="s">
-        <v>58</v>
-      </c>
-      <c r="DF4" s="160"/>
-      <c r="DG4" s="160"/>
-      <c r="DH4" s="30"/>
-      <c r="DI4" s="162" t="s">
-        <v>60</v>
-      </c>
-      <c r="DJ4" s="163"/>
-      <c r="DK4" s="164"/>
+      <c r="DJ4" s="169"/>
+      <c r="DK4" s="170"/>
       <c r="DL4" s="31"/>
       <c r="DM4" s="31"/>
       <c r="DN4" s="31"/>
@@ -11210,95 +11187,95 @@
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
       <c r="E5" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F5" s="33"/>
       <c r="G5" s="33"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
-      <c r="K5" s="170"/>
-      <c r="L5" s="161"/>
-      <c r="M5" s="171"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="161"/>
-      <c r="Q5" s="171"/>
-      <c r="S5" s="170"/>
-      <c r="T5" s="161"/>
-      <c r="U5" s="171"/>
-      <c r="W5" s="170"/>
-      <c r="X5" s="161"/>
-      <c r="Y5" s="171"/>
-      <c r="AA5" s="170"/>
-      <c r="AB5" s="161"/>
-      <c r="AC5" s="161"/>
+      <c r="K5" s="165"/>
+      <c r="L5" s="166"/>
+      <c r="M5" s="167"/>
+      <c r="O5" s="165"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="167"/>
+      <c r="S5" s="165"/>
+      <c r="T5" s="166"/>
+      <c r="U5" s="167"/>
+      <c r="W5" s="165"/>
+      <c r="X5" s="166"/>
+      <c r="Y5" s="167"/>
+      <c r="AA5" s="165"/>
+      <c r="AB5" s="166"/>
+      <c r="AC5" s="166"/>
       <c r="AD5" s="34"/>
-      <c r="AF5" s="170"/>
-      <c r="AG5" s="161"/>
-      <c r="AH5" s="171"/>
-      <c r="AJ5" s="170"/>
-      <c r="AK5" s="161"/>
-      <c r="AL5" s="161"/>
-      <c r="AN5" s="170"/>
-      <c r="AO5" s="161"/>
-      <c r="AP5" s="171"/>
-      <c r="AR5" s="161"/>
-      <c r="AS5" s="161"/>
-      <c r="AT5" s="161"/>
-      <c r="AV5" s="161"/>
-      <c r="AW5" s="161"/>
-      <c r="AX5" s="161"/>
-      <c r="AZ5" s="161"/>
-      <c r="BA5" s="161"/>
-      <c r="BB5" s="161"/>
-      <c r="BD5" s="161"/>
-      <c r="BE5" s="161"/>
-      <c r="BF5" s="161"/>
+      <c r="AF5" s="165"/>
+      <c r="AG5" s="166"/>
+      <c r="AH5" s="167"/>
+      <c r="AJ5" s="165"/>
+      <c r="AK5" s="166"/>
+      <c r="AL5" s="166"/>
+      <c r="AN5" s="165"/>
+      <c r="AO5" s="166"/>
+      <c r="AP5" s="167"/>
+      <c r="AR5" s="166"/>
+      <c r="AS5" s="166"/>
+      <c r="AT5" s="166"/>
+      <c r="AV5" s="166"/>
+      <c r="AW5" s="166"/>
+      <c r="AX5" s="166"/>
+      <c r="AZ5" s="166"/>
+      <c r="BA5" s="166"/>
+      <c r="BB5" s="166"/>
+      <c r="BD5" s="166"/>
+      <c r="BE5" s="166"/>
+      <c r="BF5" s="166"/>
       <c r="BG5" s="30"/>
-      <c r="BH5" s="165"/>
-      <c r="BI5" s="166"/>
-      <c r="BJ5" s="167"/>
+      <c r="BH5" s="171"/>
+      <c r="BI5" s="172"/>
+      <c r="BJ5" s="173"/>
       <c r="BK5" s="30"/>
-      <c r="BL5" s="170"/>
-      <c r="BM5" s="161"/>
-      <c r="BN5" s="171"/>
-      <c r="BP5" s="170"/>
-      <c r="BQ5" s="161"/>
-      <c r="BR5" s="171"/>
-      <c r="BT5" s="170"/>
-      <c r="BU5" s="161"/>
-      <c r="BV5" s="171"/>
-      <c r="BX5" s="170"/>
-      <c r="BY5" s="161"/>
-      <c r="BZ5" s="171"/>
-      <c r="CB5" s="170"/>
-      <c r="CC5" s="161"/>
-      <c r="CD5" s="161"/>
+      <c r="BL5" s="165"/>
+      <c r="BM5" s="166"/>
+      <c r="BN5" s="167"/>
+      <c r="BP5" s="165"/>
+      <c r="BQ5" s="166"/>
+      <c r="BR5" s="167"/>
+      <c r="BT5" s="165"/>
+      <c r="BU5" s="166"/>
+      <c r="BV5" s="167"/>
+      <c r="BX5" s="165"/>
+      <c r="BY5" s="166"/>
+      <c r="BZ5" s="167"/>
+      <c r="CB5" s="165"/>
+      <c r="CC5" s="166"/>
+      <c r="CD5" s="166"/>
       <c r="CE5" s="34"/>
-      <c r="CG5" s="170"/>
-      <c r="CH5" s="161"/>
-      <c r="CI5" s="171"/>
-      <c r="CK5" s="170"/>
-      <c r="CL5" s="161"/>
-      <c r="CM5" s="161"/>
-      <c r="CO5" s="170"/>
-      <c r="CP5" s="161"/>
-      <c r="CQ5" s="171"/>
-      <c r="CS5" s="161"/>
-      <c r="CT5" s="161"/>
-      <c r="CU5" s="161"/>
-      <c r="CW5" s="161"/>
-      <c r="CX5" s="161"/>
-      <c r="CY5" s="161"/>
-      <c r="DA5" s="161"/>
-      <c r="DB5" s="161"/>
-      <c r="DC5" s="161"/>
-      <c r="DE5" s="161"/>
-      <c r="DF5" s="161"/>
-      <c r="DG5" s="161"/>
+      <c r="CG5" s="165"/>
+      <c r="CH5" s="166"/>
+      <c r="CI5" s="167"/>
+      <c r="CK5" s="165"/>
+      <c r="CL5" s="166"/>
+      <c r="CM5" s="166"/>
+      <c r="CO5" s="165"/>
+      <c r="CP5" s="166"/>
+      <c r="CQ5" s="167"/>
+      <c r="CS5" s="166"/>
+      <c r="CT5" s="166"/>
+      <c r="CU5" s="166"/>
+      <c r="CW5" s="166"/>
+      <c r="CX5" s="166"/>
+      <c r="CY5" s="166"/>
+      <c r="DA5" s="166"/>
+      <c r="DB5" s="166"/>
+      <c r="DC5" s="166"/>
+      <c r="DE5" s="166"/>
+      <c r="DF5" s="166"/>
+      <c r="DG5" s="166"/>
       <c r="DH5" s="30"/>
-      <c r="DI5" s="165"/>
-      <c r="DJ5" s="166"/>
-      <c r="DK5" s="167"/>
+      <c r="DI5" s="171"/>
+      <c r="DJ5" s="172"/>
+      <c r="DK5" s="173"/>
       <c r="DL5" s="31"/>
       <c r="DM5" s="31"/>
       <c r="DN5" s="31"/>
@@ -11403,275 +11380,275 @@
     </row>
     <row r="7" spans="2:118" ht="15" customHeight="1">
       <c r="B7" s="36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" s="38"/>
       <c r="E7" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="H7" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="I7" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="K7" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="L7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="K7" s="43" t="s">
+      <c r="O7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="P7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="T7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="U7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="W7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="X7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="L7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="44" t="s">
+      <c r="AB7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD7" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="O7" s="45" t="s">
+      <c r="AF7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="P7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="S7" s="45" t="s">
+      <c r="AG7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AH7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="T7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="U7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="W7" s="45" t="s">
+      <c r="AK7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="X7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB7" s="45" t="s">
+      <c r="AO7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR7" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="AC7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD7" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="AO7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="AP7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="AR7" s="45" t="s">
-        <v>71</v>
-      </c>
       <c r="AS7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AT7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AU7" s="26"/>
       <c r="AV7" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AW7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AX7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AY7" s="26"/>
       <c r="AZ7" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BA7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BB7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BC7" s="26"/>
       <c r="BD7" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BE7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BF7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BG7" s="47"/>
       <c r="BH7" s="46" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BI7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="BJ7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="BK7" s="48"/>
       <c r="BL7" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="BM7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="BN7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="BP7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="BT7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="BU7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="BV7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="BX7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="BY7" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="BZ7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="CB7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="BN7" s="44" t="s">
+      <c r="CC7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="CD7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="CE7" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="BP7" s="45" t="s">
+      <c r="CG7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="BQ7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="BR7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT7" s="45" t="s">
+      <c r="CH7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="CI7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="CK7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="BU7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="BV7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="BX7" s="45" t="s">
+      <c r="CL7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="CM7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="CO7" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="BY7" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="BZ7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="CB7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="CC7" s="45" t="s">
+      <c r="CP7" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="CQ7" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS7" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="CD7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="CE7" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="CG7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="CH7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="CI7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="CK7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="CL7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="CM7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="CO7" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="CP7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="CQ7" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="CS7" s="45" t="s">
-        <v>71</v>
-      </c>
       <c r="CT7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="CU7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="CV7" s="26"/>
       <c r="CW7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="CX7" s="43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="CY7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="CZ7" s="26"/>
       <c r="DA7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="DB7" s="43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="DC7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="DD7" s="26"/>
       <c r="DE7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="DF7" s="43" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="DG7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="DH7" s="47"/>
       <c r="DI7" s="45" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="DJ7" s="45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="DK7" s="44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:118" ht="16.5" customHeight="1">
@@ -11684,196 +11661,196 @@
       <c r="H8" s="53"/>
       <c r="I8" s="41"/>
       <c r="K8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L8" s="55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M8" s="54"/>
       <c r="O8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q8" s="54"/>
       <c r="S8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="U8" s="54"/>
       <c r="W8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="X8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Y8" s="54"/>
       <c r="AA8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AB8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AC8" s="54"/>
       <c r="AD8" s="54"/>
       <c r="AF8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AG8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AH8" s="54"/>
       <c r="AJ8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AL8" s="54"/>
       <c r="AN8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AO8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AP8" s="54"/>
       <c r="AR8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AS8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AT8" s="54"/>
       <c r="AU8" s="26"/>
       <c r="AV8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AW8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AX8" s="54"/>
       <c r="AY8" s="26"/>
       <c r="AZ8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BA8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BB8" s="54"/>
       <c r="BC8" s="26"/>
       <c r="BD8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BE8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BF8" s="54"/>
       <c r="BG8" s="48"/>
       <c r="BH8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BI8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BJ8" s="54"/>
       <c r="BK8" s="48"/>
       <c r="BL8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BM8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BN8" s="54"/>
       <c r="BP8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BQ8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BR8" s="54"/>
       <c r="BT8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BU8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BV8" s="54"/>
       <c r="BX8" s="54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BY8" s="55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="BZ8" s="54"/>
       <c r="CB8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CC8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CD8" s="54"/>
       <c r="CE8" s="54"/>
       <c r="CG8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CH8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CI8" s="54"/>
       <c r="CK8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CL8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CM8" s="54"/>
       <c r="CO8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CP8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CQ8" s="54"/>
       <c r="CS8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CT8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="CU8" s="54"/>
       <c r="CV8" s="26"/>
       <c r="CW8" s="45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="CX8" s="55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="CY8" s="54"/>
       <c r="CZ8" s="26"/>
       <c r="DA8" s="45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="DB8" s="55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="DC8" s="54"/>
       <c r="DD8" s="26"/>
       <c r="DE8" s="45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="DF8" s="55" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="DG8" s="54"/>
       <c r="DH8" s="48"/>
       <c r="DI8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="DJ8" s="45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="DK8" s="54"/>
     </row>
@@ -11980,14 +11957,14 @@
         <v>1</v>
       </c>
       <c r="C10" s="62" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" s="63"/>
       <c r="E10" s="64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F10" s="65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G10" s="66">
         <v>0.98499999999999999</v>
@@ -12353,10 +12330,10 @@
       <c r="C12" s="83"/>
       <c r="D12" s="63"/>
       <c r="E12" s="64" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F12" s="65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G12" s="66">
         <v>0.98499999999999999</v>
@@ -12701,14 +12678,14 @@
         <v>2</v>
       </c>
       <c r="C14" s="62" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D14" s="63"/>
       <c r="E14" s="64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F14" s="65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G14" s="66">
         <v>0.98499999999999999</v>
@@ -13068,10 +13045,10 @@
       <c r="C16" s="83"/>
       <c r="D16" s="63"/>
       <c r="E16" s="64" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" s="65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G16" s="66">
         <v>0.98499999999999999</v>
@@ -13411,14 +13388,14 @@
         <v>3</v>
       </c>
       <c r="C18" s="62" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D18" s="63"/>
       <c r="E18" s="64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G18" s="66">
         <v>0.98499999999999999</v>
@@ -13772,10 +13749,10 @@
       <c r="C20" s="83"/>
       <c r="D20" s="63"/>
       <c r="E20" s="64" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F20" s="65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G20" s="66">
         <v>0.98499999999999999</v>
@@ -14109,14 +14086,14 @@
         <v>4</v>
       </c>
       <c r="C22" s="62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" s="63"/>
       <c r="E22" s="64" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F22" s="65" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G22" s="66">
         <v>0.98499999999999999</v>
@@ -14476,10 +14453,10 @@
       <c r="C24" s="83"/>
       <c r="D24" s="63"/>
       <c r="E24" s="64" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" s="65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G24" s="66">
         <v>0.98499999999999999</v>
@@ -15040,12 +15017,14 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="AF4:AH5"/>
-    <mergeCell ref="K4:M5"/>
-    <mergeCell ref="O4:Q5"/>
-    <mergeCell ref="S4:U5"/>
-    <mergeCell ref="W4:Y5"/>
-    <mergeCell ref="AA4:AC5"/>
+    <mergeCell ref="DE4:DG5"/>
+    <mergeCell ref="DI4:DK5"/>
+    <mergeCell ref="CG4:CI5"/>
+    <mergeCell ref="CK4:CM5"/>
+    <mergeCell ref="CO4:CQ5"/>
+    <mergeCell ref="CS4:CU5"/>
+    <mergeCell ref="CW4:CY5"/>
+    <mergeCell ref="DA4:DC5"/>
     <mergeCell ref="CB4:CD5"/>
     <mergeCell ref="AJ4:AL5"/>
     <mergeCell ref="AN4:AP5"/>
@@ -15058,14 +15037,12 @@
     <mergeCell ref="BP4:BR5"/>
     <mergeCell ref="BT4:BV5"/>
     <mergeCell ref="BX4:BZ5"/>
-    <mergeCell ref="DE4:DG5"/>
-    <mergeCell ref="DI4:DK5"/>
-    <mergeCell ref="CG4:CI5"/>
-    <mergeCell ref="CK4:CM5"/>
-    <mergeCell ref="CO4:CQ5"/>
-    <mergeCell ref="CS4:CU5"/>
-    <mergeCell ref="CW4:CY5"/>
-    <mergeCell ref="DA4:DC5"/>
+    <mergeCell ref="AF4:AH5"/>
+    <mergeCell ref="K4:M5"/>
+    <mergeCell ref="O4:Q5"/>
+    <mergeCell ref="S4:U5"/>
+    <mergeCell ref="W4:Y5"/>
+    <mergeCell ref="AA4:AC5"/>
   </mergeCells>
   <conditionalFormatting sqref="BR10 BR12 BR14 BR16 BR18 BR20 BR22 BR24 BV10 BV12 BV14 BV16 BV18 BV20 BV22 BV24 BZ10 BZ12 BZ14 BZ16 BZ18 BZ20 BZ22 BZ24 AC10 AC12 AC14 AC16 AC18 AC20 AC22 AC24 AH10 AH12 AH14 AH16 AH18 AH20 AH22 AH24 AL10 AL12 AL14 AL16 AL18 AL20 AL22 AL24 AP10 AP12:AP14 AP16 AP18 AP20 AP22 AP24 AT24 AT20 AT18 AT16 AT14 AT12 AT10 AT22 BJ10 BJ12 BJ14 BJ16 BJ18 BJ20 BJ22 BJ24 Y10 Y12 Y14 Y16 Y18 Y20 Y22 Y24 U10 U12 U14 U16 U18 U20 U22 U24 Q10 Q12 Q14 Q16 Q18 Q20 Q22 Q24">
     <cfRule type="cellIs" dxfId="22" priority="23" stopIfTrue="1" operator="greaterThan">
@@ -16080,18 +16057,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="B1" s="175">
+      <c r="B1" s="174">
         <f>+'[1]01'!B1:J1</f>
         <v>46174</v>
       </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="127">
@@ -16102,46 +16079,46 @@
     <row r="3" spans="1:10" ht="15" customHeight="1">
       <c r="A3" s="128"/>
       <c r="B3" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="E3" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="F3" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="G3" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="129" t="s">
+      <c r="H3" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="129" t="s">
+      <c r="I3" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="129" t="s">
+      <c r="J3" s="129" t="s">
         <v>89</v>
-      </c>
-      <c r="I3" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J3" s="129" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="128"/>
-      <c r="B4" s="173">
+      <c r="B4" s="176">
         <v>0.01</v>
       </c>
-      <c r="C4" s="174" t="s">
-        <v>92</v>
+      <c r="C4" s="177" t="s">
+        <v>90</v>
       </c>
       <c r="D4" s="130">
         <v>1</v>
       </c>
       <c r="E4" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F4" s="131"/>
       <c r="G4" s="132">
@@ -16163,13 +16140,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="128"/>
-      <c r="B5" s="173"/>
-      <c r="C5" s="174"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="177"/>
       <c r="D5" s="130">
         <v>2</v>
       </c>
       <c r="E5" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F5" s="131">
         <v>5</v>
@@ -16193,13 +16170,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="128"/>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="177"/>
       <c r="D6" s="130">
         <v>3</v>
       </c>
       <c r="E6" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F6" s="131">
         <v>14</v>
@@ -16223,13 +16200,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="135"/>
-      <c r="B7" s="174"/>
-      <c r="C7" s="174"/>
+      <c r="B7" s="177"/>
+      <c r="C7" s="177"/>
       <c r="D7" s="130">
         <v>4</v>
       </c>
       <c r="E7" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F7" s="131"/>
       <c r="G7" s="132">
@@ -16251,13 +16228,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="135"/>
-      <c r="B8" s="174"/>
-      <c r="C8" s="174"/>
+      <c r="B8" s="177"/>
+      <c r="C8" s="177"/>
       <c r="D8" s="130">
         <v>5</v>
       </c>
       <c r="E8" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F8" s="131">
         <v>6</v>
@@ -16281,13 +16258,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="135"/>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
+      <c r="B9" s="177"/>
+      <c r="C9" s="177"/>
       <c r="D9" s="130">
         <v>6</v>
       </c>
       <c r="E9" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F9" s="131"/>
       <c r="G9" s="132">
@@ -16309,10 +16286,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="135"/>
-      <c r="D10" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="172"/>
+      <c r="D10" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="178"/>
       <c r="F10" s="136">
         <f>SUM(F4:F9)</f>
         <v>25</v>
@@ -16341,46 +16318,46 @@
     <row r="12" spans="1:10">
       <c r="A12" s="135"/>
       <c r="B12" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="129" t="s">
+      <c r="E12" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="129" t="s">
+      <c r="F12" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="129" t="s">
+      <c r="G12" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="129" t="s">
+      <c r="H12" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G12" s="129" t="s">
+      <c r="I12" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="129" t="s">
+      <c r="J12" s="129" t="s">
         <v>89</v>
-      </c>
-      <c r="I12" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="129" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="135"/>
-      <c r="B13" s="173">
+      <c r="B13" s="176">
         <v>0.01</v>
       </c>
-      <c r="C13" s="174" t="s">
-        <v>100</v>
+      <c r="C13" s="177" t="s">
+        <v>98</v>
       </c>
       <c r="D13" s="130">
         <v>1</v>
       </c>
       <c r="E13" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F13" s="131"/>
       <c r="G13" s="132"/>
@@ -16399,13 +16376,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="135"/>
-      <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="177"/>
       <c r="D14" s="130">
         <v>2</v>
       </c>
       <c r="E14" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F14" s="131"/>
       <c r="G14" s="132">
@@ -16427,13 +16404,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="135"/>
-      <c r="B15" s="174"/>
-      <c r="C15" s="174"/>
+      <c r="B15" s="177"/>
+      <c r="C15" s="177"/>
       <c r="D15" s="130">
         <v>2</v>
       </c>
       <c r="E15" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F15" s="131">
         <v>1</v>
@@ -16457,13 +16434,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="135"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
+      <c r="B16" s="177"/>
+      <c r="C16" s="177"/>
       <c r="D16" s="130">
         <v>3</v>
       </c>
       <c r="E16" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F16" s="131"/>
       <c r="G16" s="132">
@@ -16485,13 +16462,13 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="135"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="177"/>
       <c r="D17" s="130">
         <v>4</v>
       </c>
       <c r="E17" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F17" s="131">
         <v>5</v>
@@ -16515,13 +16492,13 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="135"/>
-      <c r="B18" s="174"/>
-      <c r="C18" s="174"/>
+      <c r="B18" s="177"/>
+      <c r="C18" s="177"/>
       <c r="D18" s="130">
         <v>5</v>
       </c>
       <c r="E18" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F18" s="131"/>
       <c r="G18" s="132">
@@ -16543,10 +16520,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="135"/>
-      <c r="D19" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E19" s="172"/>
+      <c r="D19" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="178"/>
       <c r="F19" s="138">
         <f>SUM(F13:F18)</f>
         <v>6</v>
@@ -16573,45 +16550,45 @@
     </row>
     <row r="21" spans="1:10">
       <c r="B21" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="129" t="s">
+      <c r="E21" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="F21" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="129" t="s">
+      <c r="G21" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="129" t="s">
+      <c r="H21" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="129" t="s">
+      <c r="I21" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="129" t="s">
+      <c r="J21" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J21" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="B22" s="173">
+      <c r="B22" s="176">
         <v>0.01</v>
       </c>
-      <c r="C22" s="174" t="s">
-        <v>101</v>
+      <c r="C22" s="177" t="s">
+        <v>99</v>
       </c>
       <c r="D22" s="130">
         <v>1</v>
       </c>
       <c r="E22" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F22" s="131"/>
       <c r="G22" s="132"/>
@@ -16629,13 +16606,13 @@
       </c>
     </row>
     <row r="23" spans="1:10">
-      <c r="B23" s="173"/>
-      <c r="C23" s="174"/>
+      <c r="B23" s="176"/>
+      <c r="C23" s="177"/>
       <c r="D23" s="130">
         <v>2</v>
       </c>
       <c r="E23" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F23" s="131"/>
       <c r="G23" s="132">
@@ -16656,13 +16633,13 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="B24" s="174"/>
-      <c r="C24" s="174"/>
+      <c r="B24" s="177"/>
+      <c r="C24" s="177"/>
       <c r="D24" s="130">
         <v>2</v>
       </c>
       <c r="E24" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F24" s="131">
         <v>6</v>
@@ -16685,13 +16662,13 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="B25" s="174"/>
-      <c r="C25" s="174"/>
+      <c r="B25" s="177"/>
+      <c r="C25" s="177"/>
       <c r="D25" s="130">
         <v>3</v>
       </c>
       <c r="E25" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F25" s="131"/>
       <c r="G25" s="132">
@@ -16712,13 +16689,13 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="B26" s="174"/>
-      <c r="C26" s="174"/>
+      <c r="B26" s="177"/>
+      <c r="C26" s="177"/>
       <c r="D26" s="130">
         <v>4</v>
       </c>
       <c r="E26" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F26" s="131"/>
       <c r="G26" s="132">
@@ -16739,13 +16716,13 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="B27" s="174"/>
-      <c r="C27" s="174"/>
+      <c r="B27" s="177"/>
+      <c r="C27" s="177"/>
       <c r="D27" s="130">
         <v>5</v>
       </c>
       <c r="E27" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F27" s="131"/>
       <c r="G27" s="132">
@@ -16766,10 +16743,10 @@
       </c>
     </row>
     <row r="28" spans="1:10">
-      <c r="D28" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="172"/>
+      <c r="D28" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="178"/>
       <c r="F28" s="138">
         <f>SUM(F22:F27)</f>
         <v>6</v>
@@ -16796,45 +16773,45 @@
     </row>
     <row r="30" spans="1:10">
       <c r="B30" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="129" t="s">
+      <c r="E30" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="129" t="s">
+      <c r="F30" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E30" s="129" t="s">
+      <c r="G30" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F30" s="129" t="s">
+      <c r="H30" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="129" t="s">
+      <c r="I30" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H30" s="129" t="s">
+      <c r="J30" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J30" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="B31" s="173">
+      <c r="B31" s="176">
         <v>0.01</v>
       </c>
-      <c r="C31" s="174" t="s">
-        <v>103</v>
+      <c r="C31" s="177" t="s">
+        <v>101</v>
       </c>
       <c r="D31" s="130">
         <v>1</v>
       </c>
       <c r="E31" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F31" s="131"/>
       <c r="G31" s="132">
@@ -16854,13 +16831,13 @@
       </c>
     </row>
     <row r="32" spans="1:10">
-      <c r="B32" s="173"/>
-      <c r="C32" s="174"/>
+      <c r="B32" s="176"/>
+      <c r="C32" s="177"/>
       <c r="D32" s="130">
         <v>2</v>
       </c>
       <c r="E32" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F32" s="131">
         <v>114</v>
@@ -16883,13 +16860,13 @@
       </c>
     </row>
     <row r="33" spans="2:10">
-      <c r="B33" s="174"/>
-      <c r="C33" s="174"/>
+      <c r="B33" s="177"/>
+      <c r="C33" s="177"/>
       <c r="D33" s="130">
         <v>2</v>
       </c>
       <c r="E33" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F33" s="131">
         <v>140</v>
@@ -16912,13 +16889,13 @@
       </c>
     </row>
     <row r="34" spans="2:10">
-      <c r="B34" s="174"/>
-      <c r="C34" s="174"/>
+      <c r="B34" s="177"/>
+      <c r="C34" s="177"/>
       <c r="D34" s="130">
         <v>3</v>
       </c>
       <c r="E34" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F34" s="131"/>
       <c r="G34" s="132">
@@ -16939,13 +16916,13 @@
       </c>
     </row>
     <row r="35" spans="2:10">
-      <c r="B35" s="174"/>
-      <c r="C35" s="174"/>
+      <c r="B35" s="177"/>
+      <c r="C35" s="177"/>
       <c r="D35" s="130">
         <v>4</v>
       </c>
       <c r="E35" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F35" s="131">
         <v>433</v>
@@ -16968,13 +16945,13 @@
       </c>
     </row>
     <row r="36" spans="2:10">
-      <c r="B36" s="174"/>
-      <c r="C36" s="174"/>
+      <c r="B36" s="177"/>
+      <c r="C36" s="177"/>
       <c r="D36" s="130">
         <v>5</v>
       </c>
       <c r="E36" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F36" s="131"/>
       <c r="G36" s="132">
@@ -16995,10 +16972,10 @@
       </c>
     </row>
     <row r="37" spans="2:10">
-      <c r="D37" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" s="172"/>
+      <c r="D37" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37" s="178"/>
       <c r="F37" s="138">
         <f>SUM(F31:F36)</f>
         <v>687</v>
@@ -17025,45 +17002,45 @@
     </row>
     <row r="39" spans="2:10">
       <c r="B39" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="129" t="s">
+      <c r="E39" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="129" t="s">
+      <c r="F39" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E39" s="129" t="s">
+      <c r="G39" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="129" t="s">
+      <c r="H39" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="129" t="s">
+      <c r="I39" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="129" t="s">
+      <c r="J39" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I39" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J39" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="40" spans="2:10">
-      <c r="B40" s="173">
+      <c r="B40" s="176">
         <v>0.01</v>
       </c>
-      <c r="C40" s="174" t="s">
-        <v>104</v>
+      <c r="C40" s="177" t="s">
+        <v>102</v>
       </c>
       <c r="D40" s="130">
         <v>1</v>
       </c>
       <c r="E40" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F40" s="131"/>
       <c r="G40" s="132"/>
@@ -17081,13 +17058,13 @@
       </c>
     </row>
     <row r="41" spans="2:10">
-      <c r="B41" s="173"/>
-      <c r="C41" s="174"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="177"/>
       <c r="D41" s="130">
         <v>2</v>
       </c>
       <c r="E41" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F41" s="131"/>
       <c r="G41" s="132">
@@ -17108,13 +17085,13 @@
       </c>
     </row>
     <row r="42" spans="2:10">
-      <c r="B42" s="174"/>
-      <c r="C42" s="174"/>
+      <c r="B42" s="177"/>
+      <c r="C42" s="177"/>
       <c r="D42" s="130">
         <v>2</v>
       </c>
       <c r="E42" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F42" s="131">
         <v>6</v>
@@ -17137,13 +17114,13 @@
       </c>
     </row>
     <row r="43" spans="2:10">
-      <c r="B43" s="174"/>
-      <c r="C43" s="174"/>
+      <c r="B43" s="177"/>
+      <c r="C43" s="177"/>
       <c r="D43" s="130">
         <v>3</v>
       </c>
       <c r="E43" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F43" s="131"/>
       <c r="G43" s="132">
@@ -17164,13 +17141,13 @@
       </c>
     </row>
     <row r="44" spans="2:10">
-      <c r="B44" s="174"/>
-      <c r="C44" s="174"/>
+      <c r="B44" s="177"/>
+      <c r="C44" s="177"/>
       <c r="D44" s="130">
         <v>4</v>
       </c>
       <c r="E44" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F44" s="131"/>
       <c r="G44" s="132">
@@ -17191,13 +17168,13 @@
       </c>
     </row>
     <row r="45" spans="2:10">
-      <c r="B45" s="174"/>
-      <c r="C45" s="174"/>
+      <c r="B45" s="177"/>
+      <c r="C45" s="177"/>
       <c r="D45" s="130">
         <v>5</v>
       </c>
       <c r="E45" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F45" s="131"/>
       <c r="G45" s="132">
@@ -17218,10 +17195,10 @@
       </c>
     </row>
     <row r="46" spans="2:10">
-      <c r="D46" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E46" s="172"/>
+      <c r="D46" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="178"/>
       <c r="F46" s="138">
         <f>SUM(F40:F45)</f>
         <v>6</v>
@@ -17248,45 +17225,45 @@
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C48" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C48" s="129" t="s">
+      <c r="E48" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D48" s="129" t="s">
+      <c r="F48" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E48" s="129" t="s">
+      <c r="G48" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F48" s="129" t="s">
+      <c r="H48" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G48" s="129" t="s">
+      <c r="I48" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H48" s="129" t="s">
+      <c r="J48" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I48" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J48" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="49" spans="2:14">
-      <c r="B49" s="173">
+      <c r="B49" s="176">
         <v>0.01</v>
       </c>
-      <c r="C49" s="174" t="s">
-        <v>105</v>
+      <c r="C49" s="177" t="s">
+        <v>103</v>
       </c>
       <c r="D49" s="130">
         <v>1</v>
       </c>
       <c r="E49" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F49" s="131"/>
       <c r="G49" s="132"/>
@@ -17304,13 +17281,13 @@
       </c>
     </row>
     <row r="50" spans="2:14">
-      <c r="B50" s="173"/>
-      <c r="C50" s="174"/>
+      <c r="B50" s="176"/>
+      <c r="C50" s="177"/>
       <c r="D50" s="130">
         <v>2</v>
       </c>
       <c r="E50" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F50" s="131"/>
       <c r="G50" s="132">
@@ -17331,13 +17308,13 @@
       </c>
     </row>
     <row r="51" spans="2:14">
-      <c r="B51" s="174"/>
-      <c r="C51" s="174"/>
+      <c r="B51" s="177"/>
+      <c r="C51" s="177"/>
       <c r="D51" s="130">
         <v>2</v>
       </c>
       <c r="E51" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F51" s="131"/>
       <c r="G51" s="132">
@@ -17358,13 +17335,13 @@
       </c>
     </row>
     <row r="52" spans="2:14">
-      <c r="B52" s="174"/>
-      <c r="C52" s="174"/>
+      <c r="B52" s="177"/>
+      <c r="C52" s="177"/>
       <c r="D52" s="130">
         <v>3</v>
       </c>
       <c r="E52" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F52" s="139"/>
       <c r="G52" s="132">
@@ -17385,13 +17362,13 @@
       </c>
     </row>
     <row r="53" spans="2:14">
-      <c r="B53" s="174"/>
-      <c r="C53" s="174"/>
+      <c r="B53" s="177"/>
+      <c r="C53" s="177"/>
       <c r="D53" s="130">
         <v>4</v>
       </c>
       <c r="E53" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F53" s="131"/>
       <c r="G53" s="132">
@@ -17412,13 +17389,13 @@
       </c>
     </row>
     <row r="54" spans="2:14">
-      <c r="B54" s="174"/>
-      <c r="C54" s="174"/>
+      <c r="B54" s="177"/>
+      <c r="C54" s="177"/>
       <c r="D54" s="130">
         <v>5</v>
       </c>
       <c r="E54" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F54" s="131"/>
       <c r="G54" s="132">
@@ -17440,10 +17417,10 @@
       <c r="N54" s="140"/>
     </row>
     <row r="55" spans="2:14">
-      <c r="D55" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E55" s="172"/>
+      <c r="D55" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55" s="178"/>
       <c r="F55" s="138">
         <f>SUM(F49:F54)</f>
         <v>0</v>
@@ -17470,45 +17447,45 @@
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="129" t="s">
+      <c r="E57" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D57" s="129" t="s">
+      <c r="F57" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E57" s="129" t="s">
+      <c r="G57" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F57" s="129" t="s">
+      <c r="H57" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G57" s="129" t="s">
+      <c r="I57" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H57" s="129" t="s">
+      <c r="J57" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I57" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J57" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="58" spans="2:14">
-      <c r="B58" s="173">
+      <c r="B58" s="176">
         <v>0.01</v>
       </c>
-      <c r="C58" s="174" t="s">
-        <v>106</v>
+      <c r="C58" s="177" t="s">
+        <v>104</v>
       </c>
       <c r="D58" s="130">
         <v>1</v>
       </c>
       <c r="E58" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F58" s="131"/>
       <c r="G58" s="132"/>
@@ -17526,11 +17503,11 @@
       </c>
     </row>
     <row r="59" spans="2:14">
-      <c r="B59" s="173"/>
-      <c r="C59" s="174"/>
+      <c r="B59" s="176"/>
+      <c r="C59" s="177"/>
       <c r="D59" s="130"/>
       <c r="E59" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F59" s="131"/>
       <c r="G59" s="132">
@@ -17551,13 +17528,13 @@
       </c>
     </row>
     <row r="60" spans="2:14">
-      <c r="B60" s="174"/>
-      <c r="C60" s="174"/>
+      <c r="B60" s="177"/>
+      <c r="C60" s="177"/>
       <c r="D60" s="130">
         <v>2</v>
       </c>
       <c r="E60" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F60" s="131"/>
       <c r="G60" s="132">
@@ -17578,13 +17555,13 @@
       </c>
     </row>
     <row r="61" spans="2:14">
-      <c r="B61" s="174"/>
-      <c r="C61" s="174"/>
+      <c r="B61" s="177"/>
+      <c r="C61" s="177"/>
       <c r="D61" s="130">
         <v>3</v>
       </c>
       <c r="E61" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F61" s="131"/>
       <c r="G61" s="132">
@@ -17605,13 +17582,13 @@
       </c>
     </row>
     <row r="62" spans="2:14">
-      <c r="B62" s="174"/>
-      <c r="C62" s="174"/>
+      <c r="B62" s="177"/>
+      <c r="C62" s="177"/>
       <c r="D62" s="130">
         <v>4</v>
       </c>
       <c r="E62" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F62" s="131"/>
       <c r="G62" s="132">
@@ -17632,13 +17609,13 @@
       </c>
     </row>
     <row r="63" spans="2:14">
-      <c r="B63" s="174"/>
-      <c r="C63" s="174"/>
+      <c r="B63" s="177"/>
+      <c r="C63" s="177"/>
       <c r="D63" s="130">
         <v>5</v>
       </c>
       <c r="E63" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F63" s="131"/>
       <c r="G63" s="132">
@@ -17659,10 +17636,10 @@
       </c>
     </row>
     <row r="64" spans="2:14">
-      <c r="D64" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E64" s="172"/>
+      <c r="D64" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E64" s="178"/>
       <c r="F64" s="138">
         <f>SUM(F58:F63)</f>
         <v>0</v>
@@ -17689,45 +17666,45 @@
     </row>
     <row r="66" spans="2:10">
       <c r="B66" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C66" s="129" t="s">
+      <c r="E66" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D66" s="129" t="s">
+      <c r="F66" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E66" s="129" t="s">
+      <c r="G66" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F66" s="129" t="s">
+      <c r="H66" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G66" s="129" t="s">
+      <c r="I66" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H66" s="129" t="s">
+      <c r="J66" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I66" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J66" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="67" spans="2:10">
-      <c r="B67" s="173">
+      <c r="B67" s="176">
         <v>0.01</v>
       </c>
-      <c r="C67" s="174" t="s">
-        <v>107</v>
+      <c r="C67" s="177" t="s">
+        <v>105</v>
       </c>
       <c r="D67" s="130">
         <v>1</v>
       </c>
       <c r="E67" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F67" s="131"/>
       <c r="G67" s="141"/>
@@ -17745,13 +17722,13 @@
       </c>
     </row>
     <row r="68" spans="2:10">
-      <c r="B68" s="173"/>
-      <c r="C68" s="174"/>
+      <c r="B68" s="176"/>
+      <c r="C68" s="177"/>
       <c r="D68" s="130">
         <v>2</v>
       </c>
       <c r="E68" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F68" s="131"/>
       <c r="G68" s="141">
@@ -17772,13 +17749,13 @@
       </c>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="174"/>
-      <c r="C69" s="174"/>
+      <c r="B69" s="177"/>
+      <c r="C69" s="177"/>
       <c r="D69" s="130">
         <v>3</v>
       </c>
       <c r="E69" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F69" s="131"/>
       <c r="G69" s="141">
@@ -17799,13 +17776,13 @@
       </c>
     </row>
     <row r="70" spans="2:10">
-      <c r="B70" s="174"/>
-      <c r="C70" s="174"/>
+      <c r="B70" s="177"/>
+      <c r="C70" s="177"/>
       <c r="D70" s="130">
         <v>4</v>
       </c>
       <c r="E70" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F70" s="131"/>
       <c r="G70" s="141">
@@ -17826,13 +17803,13 @@
       </c>
     </row>
     <row r="71" spans="2:10">
-      <c r="B71" s="174"/>
-      <c r="C71" s="174"/>
+      <c r="B71" s="177"/>
+      <c r="C71" s="177"/>
       <c r="D71" s="130">
         <v>5</v>
       </c>
       <c r="E71" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F71" s="139"/>
       <c r="G71" s="141">
@@ -17853,13 +17830,13 @@
       </c>
     </row>
     <row r="72" spans="2:10">
-      <c r="B72" s="174"/>
-      <c r="C72" s="174"/>
+      <c r="B72" s="177"/>
+      <c r="C72" s="177"/>
       <c r="D72" s="130">
         <v>6</v>
       </c>
       <c r="E72" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F72" s="131"/>
       <c r="G72" s="141">
@@ -17880,10 +17857,10 @@
       </c>
     </row>
     <row r="73" spans="2:10">
-      <c r="D73" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E73" s="172"/>
+      <c r="D73" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E73" s="178"/>
       <c r="F73" s="138">
         <f>SUM(F67:F72)</f>
         <v>0</v>
@@ -17907,45 +17884,45 @@
     </row>
     <row r="75" spans="2:10">
       <c r="B75" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="C75" s="129" t="s">
+      <c r="E75" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="D75" s="129" t="s">
+      <c r="F75" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E75" s="129" t="s">
+      <c r="G75" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="F75" s="129" t="s">
+      <c r="H75" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="G75" s="129" t="s">
+      <c r="I75" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="H75" s="129" t="s">
+      <c r="J75" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="I75" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="J75" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="76" spans="2:10">
-      <c r="B76" s="173">
+      <c r="B76" s="176">
         <v>0.01</v>
       </c>
-      <c r="C76" s="174" t="s">
-        <v>108</v>
+      <c r="C76" s="177" t="s">
+        <v>106</v>
       </c>
       <c r="D76" s="130">
         <v>1</v>
       </c>
       <c r="E76" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F76" s="139"/>
       <c r="G76" s="143">
@@ -17965,13 +17942,13 @@
       </c>
     </row>
     <row r="77" spans="2:10">
-      <c r="B77" s="173"/>
-      <c r="C77" s="174"/>
+      <c r="B77" s="176"/>
+      <c r="C77" s="177"/>
       <c r="D77" s="130">
         <v>2</v>
       </c>
       <c r="E77" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F77" s="131">
         <v>1.8</v>
@@ -17994,13 +17971,13 @@
       </c>
     </row>
     <row r="78" spans="2:10">
-      <c r="B78" s="174"/>
-      <c r="C78" s="174"/>
+      <c r="B78" s="177"/>
+      <c r="C78" s="177"/>
       <c r="D78" s="130">
         <v>3</v>
       </c>
       <c r="E78" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F78" s="131">
         <v>6.75</v>
@@ -18023,13 +18000,13 @@
       </c>
     </row>
     <row r="79" spans="2:10">
-      <c r="B79" s="174"/>
-      <c r="C79" s="174"/>
+      <c r="B79" s="177"/>
+      <c r="C79" s="177"/>
       <c r="D79" s="130">
         <v>4</v>
       </c>
       <c r="E79" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F79" s="131"/>
       <c r="G79" s="143">
@@ -18050,13 +18027,13 @@
       </c>
     </row>
     <row r="80" spans="2:10">
-      <c r="B80" s="174"/>
-      <c r="C80" s="174"/>
+      <c r="B80" s="177"/>
+      <c r="C80" s="177"/>
       <c r="D80" s="130">
         <v>5</v>
       </c>
       <c r="E80" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F80" s="131"/>
       <c r="G80" s="143">
@@ -18077,13 +18054,13 @@
       </c>
     </row>
     <row r="81" spans="2:10">
-      <c r="B81" s="174"/>
-      <c r="C81" s="174"/>
+      <c r="B81" s="177"/>
+      <c r="C81" s="177"/>
       <c r="D81" s="130">
         <v>6</v>
       </c>
       <c r="E81" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F81" s="131"/>
       <c r="G81" s="132">
@@ -18104,10 +18081,10 @@
       </c>
     </row>
     <row r="82" spans="2:10">
-      <c r="D82" s="172" t="s">
-        <v>99</v>
-      </c>
-      <c r="E82" s="172"/>
+      <c r="D82" s="178" t="s">
+        <v>97</v>
+      </c>
+      <c r="E82" s="178"/>
       <c r="F82" s="138">
         <f>SUM(F76:F81)</f>
         <v>8.5500000000000007</v>
@@ -18131,24 +18108,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C4:C9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C40:C45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="C49:C54"/>
     <mergeCell ref="D73:E73"/>
     <mergeCell ref="B76:B81"/>
     <mergeCell ref="C76:C81"/>
@@ -18159,6 +18118,24 @@
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="B67:B72"/>
     <mergeCell ref="C67:C72"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C40:C45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C49:C54"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C4:C9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18496,59 +18473,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
-      <c r="A1" s="185" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
+      <c r="A1" s="179" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B3" s="129" t="s">
+      <c r="D3" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="129" t="s">
+      <c r="E3" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="F3" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="G3" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="129" t="s">
+      <c r="H3" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="129" t="s">
+      <c r="I3" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="129" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1">
+      <c r="A4" s="180">
+        <v>0.01</v>
+      </c>
+      <c r="B4" s="183" t="s">
         <v>90</v>
-      </c>
-      <c r="I3" s="129" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="179">
-        <v>0.01</v>
-      </c>
-      <c r="B4" s="182" t="s">
-        <v>92</v>
       </c>
       <c r="C4" s="130">
         <v>1</v>
       </c>
       <c r="D4" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E4" s="144">
         <f>+'[1]01'!F4+'[1]02'!F4+'[1]03'!F4+'[1]04'!F4+'[1]05'!F4+'[1]06'!F4+'[1]07'!F4+'[1]08'!F4+'[1]09'!F4+'[1]10'!F4+'[1]11'!F4+'[1]12'!F4+'[1]13'!F4+'[1]14'!F4+'[1]15'!F4+'[1]16'!F4+'[1]17'!F4+'[1]18'!F4+'[1]19'!F4+'[1]20'!F4+'[1]21'!F4+'[1]22'!F4+'[1]23'!F4+'[1]24'!F4+'[1]25'!F4+'[1]26'!F4+'[1]27'!F4+'[1]28'!F4+'[1]29'!F4+'[1]30'!F4+'[1]31'!F4</f>
@@ -18572,13 +18549,13 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5">
-      <c r="A5" s="180"/>
-      <c r="B5" s="183"/>
+      <c r="A5" s="181"/>
+      <c r="B5" s="184"/>
       <c r="C5" s="130">
         <v>2</v>
       </c>
       <c r="D5" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" s="144">
         <f>+'[1]01'!F5+'[1]02'!F5+'[1]03'!F5+'[1]04'!F5+'[1]05'!F5+'[1]06'!F5+'[1]07'!F5+'[1]08'!F5+'[1]09'!F5+'[1]10'!F5+'[1]11'!F5+'[1]12'!F5+'[1]13'!F5+'[1]14'!F5+'[1]15'!F5+'[1]16'!F5+'[1]17'!F5+'[1]18'!F5+'[1]19'!F5+'[1]20'!F5+'[1]21'!F5+'[1]22'!F5+'[1]23'!F5+'[1]24'!F5+'[1]25'!F5+'[1]26'!F5+'[1]27'!F5+'[1]28'!F5+'[1]29'!F5+'[1]30'!F5+'[1]31'!F5</f>
@@ -18602,13 +18579,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5">
-      <c r="A6" s="180"/>
-      <c r="B6" s="183"/>
+      <c r="A6" s="181"/>
+      <c r="B6" s="184"/>
       <c r="C6" s="130">
         <v>3</v>
       </c>
       <c r="D6" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6" s="144">
         <f>+'[1]01'!F6+'[1]02'!F6+'[1]03'!F6+'[1]04'!F6+'[1]05'!F6+'[1]06'!F6+'[1]07'!F6+'[1]08'!F6+'[1]09'!F6+'[1]10'!F6+'[1]11'!F6+'[1]12'!F6+'[1]13'!F6+'[1]14'!F6+'[1]15'!F6+'[1]16'!F6+'[1]17'!F6+'[1]18'!F6+'[1]19'!F6+'[1]20'!F6+'[1]21'!F6+'[1]22'!F6+'[1]23'!F6+'[1]24'!F6+'[1]25'!F6+'[1]26'!F6+'[1]27'!F6+'[1]28'!F6+'[1]29'!F6+'[1]30'!F6+'[1]31'!F6</f>
@@ -18632,13 +18609,13 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5">
-      <c r="A7" s="180"/>
-      <c r="B7" s="183"/>
+      <c r="A7" s="181"/>
+      <c r="B7" s="184"/>
       <c r="C7" s="130">
         <v>4</v>
       </c>
       <c r="D7" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" s="144">
         <f>+'[1]01'!F7+'[1]02'!F7+'[1]03'!F7+'[1]04'!F7+'[1]05'!F7+'[1]06'!F7+'[1]07'!F7+'[1]08'!F7+'[1]09'!F7+'[1]10'!F7+'[1]11'!F7+'[1]12'!F7+'[1]13'!F7+'[1]14'!F7+'[1]15'!F7+'[1]16'!F7+'[1]17'!F7+'[1]18'!F7+'[1]19'!F7+'[1]20'!F7+'[1]21'!F7+'[1]22'!F7+'[1]23'!F7+'[1]24'!F7+'[1]25'!F7+'[1]26'!F7+'[1]27'!F7+'[1]28'!F7+'[1]29'!F7+'[1]30'!F7+'[1]31'!F7</f>
@@ -18662,13 +18639,13 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5">
-      <c r="A8" s="180"/>
-      <c r="B8" s="183"/>
+      <c r="A8" s="181"/>
+      <c r="B8" s="184"/>
       <c r="C8" s="130">
         <v>5</v>
       </c>
       <c r="D8" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E8" s="144">
         <f>+'[1]01'!F8+'[1]02'!F8+'[1]03'!F8+'[1]04'!F8+'[1]05'!F8+'[1]06'!F8+'[1]07'!F8+'[1]08'!F8+'[1]09'!F8+'[1]10'!F8+'[1]11'!F8+'[1]12'!F8+'[1]13'!F8+'[1]14'!F8+'[1]15'!F8+'[1]16'!F8+'[1]17'!F8+'[1]18'!F8+'[1]19'!F8+'[1]20'!F8+'[1]21'!F8+'[1]22'!F8+'[1]23'!F8+'[1]24'!F8+'[1]25'!F8+'[1]26'!F8+'[1]27'!F8+'[1]28'!F8+'[1]29'!F8+'[1]30'!F8+'[1]31'!F8</f>
@@ -18692,13 +18669,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
-      <c r="A9" s="181"/>
-      <c r="B9" s="184"/>
+      <c r="A9" s="182"/>
+      <c r="B9" s="185"/>
       <c r="C9" s="130">
         <v>6</v>
       </c>
       <c r="D9" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E9" s="144">
         <f>+'[1]01'!F9+'[1]02'!F9+'[1]03'!F9+'[1]04'!F9+'[1]05'!F9+'[1]06'!F9+'[1]07'!F9+'[1]08'!F9+'[1]09'!F9+'[1]10'!F9+'[1]11'!F9+'[1]12'!F9+'[1]13'!F9+'[1]14'!F9+'[1]15'!F9+'[1]16'!F9+'[1]17'!F9+'[1]18'!F9+'[1]19'!F9+'[1]20'!F9+'[1]21'!F9+'[1]22'!F9+'[1]23'!F9+'[1]24'!F9+'[1]25'!F9+'[1]26'!F9+'[1]27'!F9+'[1]28'!F9+'[1]29'!F9+'[1]30'!F9+'[1]31'!F9</f>
@@ -18724,10 +18701,10 @@
     <row r="10" spans="1:9" ht="16.5">
       <c r="A10" s="126"/>
       <c r="B10" s="126"/>
-      <c r="C10" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="178"/>
+      <c r="C10" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="187"/>
       <c r="E10" s="146">
         <f>SUM(E4:E9)</f>
         <v>306</v>
@@ -18762,45 +18739,45 @@
     </row>
     <row r="12" spans="1:9" s="147" customFormat="1">
       <c r="A12" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="129" t="s">
+      <c r="D12" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="129" t="s">
+      <c r="E12" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="129" t="s">
+      <c r="F12" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E12" s="129" t="s">
+      <c r="G12" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="129" t="s">
+      <c r="H12" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="129" t="s">
+      <c r="I12" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="13" spans="1:9" ht="16.5">
-      <c r="A13" s="179">
+      <c r="A13" s="180">
         <v>0.01</v>
       </c>
-      <c r="B13" s="182" t="s">
-        <v>100</v>
+      <c r="B13" s="183" t="s">
+        <v>98</v>
       </c>
       <c r="C13" s="130">
         <v>1</v>
       </c>
       <c r="D13" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E13" s="144">
         <f>+'[1]01'!F13+'[1]02'!F13+'[1]03'!F13+'[1]04'!F13+'[1]05'!F13+'[1]06'!F13+'[1]07'!F13+'[1]08'!F13+'[1]09'!F13+'[1]10'!F13+'[1]11'!F13+'[1]12'!F13+'[1]13'!F13+'[1]14'!F13+'[1]15'!F13+'[1]16'!F13+'[1]17'!F13+'[1]18'!F13+'[1]19'!F13+'[1]20'!F13+'[1]21'!F13+'[1]22'!F13+'[1]23'!F13+'[1]24'!F13+'[1]25'!F13+'[1]26'!F13+'[1]27'!F13+'[1]28'!F13+'[1]29'!F13+'[1]30'!F13+'[1]31'!F13</f>
@@ -18824,13 +18801,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5">
-      <c r="A14" s="180"/>
-      <c r="B14" s="183"/>
+      <c r="A14" s="181"/>
+      <c r="B14" s="184"/>
       <c r="C14" s="130">
         <v>2</v>
       </c>
       <c r="D14" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E14" s="144">
         <f>+'[1]01'!F14+'[1]02'!F14+'[1]03'!F14+'[1]04'!F14+'[1]05'!F14+'[1]06'!F14+'[1]07'!F14+'[1]08'!F14+'[1]09'!F14+'[1]10'!F14+'[1]11'!F14+'[1]12'!F14+'[1]13'!F14+'[1]14'!F14+'[1]15'!F14+'[1]16'!F14+'[1]17'!F14+'[1]18'!F14+'[1]19'!F14+'[1]20'!F14+'[1]21'!F14+'[1]22'!F14+'[1]23'!F14+'[1]24'!F14+'[1]25'!F14+'[1]26'!F14+'[1]27'!F14+'[1]28'!F14+'[1]29'!F14+'[1]30'!F14+'[1]31'!F14</f>
@@ -18854,13 +18831,13 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="16.5">
-      <c r="A15" s="180"/>
-      <c r="B15" s="183"/>
+      <c r="A15" s="181"/>
+      <c r="B15" s="184"/>
       <c r="C15" s="130">
         <v>2</v>
       </c>
       <c r="D15" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E15" s="144">
         <f>+'[1]01'!F15+'[1]02'!F15+'[1]03'!F15+'[1]04'!F15+'[1]05'!F15+'[1]06'!F15+'[1]07'!F15+'[1]08'!F15+'[1]09'!F15+'[1]10'!F15+'[1]11'!F15+'[1]12'!F15+'[1]13'!F15+'[1]14'!F15+'[1]15'!F15+'[1]16'!F15+'[1]17'!F15+'[1]18'!F15+'[1]19'!F15+'[1]20'!F15+'[1]21'!F15+'[1]22'!F15+'[1]23'!F15+'[1]24'!F15+'[1]25'!F15+'[1]26'!F15+'[1]27'!F15+'[1]28'!F15+'[1]29'!F15+'[1]30'!F15+'[1]31'!F15</f>
@@ -18884,13 +18861,13 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5">
-      <c r="A16" s="180"/>
-      <c r="B16" s="183"/>
+      <c r="A16" s="181"/>
+      <c r="B16" s="184"/>
       <c r="C16" s="130">
         <v>3</v>
       </c>
       <c r="D16" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16" s="144">
         <f>+'[1]01'!F16+'[1]02'!F16+'[1]03'!F16+'[1]04'!F16+'[1]05'!F16+'[1]06'!F16+'[1]07'!F16+'[1]08'!F16+'[1]09'!F16+'[1]10'!F16+'[1]11'!F16+'[1]12'!F16+'[1]13'!F16+'[1]14'!F16+'[1]15'!F16+'[1]16'!F16+'[1]17'!F16+'[1]18'!F16+'[1]19'!F16+'[1]20'!F16+'[1]21'!F16+'[1]22'!F16+'[1]23'!F16+'[1]24'!F16+'[1]25'!F16+'[1]26'!F16+'[1]27'!F16+'[1]28'!F16+'[1]29'!F16+'[1]30'!F16+'[1]31'!F16</f>
@@ -18914,13 +18891,13 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="16.5">
-      <c r="A17" s="180"/>
-      <c r="B17" s="183"/>
+      <c r="A17" s="181"/>
+      <c r="B17" s="184"/>
       <c r="C17" s="130">
         <v>4</v>
       </c>
       <c r="D17" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E17" s="144">
         <f>+'[1]01'!F17+'[1]02'!F17+'[1]03'!F17+'[1]04'!F17+'[1]05'!F17+'[1]06'!F17+'[1]07'!F17+'[1]08'!F17+'[1]09'!F17+'[1]10'!F17+'[1]11'!F17+'[1]12'!F17+'[1]13'!F17+'[1]14'!F17+'[1]15'!F17+'[1]16'!F17+'[1]17'!F17+'[1]18'!F17+'[1]19'!F17+'[1]20'!F17+'[1]21'!F17+'[1]22'!F17+'[1]23'!F17+'[1]24'!F17+'[1]25'!F17+'[1]26'!F17+'[1]27'!F17+'[1]28'!F17+'[1]29'!F17+'[1]30'!F17+'[1]31'!F17</f>
@@ -18944,13 +18921,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="16.5">
-      <c r="A18" s="181"/>
-      <c r="B18" s="184"/>
+      <c r="A18" s="182"/>
+      <c r="B18" s="185"/>
       <c r="C18" s="130">
         <v>5</v>
       </c>
       <c r="D18" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E18" s="144">
         <f>+'[1]01'!F18+'[1]02'!F18+'[1]03'!F18+'[1]04'!F18+'[1]05'!F18+'[1]06'!F18+'[1]07'!F18+'[1]08'!F18+'[1]09'!F18+'[1]10'!F18+'[1]11'!F18+'[1]12'!F18+'[1]13'!F18+'[1]14'!F18+'[1]15'!F18+'[1]16'!F18+'[1]17'!F18+'[1]18'!F18+'[1]19'!F18+'[1]20'!F18+'[1]21'!F18+'[1]22'!F18+'[1]23'!F18+'[1]24'!F18+'[1]25'!F18+'[1]26'!F18+'[1]27'!F18+'[1]28'!F18+'[1]29'!F18+'[1]30'!F18+'[1]31'!F18</f>
@@ -18976,10 +18953,10 @@
     <row r="19" spans="1:9" ht="16.5">
       <c r="A19" s="126"/>
       <c r="B19" s="126"/>
-      <c r="C19" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="178"/>
+      <c r="C19" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="187"/>
       <c r="E19" s="146">
         <f>SUM(E13:E18)</f>
         <v>474</v>
@@ -19014,45 +18991,45 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="129" t="s">
+      <c r="D21" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="129" t="s">
+      <c r="E21" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="129" t="s">
+      <c r="F21" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="129" t="s">
+      <c r="G21" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="129" t="s">
+      <c r="H21" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="129" t="s">
+      <c r="I21" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H21" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I21" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="22" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A22" s="179">
+      <c r="A22" s="180">
         <v>0.01</v>
       </c>
-      <c r="B22" s="182" t="s">
-        <v>101</v>
+      <c r="B22" s="183" t="s">
+        <v>99</v>
       </c>
       <c r="C22" s="130">
         <v>1</v>
       </c>
       <c r="D22" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E22" s="144">
         <f>+'[1]01'!F22+'[1]02'!F22+'[1]03'!F22+'[1]04'!F22+'[1]05'!F22+'[1]06'!F22+'[1]07'!F22+'[1]08'!F22+'[1]09'!F22+'[1]10'!F22+'[1]11'!F22+'[1]12'!F22+'[1]13'!F22+'[1]14'!F22+'[1]15'!F22+'[1]16'!F22+'[1]17'!F22+'[1]18'!F22+'[1]19'!F22+'[1]20'!F22+'[1]21'!F22+'[1]22'!F22+'[1]23'!F22+'[1]24'!F22+'[1]25'!F22+'[1]26'!F22+'[1]27'!F22+'[1]28'!F22+'[1]29'!F22+'[1]30'!F22+'[1]31'!F22</f>
@@ -19076,13 +19053,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="16.5">
-      <c r="A23" s="180"/>
-      <c r="B23" s="183"/>
+      <c r="A23" s="181"/>
+      <c r="B23" s="184"/>
       <c r="C23" s="130">
         <v>2</v>
       </c>
       <c r="D23" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" s="144">
         <f>+'[1]01'!F23+'[1]02'!F23+'[1]03'!F23+'[1]04'!F23+'[1]05'!F23+'[1]06'!F23+'[1]07'!F23+'[1]08'!F23+'[1]09'!F23+'[1]10'!F23+'[1]11'!F23+'[1]12'!F23+'[1]13'!F23+'[1]14'!F23+'[1]15'!F23+'[1]16'!F23+'[1]17'!F23+'[1]18'!F23+'[1]19'!F23+'[1]20'!F23+'[1]21'!F23+'[1]22'!F23+'[1]23'!F23+'[1]24'!F23+'[1]25'!F23+'[1]26'!F23+'[1]27'!F23+'[1]28'!F23+'[1]29'!F23+'[1]30'!F23+'[1]31'!F23</f>
@@ -19106,13 +19083,13 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="16.5">
-      <c r="A24" s="180"/>
-      <c r="B24" s="183"/>
+      <c r="A24" s="181"/>
+      <c r="B24" s="184"/>
       <c r="C24" s="130">
         <v>2</v>
       </c>
       <c r="D24" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E24" s="144">
         <f>+'[1]01'!F24+'[1]02'!F24+'[1]03'!F24+'[1]04'!F24+'[1]05'!F24+'[1]06'!F24+'[1]07'!F24+'[1]08'!F24+'[1]09'!F24+'[1]10'!F24+'[1]11'!F24+'[1]12'!F24+'[1]13'!F24+'[1]14'!F24+'[1]15'!F24+'[1]16'!F24+'[1]17'!F24+'[1]18'!F24+'[1]19'!F24+'[1]20'!F24+'[1]21'!F24+'[1]22'!F24+'[1]23'!F24+'[1]24'!F24+'[1]25'!F24+'[1]26'!F24+'[1]27'!F24+'[1]28'!F24+'[1]29'!F24+'[1]30'!F24+'[1]31'!F24</f>
@@ -19136,13 +19113,13 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="16.5">
-      <c r="A25" s="180"/>
-      <c r="B25" s="183"/>
+      <c r="A25" s="181"/>
+      <c r="B25" s="184"/>
       <c r="C25" s="130">
         <v>3</v>
       </c>
       <c r="D25" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E25" s="144">
         <f>+'[1]01'!F25+'[1]02'!F25+'[1]03'!F25+'[1]04'!F25+'[1]05'!F25+'[1]06'!F25+'[1]07'!F25+'[1]08'!F25+'[1]09'!F25+'[1]10'!F25+'[1]11'!F25+'[1]12'!F25+'[1]13'!F25+'[1]14'!F25+'[1]15'!F25+'[1]16'!F25+'[1]17'!F25+'[1]18'!F25+'[1]19'!F25+'[1]20'!F25+'[1]21'!F25+'[1]22'!F25+'[1]23'!F25+'[1]24'!F25+'[1]25'!F25+'[1]26'!F25+'[1]27'!F25+'[1]28'!F25+'[1]29'!F25+'[1]30'!F25+'[1]31'!F25</f>
@@ -19166,13 +19143,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="16.5">
-      <c r="A26" s="180"/>
-      <c r="B26" s="183"/>
+      <c r="A26" s="181"/>
+      <c r="B26" s="184"/>
       <c r="C26" s="130">
         <v>4</v>
       </c>
       <c r="D26" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E26" s="144">
         <f>+'[1]01'!F26+'[1]02'!F26+'[1]03'!F26+'[1]04'!F26+'[1]05'!F26+'[1]06'!F26+'[1]07'!F26+'[1]08'!F26+'[1]09'!F26+'[1]10'!F26+'[1]11'!F26+'[1]12'!F26+'[1]13'!F26+'[1]14'!F26+'[1]15'!F26+'[1]16'!F26+'[1]17'!F26+'[1]18'!F26+'[1]19'!F26+'[1]20'!F26+'[1]21'!F26+'[1]22'!F26+'[1]23'!F26+'[1]24'!F26+'[1]25'!F26+'[1]26'!F26+'[1]27'!F26+'[1]28'!F26+'[1]29'!F26+'[1]30'!F26+'[1]31'!F26</f>
@@ -19196,13 +19173,13 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="16.5">
-      <c r="A27" s="181"/>
-      <c r="B27" s="184"/>
+      <c r="A27" s="182"/>
+      <c r="B27" s="185"/>
       <c r="C27" s="130">
         <v>5</v>
       </c>
       <c r="D27" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E27" s="144">
         <f>+'[1]01'!F27+'[1]02'!F27+'[1]03'!F27+'[1]04'!F27+'[1]05'!F27+'[1]06'!F27+'[1]07'!F27+'[1]08'!F27+'[1]09'!F27+'[1]10'!F27+'[1]11'!F27+'[1]12'!F27+'[1]13'!F27+'[1]14'!F27+'[1]15'!F27+'[1]16'!F27+'[1]17'!F27+'[1]18'!F27+'[1]19'!F27+'[1]20'!F27+'[1]21'!F27+'[1]22'!F27+'[1]23'!F27+'[1]24'!F27+'[1]25'!F27+'[1]26'!F27+'[1]27'!F27+'[1]28'!F27+'[1]29'!F27+'[1]30'!F27+'[1]31'!F27</f>
@@ -19228,10 +19205,10 @@
     <row r="28" spans="1:9" ht="16.5">
       <c r="A28" s="126"/>
       <c r="B28" s="126"/>
-      <c r="C28" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="178"/>
+      <c r="C28" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="187"/>
       <c r="E28" s="146">
         <f>SUM(E22:E27)</f>
         <v>1855</v>
@@ -19266,45 +19243,45 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="129" t="s">
+      <c r="D30" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="129" t="s">
+      <c r="E30" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="129" t="s">
+      <c r="F30" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="129" t="s">
+      <c r="G30" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F30" s="129" t="s">
+      <c r="H30" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G30" s="129" t="s">
+      <c r="I30" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H30" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I30" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="31" spans="1:9" s="148" customFormat="1" ht="16.5">
-      <c r="A31" s="179">
+      <c r="A31" s="180">
         <v>0.01</v>
       </c>
-      <c r="B31" s="182" t="s">
-        <v>103</v>
+      <c r="B31" s="183" t="s">
+        <v>101</v>
       </c>
       <c r="C31" s="130">
         <v>1</v>
       </c>
       <c r="D31" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E31" s="144">
         <f>+'[1]01'!F31+'[1]02'!F31+'[1]03'!F31+'[1]04'!F31+'[1]05'!F31+'[1]06'!F31+'[1]07'!F31+'[1]08'!F31+'[1]09'!F31+'[1]10'!F31+'[1]11'!F31+'[1]12'!F31+'[1]13'!F31+'[1]14'!F31+'[1]15'!F31+'[1]16'!F31+'[1]17'!F31+'[1]18'!F31+'[1]19'!F31+'[1]20'!F31+'[1]21'!F31+'[1]22'!F31+'[1]23'!F31+'[1]24'!F31+'[1]25'!F31+'[1]26'!F31+'[1]27'!F31+'[1]28'!F31+'[1]29'!F31+'[1]30'!F31+'[1]31'!F31</f>
@@ -19328,13 +19305,13 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="16.5">
-      <c r="A32" s="180"/>
-      <c r="B32" s="183"/>
+      <c r="A32" s="181"/>
+      <c r="B32" s="184"/>
       <c r="C32" s="130">
         <v>2</v>
       </c>
       <c r="D32" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E32" s="144">
         <f>+'[1]01'!F32+'[1]02'!F32+'[1]03'!F32+'[1]04'!F32+'[1]05'!F32+'[1]06'!F32+'[1]07'!F32+'[1]08'!F32+'[1]09'!F32+'[1]10'!F32+'[1]11'!F32+'[1]12'!F32+'[1]13'!F32+'[1]14'!F32+'[1]15'!F32+'[1]16'!F32+'[1]17'!F32+'[1]18'!F32+'[1]19'!F32+'[1]20'!F32+'[1]21'!F32+'[1]22'!F32+'[1]23'!F32+'[1]24'!F32+'[1]25'!F32+'[1]26'!F32+'[1]27'!F32+'[1]28'!F32+'[1]29'!F32+'[1]30'!F32+'[1]31'!F32</f>
@@ -19358,13 +19335,13 @@
       </c>
     </row>
     <row r="33" spans="1:9" ht="16.5">
-      <c r="A33" s="180"/>
-      <c r="B33" s="183"/>
+      <c r="A33" s="181"/>
+      <c r="B33" s="184"/>
       <c r="C33" s="130">
         <v>2</v>
       </c>
       <c r="D33" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E33" s="144">
         <f>+'[1]01'!F33+'[1]02'!F33+'[1]03'!F33+'[1]04'!F33+'[1]05'!F33+'[1]06'!F33+'[1]07'!F33+'[1]08'!F33+'[1]09'!F33+'[1]10'!F33+'[1]11'!F33+'[1]12'!F33+'[1]13'!F33+'[1]14'!F33+'[1]15'!F33+'[1]16'!F33+'[1]17'!F33+'[1]18'!F33+'[1]19'!F33+'[1]20'!F33+'[1]21'!F33+'[1]22'!F33+'[1]23'!F33+'[1]24'!F33+'[1]25'!F33+'[1]26'!F33+'[1]27'!F33+'[1]28'!F33+'[1]29'!F33+'[1]30'!F33+'[1]31'!F33</f>
@@ -19388,13 +19365,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="16.5">
-      <c r="A34" s="180"/>
-      <c r="B34" s="183"/>
+      <c r="A34" s="181"/>
+      <c r="B34" s="184"/>
       <c r="C34" s="130">
         <v>3</v>
       </c>
       <c r="D34" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E34" s="144">
         <f>+'[1]01'!F34+'[1]02'!F34+'[1]03'!F34+'[1]04'!F34+'[1]05'!F34+'[1]06'!F34+'[1]07'!F34+'[1]08'!F34+'[1]09'!F34+'[1]10'!F34+'[1]11'!F34+'[1]12'!F34+'[1]13'!F34+'[1]14'!F34+'[1]15'!F34+'[1]16'!F34+'[1]17'!F34+'[1]18'!F34+'[1]19'!F34+'[1]20'!F34+'[1]21'!F34+'[1]22'!F34+'[1]23'!F34+'[1]24'!F34+'[1]25'!F34+'[1]26'!F34+'[1]27'!F34+'[1]28'!F34+'[1]29'!F34+'[1]30'!F34+'[1]31'!F34</f>
@@ -19418,13 +19395,13 @@
       </c>
     </row>
     <row r="35" spans="1:9" ht="16.5">
-      <c r="A35" s="180"/>
-      <c r="B35" s="183"/>
+      <c r="A35" s="181"/>
+      <c r="B35" s="184"/>
       <c r="C35" s="130">
         <v>4</v>
       </c>
       <c r="D35" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E35" s="144">
         <f>+'[1]01'!F35+'[1]02'!F35+'[1]03'!F35+'[1]04'!F35+'[1]05'!F35+'[1]06'!F35+'[1]07'!F35+'[1]08'!F35+'[1]09'!F35+'[1]10'!F35+'[1]11'!F35+'[1]12'!F35+'[1]13'!F35+'[1]14'!F35+'[1]15'!F35+'[1]16'!F35+'[1]17'!F35+'[1]18'!F35+'[1]19'!F35+'[1]20'!F35+'[1]21'!F35+'[1]22'!F35+'[1]23'!F35+'[1]24'!F35+'[1]25'!F35+'[1]26'!F35+'[1]27'!F35+'[1]28'!F35+'[1]29'!F35+'[1]30'!F35+'[1]31'!F35</f>
@@ -19448,13 +19425,13 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5">
-      <c r="A36" s="181"/>
-      <c r="B36" s="184"/>
+      <c r="A36" s="182"/>
+      <c r="B36" s="185"/>
       <c r="C36" s="130">
         <v>5</v>
       </c>
       <c r="D36" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E36" s="144">
         <f>+'[1]01'!F36+'[1]02'!F36+'[1]03'!F36+'[1]04'!F36+'[1]05'!F36+'[1]06'!F36+'[1]07'!F36+'[1]08'!F36+'[1]09'!F36+'[1]10'!F36+'[1]11'!F36+'[1]12'!F36+'[1]13'!F36+'[1]14'!F36+'[1]15'!F36+'[1]16'!F36+'[1]17'!F36+'[1]18'!F36+'[1]19'!F36+'[1]20'!F36+'[1]21'!F36+'[1]22'!F36+'[1]23'!F36+'[1]24'!F36+'[1]25'!F36+'[1]26'!F36+'[1]27'!F36+'[1]28'!F36+'[1]29'!F36+'[1]30'!F36+'[1]31'!F36</f>
@@ -19480,10 +19457,10 @@
     <row r="37" spans="1:9" ht="16.5">
       <c r="A37" s="126"/>
       <c r="B37" s="126"/>
-      <c r="C37" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="178"/>
+      <c r="C37" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="187"/>
       <c r="E37" s="146">
         <f>SUM(E31:E36)</f>
         <v>5270</v>
@@ -19518,45 +19495,45 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B39" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B39" s="129" t="s">
+      <c r="D39" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="129" t="s">
+      <c r="E39" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="129" t="s">
+      <c r="F39" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E39" s="129" t="s">
+      <c r="G39" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F39" s="129" t="s">
+      <c r="H39" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G39" s="129" t="s">
+      <c r="I39" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H39" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I39" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="40" spans="1:9" ht="16.5">
-      <c r="A40" s="179">
+      <c r="A40" s="180">
         <v>0.01</v>
       </c>
-      <c r="B40" s="182" t="s">
-        <v>104</v>
+      <c r="B40" s="183" t="s">
+        <v>102</v>
       </c>
       <c r="C40" s="130">
         <v>1</v>
       </c>
       <c r="D40" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E40" s="144">
         <f>+'[1]01'!F40+'[1]02'!F40+'[1]03'!F40+'[1]04'!F40+'[1]05'!F40+'[1]06'!F40+'[1]07'!F40+'[1]08'!F40+'[1]09'!F40+'[1]10'!F40+'[1]11'!F40+'[1]12'!F40+'[1]13'!F40+'[1]14'!F40+'[1]15'!F40+'[1]16'!F40+'[1]17'!F40+'[1]18'!F40+'[1]19'!F40+'[1]20'!F40+'[1]21'!F40+'[1]22'!F40+'[1]23'!F40+'[1]24'!F40+'[1]25'!F40+'[1]26'!F40+'[1]27'!F40+'[1]28'!F40+'[1]29'!F40+'[1]30'!F40+'[1]31'!F40</f>
@@ -19580,13 +19557,13 @@
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5">
-      <c r="A41" s="180"/>
-      <c r="B41" s="183"/>
+      <c r="A41" s="181"/>
+      <c r="B41" s="184"/>
       <c r="C41" s="130">
         <v>2</v>
       </c>
       <c r="D41" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E41" s="144">
         <f>+'[1]01'!F41+'[1]02'!F41+'[1]03'!F41+'[1]04'!F41+'[1]05'!F41+'[1]06'!F41+'[1]07'!F41+'[1]08'!F41+'[1]09'!F41+'[1]10'!F41+'[1]11'!F41+'[1]12'!F41+'[1]13'!F41+'[1]14'!F41+'[1]15'!F41+'[1]16'!F41+'[1]17'!F41+'[1]18'!F41+'[1]19'!F41+'[1]20'!F41+'[1]21'!F41+'[1]22'!F41+'[1]23'!F41+'[1]24'!F41+'[1]25'!F41+'[1]26'!F41+'[1]27'!F41+'[1]28'!F41+'[1]29'!F41+'[1]30'!F41+'[1]31'!F41</f>
@@ -19610,13 +19587,13 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="16.5">
-      <c r="A42" s="180"/>
-      <c r="B42" s="183"/>
+      <c r="A42" s="181"/>
+      <c r="B42" s="184"/>
       <c r="C42" s="130">
         <v>2</v>
       </c>
       <c r="D42" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E42" s="144">
         <f>+'[1]01'!F42+'[1]02'!F42+'[1]03'!F42+'[1]04'!F42+'[1]05'!F42+'[1]06'!F42+'[1]07'!F42+'[1]08'!F42+'[1]09'!F42+'[1]10'!F42+'[1]11'!F42+'[1]12'!F42+'[1]13'!F42+'[1]14'!F42+'[1]15'!F42+'[1]16'!F42+'[1]17'!F42+'[1]18'!F42+'[1]19'!F42+'[1]20'!F42+'[1]21'!F42+'[1]22'!F42+'[1]23'!F42+'[1]24'!F42+'[1]25'!F42+'[1]26'!F42+'[1]27'!F42+'[1]28'!F42+'[1]29'!F42+'[1]30'!F42+'[1]31'!F42</f>
@@ -19640,13 +19617,13 @@
       </c>
     </row>
     <row r="43" spans="1:9" ht="16.5">
-      <c r="A43" s="180"/>
-      <c r="B43" s="183"/>
+      <c r="A43" s="181"/>
+      <c r="B43" s="184"/>
       <c r="C43" s="130">
         <v>3</v>
       </c>
       <c r="D43" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E43" s="144">
         <f>+'[1]01'!F43+'[1]02'!F43+'[1]03'!F43+'[1]04'!F43+'[1]05'!F43+'[1]06'!F43+'[1]07'!F43+'[1]08'!F43+'[1]09'!F43+'[1]10'!F43+'[1]11'!F43+'[1]12'!F43+'[1]13'!F43+'[1]14'!F43+'[1]15'!F43+'[1]16'!F43+'[1]17'!F43+'[1]18'!F43+'[1]19'!F43+'[1]20'!F43+'[1]21'!F43+'[1]22'!F43+'[1]23'!F43+'[1]24'!F43+'[1]25'!F43+'[1]26'!F43+'[1]27'!F43+'[1]28'!F43+'[1]29'!F43+'[1]30'!F43+'[1]31'!F43</f>
@@ -19670,13 +19647,13 @@
       </c>
     </row>
     <row r="44" spans="1:9" ht="16.5">
-      <c r="A44" s="180"/>
-      <c r="B44" s="183"/>
+      <c r="A44" s="181"/>
+      <c r="B44" s="184"/>
       <c r="C44" s="130">
         <v>4</v>
       </c>
       <c r="D44" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E44" s="144">
         <f>+'[1]01'!F44+'[1]02'!F44+'[1]03'!F44+'[1]04'!F44+'[1]05'!F44+'[1]06'!F44+'[1]07'!F44+'[1]08'!F44+'[1]09'!F44+'[1]10'!F44+'[1]11'!F44+'[1]12'!F44+'[1]13'!F44+'[1]14'!F44+'[1]15'!F44+'[1]16'!F44+'[1]17'!F44+'[1]18'!F44+'[1]19'!F44+'[1]20'!F44+'[1]21'!F44+'[1]22'!F44+'[1]23'!F44+'[1]24'!F44+'[1]25'!F44+'[1]26'!F44+'[1]27'!F44+'[1]28'!F44+'[1]29'!F44+'[1]30'!F44+'[1]31'!F44</f>
@@ -19700,13 +19677,13 @@
       </c>
     </row>
     <row r="45" spans="1:9" ht="16.5">
-      <c r="A45" s="181"/>
-      <c r="B45" s="184"/>
+      <c r="A45" s="182"/>
+      <c r="B45" s="185"/>
       <c r="C45" s="130">
         <v>5</v>
       </c>
       <c r="D45" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E45" s="144">
         <f>+'[1]01'!F45+'[1]02'!F45+'[1]03'!F45+'[1]04'!F45+'[1]05'!F45+'[1]06'!F45+'[1]07'!F45+'[1]08'!F45+'[1]09'!F45+'[1]10'!F45+'[1]11'!F45+'[1]12'!F45+'[1]13'!F45+'[1]14'!F45+'[1]15'!F45+'[1]16'!F45+'[1]17'!F45+'[1]18'!F45+'[1]19'!F45+'[1]20'!F45+'[1]21'!F45+'[1]22'!F45+'[1]23'!F45+'[1]24'!F45+'[1]25'!F45+'[1]26'!F45+'[1]27'!F45+'[1]28'!F45+'[1]29'!F45+'[1]30'!F45+'[1]31'!F45</f>
@@ -19732,10 +19709,10 @@
     <row r="46" spans="1:9" ht="16.5">
       <c r="A46" s="126"/>
       <c r="B46" s="126"/>
-      <c r="C46" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="178"/>
+      <c r="C46" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="187"/>
       <c r="E46" s="146">
         <f>SUM(E40:E45)</f>
         <v>1161</v>
@@ -19770,45 +19747,45 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B48" s="129" t="s">
+      <c r="D48" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C48" s="129" t="s">
+      <c r="E48" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D48" s="129" t="s">
+      <c r="F48" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="129" t="s">
+      <c r="G48" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F48" s="129" t="s">
+      <c r="H48" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G48" s="129" t="s">
+      <c r="I48" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H48" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I48" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="49" spans="1:9" ht="16.5">
-      <c r="A49" s="179">
+      <c r="A49" s="180">
         <v>0.01</v>
       </c>
-      <c r="B49" s="182" t="s">
-        <v>105</v>
+      <c r="B49" s="183" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="130">
         <v>1</v>
       </c>
       <c r="D49" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E49" s="144">
         <f>+'[1]01'!F49+'[1]02'!F49+'[1]03'!F49+'[1]04'!F49+'[1]05'!F49+'[1]06'!F49+'[1]07'!F49+'[1]08'!F49+'[1]09'!F49+'[1]10'!F49+'[1]11'!F49+'[1]12'!F49+'[1]13'!F49+'[1]14'!F49+'[1]15'!F49+'[1]16'!F49+'[1]17'!F49+'[1]18'!F49+'[1]19'!F49+'[1]20'!F49+'[1]21'!F49+'[1]22'!F49+'[1]23'!F49+'[1]24'!F49+'[1]25'!F49+'[1]26'!F49+'[1]27'!F49+'[1]28'!F49+'[1]29'!F49+'[1]30'!F49+'[1]31'!F49</f>
@@ -19832,13 +19809,13 @@
       </c>
     </row>
     <row r="50" spans="1:9" ht="16.5">
-      <c r="A50" s="180"/>
-      <c r="B50" s="183"/>
+      <c r="A50" s="181"/>
+      <c r="B50" s="184"/>
       <c r="C50" s="130">
         <v>2</v>
       </c>
       <c r="D50" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E50" s="144">
         <f>+'[1]01'!F50+'[1]02'!F50+'[1]03'!F50+'[1]04'!F50+'[1]05'!F50+'[1]06'!F50+'[1]07'!F50+'[1]08'!F50+'[1]09'!F50+'[1]10'!F50+'[1]11'!F50+'[1]12'!F50+'[1]13'!F50+'[1]14'!F50+'[1]15'!F50+'[1]16'!F50+'[1]17'!F50+'[1]18'!F50+'[1]19'!F50+'[1]20'!F50+'[1]21'!F50+'[1]22'!F50+'[1]23'!F50+'[1]24'!F50+'[1]25'!F50+'[1]26'!F50+'[1]27'!F50+'[1]28'!F50+'[1]29'!F50+'[1]30'!F50+'[1]31'!F50</f>
@@ -19862,13 +19839,13 @@
       </c>
     </row>
     <row r="51" spans="1:9" ht="16.5">
-      <c r="A51" s="180"/>
-      <c r="B51" s="183"/>
+      <c r="A51" s="181"/>
+      <c r="B51" s="184"/>
       <c r="C51" s="130">
         <v>2</v>
       </c>
       <c r="D51" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E51" s="144">
         <f>+'[1]01'!F51+'[1]02'!F51+'[1]03'!F51+'[1]04'!F51+'[1]05'!F51+'[1]06'!F51+'[1]07'!F51+'[1]08'!F51+'[1]09'!F51+'[1]10'!F51+'[1]11'!F51+'[1]12'!F51+'[1]13'!F51+'[1]14'!F51+'[1]15'!F51+'[1]16'!F51+'[1]17'!F51+'[1]18'!F51+'[1]19'!F51+'[1]20'!F51+'[1]21'!F51+'[1]22'!F51+'[1]23'!F51+'[1]24'!F51+'[1]25'!F51+'[1]26'!F51+'[1]27'!F51+'[1]28'!F51+'[1]29'!F51+'[1]30'!F51+'[1]31'!F51</f>
@@ -19892,13 +19869,13 @@
       </c>
     </row>
     <row r="52" spans="1:9" ht="16.5">
-      <c r="A52" s="180"/>
-      <c r="B52" s="183"/>
+      <c r="A52" s="181"/>
+      <c r="B52" s="184"/>
       <c r="C52" s="130">
         <v>3</v>
       </c>
       <c r="D52" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E52" s="144">
         <f>+'[1]01'!F52+'[1]02'!F52+'[1]03'!F52+'[1]04'!F52+'[1]05'!F52+'[1]06'!F52+'[1]07'!F52+'[1]08'!F52+'[1]09'!F52+'[1]10'!F52+'[1]11'!F52+'[1]12'!F52+'[1]13'!F52+'[1]14'!F52+'[1]15'!F52+'[1]16'!F52+'[1]17'!F52+'[1]18'!F52+'[1]19'!F52+'[1]20'!F52+'[1]21'!F52+'[1]22'!F52+'[1]23'!F52+'[1]24'!F52+'[1]25'!F52+'[1]26'!F52+'[1]27'!F52+'[1]28'!F52+'[1]29'!F52+'[1]30'!F52+'[1]31'!F52</f>
@@ -19922,13 +19899,13 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="16.5">
-      <c r="A53" s="180"/>
-      <c r="B53" s="183"/>
+      <c r="A53" s="181"/>
+      <c r="B53" s="184"/>
       <c r="C53" s="130">
         <v>4</v>
       </c>
       <c r="D53" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E53" s="144">
         <f>+'[1]01'!F53+'[1]02'!F53+'[1]03'!F53+'[1]04'!F53+'[1]05'!F53+'[1]06'!F53+'[1]07'!F53+'[1]08'!F53+'[1]09'!F53+'[1]10'!F53+'[1]11'!F53+'[1]12'!F53+'[1]13'!F53+'[1]14'!F53+'[1]15'!F53+'[1]16'!F53+'[1]17'!F53+'[1]18'!F53+'[1]19'!F53+'[1]20'!F53+'[1]21'!F53+'[1]22'!F53+'[1]23'!F53+'[1]24'!F53+'[1]25'!F53+'[1]26'!F53+'[1]27'!F53+'[1]28'!F53+'[1]29'!F53+'[1]30'!F53+'[1]31'!F53</f>
@@ -19952,13 +19929,13 @@
       </c>
     </row>
     <row r="54" spans="1:9" ht="16.5">
-      <c r="A54" s="181"/>
-      <c r="B54" s="184"/>
+      <c r="A54" s="182"/>
+      <c r="B54" s="185"/>
       <c r="C54" s="130">
         <v>5</v>
       </c>
       <c r="D54" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E54" s="144">
         <f>+'[1]01'!F54+'[1]02'!F54+'[1]03'!F54+'[1]04'!F54+'[1]05'!F54+'[1]06'!F54+'[1]07'!F54+'[1]08'!F54+'[1]09'!F54+'[1]10'!F54+'[1]11'!F54+'[1]12'!F54+'[1]13'!F54+'[1]14'!F54+'[1]15'!F54+'[1]16'!F54+'[1]17'!F54+'[1]18'!F54+'[1]19'!F54+'[1]20'!F54+'[1]21'!F54+'[1]22'!F54+'[1]23'!F54+'[1]24'!F54+'[1]25'!F54+'[1]26'!F54+'[1]27'!F54+'[1]28'!F54+'[1]29'!F54+'[1]30'!F54+'[1]31'!F54</f>
@@ -19984,10 +19961,10 @@
     <row r="55" spans="1:9" ht="16.5">
       <c r="A55" s="126"/>
       <c r="B55" s="126"/>
-      <c r="C55" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" s="178"/>
+      <c r="C55" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="187"/>
       <c r="E55" s="146">
         <f>SUM(E49:E54)</f>
         <v>138</v>
@@ -20022,45 +19999,45 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B57" s="129" t="s">
+      <c r="D57" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="129" t="s">
+      <c r="E57" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D57" s="129" t="s">
+      <c r="F57" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E57" s="129" t="s">
+      <c r="G57" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F57" s="129" t="s">
+      <c r="H57" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G57" s="129" t="s">
+      <c r="I57" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H57" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I57" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="58" spans="1:9" ht="16.5">
-      <c r="A58" s="179">
+      <c r="A58" s="180">
         <v>0.01</v>
       </c>
-      <c r="B58" s="182" t="s">
-        <v>106</v>
+      <c r="B58" s="183" t="s">
+        <v>104</v>
       </c>
       <c r="C58" s="130">
         <v>1</v>
       </c>
       <c r="D58" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E58" s="144">
         <f>+'[1]01'!F58+'[1]02'!F58+'[1]03'!F58+'[1]04'!F58+'[1]05'!F58+'[1]06'!F58+'[1]07'!F58+'[1]08'!F58+'[1]09'!F58+'[1]10'!F58+'[1]11'!F58+'[1]12'!F58+'[1]13'!F58+'[1]14'!F58+'[1]15'!F58+'[1]16'!F58+'[1]17'!F58+'[1]18'!F58+'[1]19'!F58+'[1]20'!F58+'[1]21'!F58+'[1]22'!F58+'[1]23'!F58+'[1]24'!F58+'[1]25'!F58+'[1]26'!F58+'[1]27'!F58+'[1]28'!F58+'[1]29'!F58+'[1]30'!F58+'[1]31'!F58</f>
@@ -20084,11 +20061,11 @@
       </c>
     </row>
     <row r="59" spans="1:9" ht="16.5">
-      <c r="A59" s="180"/>
-      <c r="B59" s="183"/>
+      <c r="A59" s="181"/>
+      <c r="B59" s="184"/>
       <c r="C59" s="130"/>
       <c r="D59" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E59" s="144">
         <f>+'[1]01'!F59+'[1]02'!F59+'[1]03'!F59+'[1]04'!F59+'[1]05'!F59+'[1]06'!F59+'[1]07'!F59+'[1]08'!F59+'[1]09'!F59+'[1]10'!F59+'[1]11'!F59+'[1]12'!F59+'[1]13'!F59+'[1]14'!F59+'[1]15'!F59+'[1]16'!F59+'[1]17'!F59+'[1]18'!F59+'[1]19'!F59+'[1]20'!F59+'[1]21'!F59+'[1]22'!F59+'[1]23'!F59+'[1]24'!F59+'[1]25'!F59+'[1]26'!F59+'[1]27'!F59+'[1]28'!F59+'[1]29'!F59+'[1]30'!F59+'[1]31'!F59</f>
@@ -20112,13 +20089,13 @@
       </c>
     </row>
     <row r="60" spans="1:9" ht="16.5">
-      <c r="A60" s="180"/>
-      <c r="B60" s="183"/>
+      <c r="A60" s="181"/>
+      <c r="B60" s="184"/>
       <c r="C60" s="130">
         <v>2</v>
       </c>
       <c r="D60" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E60" s="144">
         <f>+'[1]01'!F60+'[1]02'!F60+'[1]03'!F60+'[1]04'!F60+'[1]05'!F60+'[1]06'!F60+'[1]07'!F60+'[1]08'!F60+'[1]09'!F60+'[1]10'!F60+'[1]11'!F60+'[1]12'!F60+'[1]13'!F60+'[1]14'!F60+'[1]15'!F60+'[1]16'!F60+'[1]17'!F60+'[1]18'!F60+'[1]19'!F60+'[1]20'!F60+'[1]21'!F60+'[1]22'!F60+'[1]23'!F60+'[1]24'!F60+'[1]25'!F60+'[1]26'!F60+'[1]27'!F60+'[1]28'!F60+'[1]29'!F60+'[1]30'!F60+'[1]31'!F60</f>
@@ -20142,13 +20119,13 @@
       </c>
     </row>
     <row r="61" spans="1:9" ht="16.5">
-      <c r="A61" s="180"/>
-      <c r="B61" s="183"/>
+      <c r="A61" s="181"/>
+      <c r="B61" s="184"/>
       <c r="C61" s="130">
         <v>3</v>
       </c>
       <c r="D61" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E61" s="144">
         <f>+'[1]01'!F61+'[1]02'!F61+'[1]03'!F61+'[1]04'!F61+'[1]05'!F61+'[1]06'!F61+'[1]07'!F61+'[1]08'!F61+'[1]09'!F61+'[1]10'!F61+'[1]11'!F61+'[1]12'!F61+'[1]13'!F61+'[1]14'!F61+'[1]15'!F61+'[1]16'!F61+'[1]17'!F61+'[1]18'!F61+'[1]19'!F61+'[1]20'!F61+'[1]21'!F61+'[1]22'!F61+'[1]23'!F61+'[1]24'!F61+'[1]25'!F61+'[1]26'!F61+'[1]27'!F61+'[1]28'!F61+'[1]29'!F61+'[1]30'!F61+'[1]31'!F61</f>
@@ -20172,13 +20149,13 @@
       </c>
     </row>
     <row r="62" spans="1:9" ht="16.5">
-      <c r="A62" s="180"/>
-      <c r="B62" s="183"/>
+      <c r="A62" s="181"/>
+      <c r="B62" s="184"/>
       <c r="C62" s="130">
         <v>4</v>
       </c>
       <c r="D62" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E62" s="144">
         <f>+'[1]01'!F62+'[1]02'!F62+'[1]03'!F62+'[1]04'!F62+'[1]05'!F62+'[1]06'!F62+'[1]07'!F62+'[1]08'!F62+'[1]09'!F62+'[1]10'!F62+'[1]11'!F62+'[1]12'!F62+'[1]13'!F62+'[1]14'!F62+'[1]15'!F62+'[1]16'!F62+'[1]17'!F62+'[1]18'!F62+'[1]19'!F62+'[1]20'!F62+'[1]21'!F62+'[1]22'!F62+'[1]23'!F62+'[1]24'!F62+'[1]25'!F62+'[1]26'!F62+'[1]27'!F62+'[1]28'!F62+'[1]29'!F62+'[1]30'!F62+'[1]31'!F62</f>
@@ -20202,13 +20179,13 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="16.5">
-      <c r="A63" s="181"/>
-      <c r="B63" s="184"/>
+      <c r="A63" s="182"/>
+      <c r="B63" s="185"/>
       <c r="C63" s="130">
         <v>5</v>
       </c>
       <c r="D63" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E63" s="144">
         <f>+'[1]01'!F63+'[1]02'!F63+'[1]03'!F63+'[1]04'!F63+'[1]05'!F63+'[1]06'!F63+'[1]07'!F63+'[1]08'!F63+'[1]09'!F63+'[1]10'!F63+'[1]11'!F63+'[1]12'!F63+'[1]13'!F63+'[1]14'!F63+'[1]15'!F63+'[1]16'!F63+'[1]17'!F63+'[1]18'!F63+'[1]19'!F63+'[1]20'!F63+'[1]21'!F63+'[1]22'!F63+'[1]23'!F63+'[1]24'!F63+'[1]25'!F63+'[1]26'!F63+'[1]27'!F63+'[1]28'!F63+'[1]29'!F63+'[1]30'!F63+'[1]31'!F63</f>
@@ -20234,10 +20211,10 @@
     <row r="64" spans="1:9" ht="16.5">
       <c r="A64" s="126"/>
       <c r="B64" s="126"/>
-      <c r="C64" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D64" s="178"/>
+      <c r="C64" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" s="187"/>
       <c r="E64" s="146">
         <f>SUM(E58:E63)</f>
         <v>18</v>
@@ -20272,45 +20249,45 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C66" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B66" s="129" t="s">
+      <c r="D66" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C66" s="129" t="s">
+      <c r="E66" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D66" s="129" t="s">
+      <c r="F66" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E66" s="129" t="s">
+      <c r="G66" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F66" s="129" t="s">
+      <c r="H66" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G66" s="129" t="s">
+      <c r="I66" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H66" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I66" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="67" spans="1:9" ht="16.5">
-      <c r="A67" s="179">
+      <c r="A67" s="180">
         <v>0.01</v>
       </c>
-      <c r="B67" s="182" t="s">
-        <v>107</v>
+      <c r="B67" s="183" t="s">
+        <v>105</v>
       </c>
       <c r="C67" s="130">
         <v>1</v>
       </c>
       <c r="D67" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E67" s="149">
         <f>+'[1]01'!F67+'[1]02'!F67+'[1]03'!F67+'[1]04'!F67+'[1]05'!F67+'[1]06'!F67+'[1]07'!F67+'[1]08'!F67+'[1]09'!F67+'[1]10'!F67+'[1]11'!F67+'[1]12'!F67+'[1]13'!F67+'[1]14'!F67+'[1]15'!F67+'[1]16'!F67+'[1]17'!F67+'[1]18'!F67+'[1]19'!F67+'[1]20'!F67+'[1]21'!F67+'[1]22'!F67+'[1]23'!F67+'[1]24'!F67+'[1]25'!F67+'[1]26'!F67+'[1]27'!F67+'[1]28'!F67+'[1]29'!F67+'[1]30'!F67+'[1]31'!F67</f>
@@ -20334,13 +20311,13 @@
       </c>
     </row>
     <row r="68" spans="1:9" ht="16.5">
-      <c r="A68" s="180"/>
-      <c r="B68" s="183"/>
+      <c r="A68" s="181"/>
+      <c r="B68" s="184"/>
       <c r="C68" s="130">
         <v>2</v>
       </c>
       <c r="D68" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E68" s="149">
         <f>+'[1]01'!F68+'[1]02'!F68+'[1]03'!F68+'[1]04'!F68+'[1]05'!F68+'[1]06'!F68+'[1]07'!F68+'[1]08'!F68+'[1]09'!F68+'[1]10'!F68+'[1]11'!F68+'[1]12'!F68+'[1]13'!F68+'[1]14'!F68+'[1]15'!F68+'[1]16'!F68+'[1]17'!F68+'[1]18'!F68+'[1]19'!F68+'[1]20'!F68+'[1]21'!F68+'[1]22'!F68+'[1]23'!F68+'[1]24'!F68+'[1]25'!F68+'[1]26'!F68+'[1]27'!F68+'[1]28'!F68+'[1]29'!F68+'[1]30'!F68+'[1]31'!F68</f>
@@ -20364,13 +20341,13 @@
       </c>
     </row>
     <row r="69" spans="1:9" ht="16.5">
-      <c r="A69" s="180"/>
-      <c r="B69" s="183"/>
+      <c r="A69" s="181"/>
+      <c r="B69" s="184"/>
       <c r="C69" s="130">
         <v>3</v>
       </c>
       <c r="D69" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E69" s="149">
         <f>+'[1]01'!F69+'[1]02'!F69+'[1]03'!F69+'[1]04'!F69+'[1]05'!F69+'[1]06'!F69+'[1]07'!F69+'[1]08'!F69+'[1]09'!F69+'[1]10'!F69+'[1]11'!F69+'[1]12'!F69+'[1]13'!F69+'[1]14'!F69+'[1]15'!F69+'[1]16'!F69+'[1]17'!F69+'[1]18'!F69+'[1]19'!F69+'[1]20'!F69+'[1]21'!F69+'[1]22'!F69+'[1]23'!F69+'[1]24'!F69+'[1]25'!F69+'[1]26'!F69+'[1]27'!F69+'[1]28'!F69+'[1]29'!F69+'[1]30'!F69+'[1]31'!F69</f>
@@ -20394,13 +20371,13 @@
       </c>
     </row>
     <row r="70" spans="1:9" ht="16.5">
-      <c r="A70" s="180"/>
-      <c r="B70" s="183"/>
+      <c r="A70" s="181"/>
+      <c r="B70" s="184"/>
       <c r="C70" s="130">
         <v>4</v>
       </c>
       <c r="D70" s="130" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E70" s="149">
         <f>+'[1]01'!F70+'[1]02'!F70+'[1]03'!F70+'[1]04'!F70+'[1]05'!F70+'[1]06'!F70+'[1]07'!F70+'[1]08'!F70+'[1]09'!F70+'[1]10'!F70+'[1]11'!F70+'[1]12'!F70+'[1]13'!F70+'[1]14'!F70+'[1]15'!F70+'[1]16'!F70+'[1]17'!F70+'[1]18'!F70+'[1]19'!F70+'[1]20'!F70+'[1]21'!F70+'[1]22'!F70+'[1]23'!F70+'[1]24'!F70+'[1]25'!F70+'[1]26'!F70+'[1]27'!F70+'[1]28'!F70+'[1]29'!F70+'[1]30'!F70+'[1]31'!F70</f>
@@ -20424,13 +20401,13 @@
       </c>
     </row>
     <row r="71" spans="1:9" ht="16.5">
-      <c r="A71" s="180"/>
-      <c r="B71" s="183"/>
+      <c r="A71" s="181"/>
+      <c r="B71" s="184"/>
       <c r="C71" s="130">
         <v>5</v>
       </c>
       <c r="D71" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E71" s="149">
         <f>+'[1]01'!F71+'[1]02'!F71+'[1]03'!F71+'[1]04'!F71+'[1]05'!F71+'[1]06'!F71+'[1]07'!F71+'[1]08'!F71+'[1]09'!F71+'[1]10'!F71+'[1]11'!F71+'[1]12'!F71+'[1]13'!F71+'[1]14'!F71+'[1]15'!F71+'[1]16'!F71+'[1]17'!F71+'[1]18'!F71+'[1]19'!F71+'[1]20'!F71+'[1]21'!F71+'[1]22'!F71+'[1]23'!F71+'[1]24'!F71+'[1]25'!F71+'[1]26'!F71+'[1]27'!F71+'[1]28'!F71+'[1]29'!F71+'[1]30'!F71+'[1]31'!F71</f>
@@ -20454,13 +20431,13 @@
       </c>
     </row>
     <row r="72" spans="1:9" ht="16.5">
-      <c r="A72" s="181"/>
-      <c r="B72" s="184"/>
+      <c r="A72" s="182"/>
+      <c r="B72" s="185"/>
       <c r="C72" s="130">
         <v>6</v>
       </c>
       <c r="D72" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E72" s="149">
         <f>+'[1]01'!F72+'[1]02'!F72+'[1]03'!F72+'[1]04'!F72+'[1]05'!F72+'[1]06'!F72+'[1]07'!F72+'[1]08'!F72+'[1]09'!F72+'[1]10'!F72+'[1]11'!F72+'[1]12'!F72+'[1]13'!F72+'[1]14'!F72+'[1]15'!F72+'[1]16'!F72+'[1]17'!F72+'[1]18'!F72+'[1]19'!F72+'[1]20'!F72+'[1]21'!F72+'[1]22'!F72+'[1]23'!F72+'[1]24'!F72+'[1]25'!F72+'[1]26'!F72+'[1]27'!F72+'[1]28'!F72+'[1]29'!F72+'[1]30'!F72+'[1]31'!F72</f>
@@ -20486,10 +20463,10 @@
     <row r="73" spans="1:9" ht="16.5">
       <c r="A73" s="126"/>
       <c r="B73" s="126"/>
-      <c r="C73" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D73" s="178"/>
+      <c r="C73" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="187"/>
       <c r="E73" s="151">
         <f>SUM(E67:E72)</f>
         <v>3.8085000000000004</v>
@@ -20524,45 +20501,45 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="129" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="129" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="129" t="s">
         <v>83</v>
       </c>
-      <c r="B75" s="129" t="s">
+      <c r="D75" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="129" t="s">
+      <c r="E75" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="129" t="s">
+      <c r="F75" s="129" t="s">
         <v>86</v>
       </c>
-      <c r="E75" s="129" t="s">
+      <c r="G75" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="F75" s="129" t="s">
+      <c r="H75" s="129" t="s">
         <v>88</v>
       </c>
-      <c r="G75" s="129" t="s">
+      <c r="I75" s="129" t="s">
         <v>89</v>
       </c>
-      <c r="H75" s="129" t="s">
-        <v>90</v>
-      </c>
-      <c r="I75" s="129" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="76" spans="1:9" ht="16.5">
-      <c r="A76" s="179">
+      <c r="A76" s="180">
         <v>0.01</v>
       </c>
-      <c r="B76" s="182" t="s">
-        <v>108</v>
+      <c r="B76" s="183" t="s">
+        <v>106</v>
       </c>
       <c r="C76" s="130">
         <v>1</v>
       </c>
       <c r="D76" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E76" s="144">
         <f>+'[1]01'!F76+'[1]02'!F76+'[1]03'!F76+'[1]04'!F76+'[1]05'!F76+'[1]06'!F76+'[1]07'!F76+'[1]08'!F76+'[1]09'!F76+'[1]10'!F76+'[1]11'!F76+'[1]12'!F76+'[1]13'!F76+'[1]14'!F76+'[1]15'!F76+'[1]16'!F76+'[1]17'!F76+'[1]18'!F76+'[1]19'!F76+'[1]20'!F76+'[1]21'!F76+'[1]22'!F76+'[1]23'!F76+'[1]24'!F76+'[1]25'!F76+'[1]26'!F76+'[1]27'!F76+'[1]28'!F76+'[1]29'!F76+'[1]30'!F76+'[1]31'!F76</f>
@@ -20586,13 +20563,13 @@
       </c>
     </row>
     <row r="77" spans="1:9" ht="16.5">
-      <c r="A77" s="180"/>
-      <c r="B77" s="183"/>
+      <c r="A77" s="181"/>
+      <c r="B77" s="184"/>
       <c r="C77" s="130">
         <v>2</v>
       </c>
       <c r="D77" s="130" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E77" s="144">
         <f>+'[1]01'!F77+'[1]02'!F77+'[1]03'!F77+'[1]04'!F77+'[1]05'!F77+'[1]06'!F77+'[1]07'!F77+'[1]08'!F77+'[1]09'!F77+'[1]10'!F77+'[1]11'!F77+'[1]12'!F77+'[1]13'!F77+'[1]14'!F77+'[1]15'!F77+'[1]16'!F77+'[1]17'!F77+'[1]18'!F77+'[1]19'!F77+'[1]20'!F77+'[1]21'!F77+'[1]22'!F77+'[1]23'!F77+'[1]24'!F77+'[1]25'!F77+'[1]26'!F77+'[1]27'!F77+'[1]28'!F77+'[1]29'!F77+'[1]30'!F77+'[1]31'!F77</f>
@@ -20616,13 +20593,13 @@
       </c>
     </row>
     <row r="78" spans="1:9" ht="16.5">
-      <c r="A78" s="180"/>
-      <c r="B78" s="183"/>
+      <c r="A78" s="181"/>
+      <c r="B78" s="184"/>
       <c r="C78" s="130">
         <v>3</v>
       </c>
       <c r="D78" s="130" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E78" s="144">
         <f>+'[1]01'!F78+'[1]02'!F78+'[1]03'!F78+'[1]04'!F78+'[1]05'!F78+'[1]06'!F78+'[1]07'!F78+'[1]08'!F78+'[1]09'!F78+'[1]10'!F78+'[1]11'!F78+'[1]12'!F78+'[1]13'!F78+'[1]14'!F78+'[1]15'!F78+'[1]16'!F78+'[1]17'!F78+'[1]18'!F78+'[1]19'!F78+'[1]20'!F78+'[1]21'!F78+'[1]22'!F78+'[1]23'!F78+'[1]24'!F78+'[1]25'!F78+'[1]26'!F78+'[1]27'!F78+'[1]28'!F78+'[1]29'!F78+'[1]30'!F78+'[1]31'!F78</f>
@@ -20646,13 +20623,13 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="16.5">
-      <c r="A79" s="180"/>
-      <c r="B79" s="183"/>
+      <c r="A79" s="181"/>
+      <c r="B79" s="184"/>
       <c r="C79" s="130">
         <v>4</v>
       </c>
       <c r="D79" s="130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E79" s="144">
         <f>+'[1]01'!F79+'[1]02'!F79+'[1]03'!F79+'[1]04'!F79+'[1]05'!F79+'[1]06'!F79+'[1]07'!F79+'[1]08'!F79+'[1]09'!F79+'[1]10'!F79+'[1]11'!F79+'[1]12'!F79+'[1]13'!F79+'[1]14'!F79+'[1]15'!F79+'[1]16'!F79+'[1]17'!F79+'[1]18'!F79+'[1]19'!F79+'[1]20'!F79+'[1]21'!F79+'[1]22'!F79+'[1]23'!F79+'[1]24'!F79+'[1]25'!F79+'[1]26'!F79+'[1]27'!F79+'[1]28'!F79+'[1]29'!F79+'[1]30'!F79+'[1]31'!F79</f>
@@ -20676,13 +20653,13 @@
       </c>
     </row>
     <row r="80" spans="1:9" ht="16.5">
-      <c r="A80" s="180"/>
-      <c r="B80" s="183"/>
+      <c r="A80" s="181"/>
+      <c r="B80" s="184"/>
       <c r="C80" s="130">
         <v>5</v>
       </c>
       <c r="D80" s="130" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E80" s="144">
         <f>+'[1]01'!F80+'[1]02'!F80+'[1]03'!F80+'[1]04'!F80+'[1]05'!F80+'[1]06'!F80+'[1]07'!F80+'[1]08'!F80+'[1]09'!F80+'[1]10'!F80+'[1]11'!F80+'[1]12'!F80+'[1]13'!F80+'[1]14'!F80+'[1]15'!F80+'[1]16'!F80+'[1]17'!F80+'[1]18'!F80+'[1]19'!F80+'[1]20'!F80+'[1]21'!F80+'[1]22'!F80+'[1]23'!F80+'[1]24'!F80+'[1]25'!F80+'[1]26'!F80+'[1]27'!F80+'[1]28'!F80+'[1]29'!F80+'[1]30'!F80+'[1]31'!F80</f>
@@ -20706,13 +20683,13 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="16.5">
-      <c r="A81" s="181"/>
-      <c r="B81" s="184"/>
+      <c r="A81" s="182"/>
+      <c r="B81" s="185"/>
       <c r="C81" s="130">
         <v>6</v>
       </c>
       <c r="D81" s="130" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E81" s="144">
         <f>+'[1]01'!F81+'[1]02'!F81+'[1]03'!F81+'[1]04'!F81+'[1]05'!F81+'[1]06'!F81+'[1]07'!F81+'[1]08'!F81+'[1]09'!F81+'[1]10'!F81+'[1]11'!F81+'[1]12'!F81+'[1]13'!F81+'[1]14'!F81+'[1]15'!F81+'[1]16'!F81+'[1]17'!F81+'[1]18'!F81+'[1]19'!F81+'[1]20'!F81+'[1]21'!F81+'[1]22'!F81+'[1]23'!F81+'[1]24'!F81+'[1]25'!F81+'[1]26'!F81+'[1]27'!F81+'[1]28'!F81+'[1]29'!F81+'[1]30'!F81+'[1]31'!F81</f>
@@ -20738,10 +20715,10 @@
     <row r="82" spans="1:9" ht="16.5">
       <c r="A82" s="126"/>
       <c r="B82" s="126"/>
-      <c r="C82" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82" s="178"/>
+      <c r="C82" s="186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" s="187"/>
       <c r="E82" s="151">
         <f>SUM(E76:E81)</f>
         <v>188.65</v>
@@ -20765,24 +20742,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="B4:B9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:A36"/>
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:A45"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
     <mergeCell ref="C73:D73"/>
     <mergeCell ref="A76:A81"/>
     <mergeCell ref="B76:B81"/>
@@ -20793,6 +20752,24 @@
     <mergeCell ref="C64:D64"/>
     <mergeCell ref="A67:A72"/>
     <mergeCell ref="B67:B72"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:A45"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B13:B18"/>
   </mergeCells>
   <pageMargins left="0.17" right="0.17" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -20810,74 +20787,74 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:15">
-      <c r="B5" s="186" t="s">
+      <c r="B5" s="188" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="B8" s="191" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="189">
+        <v>46174</v>
+      </c>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="190" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="190" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="190" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="186"/>
-      <c r="I5" s="186"/>
-      <c r="J5" s="186"/>
-      <c r="K5" s="186"/>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="189" t="s">
+      <c r="J8" s="190"/>
+      <c r="K8" s="190"/>
+      <c r="N8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="192"/>
+      <c r="C9" s="153" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="187">
-        <v>46174</v>
-      </c>
-      <c r="D8" s="187"/>
-      <c r="E8" s="187"/>
-      <c r="F8" s="187"/>
-      <c r="G8" s="188" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="188" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="188" t="s">
+      <c r="D9" s="153" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="153" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
-      <c r="N8" t="s">
+      <c r="F9" s="153" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="190"/>
+      <c r="H9" s="190"/>
+      <c r="I9" s="153" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="153" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="153" t="s">
+        <v>114</v>
+      </c>
+      <c r="N9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="B9" s="190"/>
-      <c r="C9" s="153" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="153" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="153" t="s">
-        <v>114</v>
-      </c>
-      <c r="F9" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="188"/>
-      <c r="H9" s="188"/>
-      <c r="I9" s="153" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="153" t="s">
-        <v>115</v>
-      </c>
-      <c r="K9" s="153" t="s">
-        <v>116</v>
-      </c>
-      <c r="N9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:15">
@@ -20892,18 +20869,18 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="N10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:15">
       <c r="B11" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1">
         <v>306</v>
@@ -20930,18 +20907,18 @@
         <v>-163331.99999999924</v>
       </c>
       <c r="N11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:15">
       <c r="B12" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" s="1">
         <v>474</v>
@@ -20968,18 +20945,18 @@
         <v>141499.10000000533</v>
       </c>
       <c r="N12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:15">
       <c r="B13" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D13" s="1">
         <v>1855</v>
@@ -21008,10 +20985,10 @@
     </row>
     <row r="14" spans="2:15">
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D14" s="1">
         <v>3.8085000000000004</v>
@@ -21040,10 +21017,10 @@
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15" s="1">
         <v>5270</v>
@@ -21072,10 +21049,10 @@
     </row>
     <row r="16" spans="2:15">
       <c r="B16" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -21098,10 +21075,10 @@
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" s="1">
         <v>1161</v>
@@ -21130,10 +21107,10 @@
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1">
         <v>138</v>
@@ -21162,10 +21139,10 @@
     </row>
     <row r="19" spans="2:11">
       <c r="B19" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D19" s="1">
         <v>188.65</v>
@@ -21194,10 +21171,10 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -21224,10 +21201,10 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D21" s="1">
         <v>18</v>
@@ -21272,31 +21249,31 @@
     </row>
     <row r="24" spans="2:11">
       <c r="C24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="2:11">
       <c r="B27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="2:11">
       <c r="B28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C28">
         <v>14</v>
@@ -21310,7 +21287,7 @@
     </row>
     <row r="29" spans="2:11">
       <c r="B29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C29">
         <v>17</v>
@@ -21324,7 +21301,7 @@
     </row>
     <row r="30" spans="2:11">
       <c r="B30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -21338,7 +21315,7 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -21352,7 +21329,7 @@
     </row>
     <row r="32" spans="2:11">
       <c r="B32" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -21366,7 +21343,7 @@
     </row>
     <row r="33" spans="2:10">
       <c r="B33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -21380,7 +21357,7 @@
     </row>
     <row r="34" spans="2:10">
       <c r="B34" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -21394,7 +21371,7 @@
     </row>
     <row r="35" spans="2:10">
       <c r="B35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -21408,7 +21385,7 @@
     </row>
     <row r="36" spans="2:10">
       <c r="B36" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C36">
         <v>13.5</v>
@@ -21422,7 +21399,7 @@
     </row>
     <row r="37" spans="2:10">
       <c r="B37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E37">
         <v>65600</v>
@@ -21430,26 +21407,26 @@
     </row>
     <row r="40" spans="2:10">
       <c r="B40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="2:10">
       <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>135</v>
+      </c>
+      <c r="D41" t="s">
         <v>136</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>137</v>
-      </c>
-      <c r="D41" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="42" spans="2:10">
       <c r="B42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C42">
         <v>43</v>
@@ -21463,7 +21440,7 @@
     </row>
     <row r="43" spans="2:10">
       <c r="B43" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C43">
         <v>75</v>
@@ -21477,7 +21454,7 @@
     </row>
     <row r="44" spans="2:10">
       <c r="B44" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C44">
         <v>1376</v>
@@ -21491,7 +21468,7 @@
     </row>
     <row r="45" spans="2:10">
       <c r="B45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E45">
         <v>270074</v>
